--- a/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040B5EC6-1E7F-4024-AAAD-ACA095137182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15804FC2-C2F8-4EB2-A67B-51C92B5B11D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="227">
   <si>
     <t>TOTAL</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>REEMPLAZOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANOTACION </t>
   </si>
   <si>
     <t>FECHA DE LA ANOTACION:</t>
@@ -607,25 +604,6 @@
     <t>Inicio del mes</t>
   </si>
   <si>
-    <t>Silvina albaneda volvio a no respetar centavos, transfirio: $ 249002,48 - Sumo: $243079,14 dpto
-$5923,34 cochera</t>
-  </si>
-  <si>
-    <t>14 y 34</t>
-  </si>
-  <si>
-    <t>Mayra Gimenez</t>
-  </si>
-  <si>
-    <t>Transfirio $229.441 el 13/08 - Dice que pago $20.000 de mas</t>
-  </si>
-  <si>
-    <t>Cochera 1, 15 y 22</t>
-  </si>
-  <si>
-    <t>Dice que no tiene deuda en las cocheras adjunta depositos por $160.000 el 29/06 - $137.000 el 16/07 - $152.000 el 21/08</t>
-  </si>
-  <si>
     <t>Transf 17/8</t>
   </si>
   <si>
@@ -735,6 +713,12 @@
   </si>
   <si>
     <t>Transf 09/09</t>
+  </si>
+  <si>
+    <t>Maria Belen Gomez</t>
+  </si>
+  <si>
+    <t>6C $251.908 el 16/09 y $923.325 el 29/09</t>
   </si>
 </sst>
 </file>
@@ -916,7 +900,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -985,12 +969,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1009,13 +987,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FF74FA84"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1522,7 +1494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1691,13 +1663,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1728,10 +1694,10 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1739,20 +1705,20 @@
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="13" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="13" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1816,18 +1782,17 @@
     <xf numFmtId="44" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1835,15 +1800,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1863,191 +1822,196 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2435,12 +2399,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="217" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218"/>
+      <c r="B1" s="207" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="208"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2453,12 +2417,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="219" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="220"/>
+      <c r="B3" s="209" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2473,10 +2437,10 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2486,7 +2450,7 @@
     </row>
     <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2496,54 +2460,54 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="221" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="221"/>
+      <c r="B8" s="211" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="211"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="221"/>
-      <c r="C9" s="221"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="221"/>
-      <c r="C10" s="221"/>
+      <c r="B10" s="211"/>
+      <c r="C10" s="211"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="222" t="s">
-        <v>144</v>
-      </c>
-      <c r="B13" s="222"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
+      <c r="A13" s="212" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="212"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="222"/>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="222"/>
-      <c r="B15" s="222"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="222"/>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2561,7 +2525,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -2569,24 +2533,24 @@
       <c r="E21" s="96"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="223" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" s="224"/>
+      <c r="A22" s="213" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="214"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="207">
+      <c r="D22" s="194">
         <v>1460357.72</v>
       </c>
       <c r="E22" s="97"/>
       <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="210" t="s">
+      <c r="A23" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="211"/>
-      <c r="C23" s="150"/>
-      <c r="D23" s="207">
+      <c r="B23" s="201"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="194">
         <v>-317627.71999999997</v>
       </c>
       <c r="E23" s="21"/>
@@ -2594,22 +2558,22 @@
       <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="210" t="s">
+      <c r="A24" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="211"/>
-      <c r="C24" s="150"/>
-      <c r="D24" s="194"/>
+      <c r="B24" s="201"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="187"/>
       <c r="E24" s="21"/>
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="145"/>
       <c r="D25" s="22"/>
       <c r="E25" s="98">
         <f>SUM(D22:D24)</f>
@@ -2618,45 +2582,45 @@
       <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="151" t="s">
+      <c r="A26" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="151"/>
-      <c r="C26" s="151"/>
+      <c r="B26" s="145"/>
+      <c r="C26" s="145"/>
       <c r="D26" s="22"/>
       <c r="E26" s="99"/>
       <c r="F26" s="38"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="150"/>
-      <c r="B27" s="150"/>
-      <c r="C27" s="150"/>
+      <c r="A27" s="144"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
       <c r="D27" s="28"/>
       <c r="E27" s="110"/>
       <c r="F27" s="38"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="150"/>
-      <c r="B28" s="150"/>
-      <c r="C28" s="150"/>
+      <c r="A28" s="144"/>
+      <c r="B28" s="144"/>
+      <c r="C28" s="144"/>
       <c r="D28" s="28"/>
       <c r="E28" s="110"/>
       <c r="F28" s="38"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="150"/>
-      <c r="B29" s="150"/>
-      <c r="C29" s="150"/>
+      <c r="A29" s="144"/>
+      <c r="B29" s="144"/>
+      <c r="C29" s="144"/>
       <c r="D29" s="28"/>
       <c r="E29" s="110"/>
       <c r="F29" s="38"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="151" t="s">
+      <c r="A30" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="152"/>
-      <c r="C30" s="152"/>
+      <c r="B30" s="146"/>
+      <c r="C30" s="146"/>
       <c r="D30" s="71"/>
       <c r="E30" s="101">
         <f>SUM(D27:D29)</f>
@@ -2668,66 +2632,66 @@
       <c r="A31" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="151"/>
-      <c r="C31" s="151"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
       <c r="D31" s="22"/>
       <c r="E31" s="99"/>
       <c r="F31" s="38"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="150" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="153"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="272">
+      <c r="A32" s="144" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="147"/>
+      <c r="C32" s="147"/>
+      <c r="D32" s="199">
         <v>718331.03</v>
       </c>
       <c r="E32" s="100" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="150" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" s="150" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="153"/>
+      <c r="A33" s="144" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="144" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="147"/>
       <c r="D33" s="28">
         <v>182823.01</v>
       </c>
       <c r="E33" s="100" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="150" t="s">
+      <c r="A34" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="272">
+      <c r="B34" s="147"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="199">
         <v>65716.08</v>
       </c>
       <c r="E34" s="100" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="150" t="s">
+      <c r="A35" s="144" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="153"/>
-      <c r="C35" s="153"/>
-      <c r="D35" s="272">
+      <c r="B35" s="147"/>
+      <c r="C35" s="147"/>
+      <c r="D35" s="199">
         <v>7301.79</v>
       </c>
       <c r="E35" s="100" t="str">
@@ -2738,12 +2702,12 @@
       <c r="G35" s="40"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="153"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="272">
+      <c r="B36" s="147"/>
+      <c r="C36" s="147"/>
+      <c r="D36" s="199">
         <v>116816.78</v>
       </c>
       <c r="E36" s="100" t="str">
@@ -2753,11 +2717,11 @@
       <c r="F36" s="38"/>
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="151" t="s">
+      <c r="A37" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="151"/>
-      <c r="C37" s="151"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="145"/>
       <c r="D37" s="22"/>
       <c r="E37" s="32">
         <f>SUM(D32:D36)</f>
@@ -2769,33 +2733,33 @@
       <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="151"/>
-      <c r="C38" s="151"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="145"/>
       <c r="D38" s="23"/>
       <c r="E38" s="101"/>
       <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="225" t="s">
+      <c r="A39" s="215" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="216"/>
+      <c r="C39" s="148"/>
+      <c r="D39" s="188">
+        <v>205033.71</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="38"/>
+    </row>
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="215" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="226"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="195">
-        <v>205033.71</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="F39" s="38"/>
-    </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="225" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="226"/>
-      <c r="C40" s="154"/>
-      <c r="D40" s="195">
+      <c r="B40" s="216"/>
+      <c r="C40" s="148"/>
+      <c r="D40" s="188">
         <v>0</v>
       </c>
       <c r="E40" s="21" t="str">
@@ -2805,11 +2769,11 @@
       <c r="F40" s="38"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="151" t="s">
+      <c r="A41" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="151"/>
-      <c r="C41" s="151"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="145"/>
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
@@ -2821,92 +2785,92 @@
       <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="152"/>
-      <c r="C42" s="152"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
       <c r="D42" s="25"/>
       <c r="E42" s="102"/>
       <c r="F42" s="38"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="270">
+      <c r="D43" s="197">
         <v>2001312.7</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F43" s="38"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="155"/>
+        <v>64</v>
+      </c>
+      <c r="B44" s="149"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="204">
+      <c r="D44" s="191">
         <v>6637.89</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F44" s="38"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="149" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="33"/>
+      <c r="D45" s="197">
+        <v>883.29</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="215" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="155" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="270">
-        <v>883.29</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="F45" s="38"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="225" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" s="226"/>
+      <c r="B46" s="216"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="204">
+      <c r="D46" s="191">
         <v>542877.21</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F46" s="38"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="156" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="157" t="s">
-        <v>174</v>
+      <c r="A47" s="150" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="151" t="s">
+        <v>173</v>
       </c>
       <c r="C47" s="33"/>
-      <c r="D47" s="270">
+      <c r="D47" s="197">
         <v>42239.197999999997</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F47" s="38"/>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="151" t="s">
+      <c r="A48" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="151"/>
-      <c r="C48" s="151"/>
+      <c r="B48" s="145"/>
+      <c r="C48" s="145"/>
       <c r="D48" s="26"/>
       <c r="E48" s="103">
         <f>SUM(D43:D47)</f>
@@ -2916,170 +2880,170 @@
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="151"/>
-      <c r="C49" s="151"/>
+        <v>62</v>
+      </c>
+      <c r="B49" s="145"/>
+      <c r="C49" s="145"/>
       <c r="D49" s="22"/>
       <c r="E49" s="104"/>
       <c r="F49" s="38"/>
     </row>
     <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="210" t="s">
+      <c r="A50" s="200" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="201"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="191">
+        <v>250600</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="38"/>
+    </row>
+    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="200" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="201"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="197">
+        <v>298200</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="F51" s="38"/>
+    </row>
+    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="215" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="216"/>
+      <c r="C52" s="144"/>
+      <c r="D52" s="191">
+        <v>300000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F52" s="126"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="205" t="s">
+        <v>194</v>
+      </c>
+      <c r="B53" s="206"/>
+      <c r="C53" s="144"/>
+      <c r="D53" s="191">
+        <v>150000</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="126"/>
+    </row>
+    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="205" t="s">
+        <v>195</v>
+      </c>
+      <c r="B54" s="206"/>
+      <c r="C54" s="144"/>
+      <c r="D54" s="191">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="126"/>
+    </row>
+    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="150" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="189"/>
+      <c r="C55" s="144"/>
+      <c r="D55" s="191">
+        <v>240000</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F55" s="126"/>
+    </row>
+    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="205" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" s="206"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="197">
+        <v>50000</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="126"/>
+    </row>
+    <row r="57" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="215" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="216"/>
+      <c r="C57" s="144"/>
+      <c r="D57" s="197">
+        <v>8400</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="F57" s="38"/>
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="200" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="201"/>
+      <c r="C58" s="144"/>
+      <c r="D58" s="191">
+        <v>265200</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F58" s="38"/>
+    </row>
+    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" s="152"/>
+      <c r="C59" s="144"/>
+      <c r="D59" s="191">
+        <v>130500</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="38"/>
+    </row>
+    <row r="60" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="152"/>
+      <c r="C60" s="144"/>
+      <c r="D60" s="191">
+        <v>118800</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="211"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="204">
-        <v>250600</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F50" s="38"/>
-    </row>
-    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="210" t="s">
-        <v>208</v>
-      </c>
-      <c r="B51" s="211"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="270">
-        <v>298200</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="F51" s="38"/>
-    </row>
-    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="225" t="s">
-        <v>200</v>
-      </c>
-      <c r="B52" s="226"/>
-      <c r="C52" s="150"/>
-      <c r="D52" s="204">
-        <v>300000</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F52" s="132"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="215" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="216"/>
-      <c r="C53" s="150"/>
-      <c r="D53" s="204">
-        <v>150000</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" s="132"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="215" t="s">
-        <v>202</v>
-      </c>
-      <c r="B54" s="216"/>
-      <c r="C54" s="150"/>
-      <c r="D54" s="204">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" s="132"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="156" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="200"/>
-      <c r="C55" s="150"/>
-      <c r="D55" s="204">
-        <v>240000</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="F55" s="132"/>
-    </row>
-    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="215" t="s">
-        <v>228</v>
-      </c>
-      <c r="B56" s="216"/>
-      <c r="C56" s="150"/>
-      <c r="D56" s="270">
-        <v>50000</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="F56" s="132"/>
-    </row>
-    <row r="57" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="225" t="s">
-        <v>224</v>
-      </c>
-      <c r="B57" s="226"/>
-      <c r="C57" s="150"/>
-      <c r="D57" s="270">
-        <v>8400</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F57" s="38"/>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="210" t="s">
-        <v>196</v>
-      </c>
-      <c r="B58" s="211"/>
-      <c r="C58" s="150"/>
-      <c r="D58" s="204">
-        <v>265200</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F58" s="38"/>
-    </row>
-    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="193" t="s">
-        <v>186</v>
-      </c>
-      <c r="B59" s="158"/>
-      <c r="C59" s="150"/>
-      <c r="D59" s="204">
-        <v>130500</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="F59" s="38"/>
-    </row>
-    <row r="60" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="193" t="s">
-        <v>186</v>
-      </c>
-      <c r="B60" s="158"/>
-      <c r="C60" s="150"/>
-      <c r="D60" s="204">
-        <v>118800</v>
-      </c>
-      <c r="E60" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="F60" s="132"/>
+      <c r="F60" s="126"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="151" t="s">
+      <c r="A61" s="145" t="s">
         <v>0</v>
       </c>
       <c r="B61" s="29"/>
@@ -3102,49 +3066,49 @@
       <c r="F62" s="38"/>
     </row>
     <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="210" t="s">
-        <v>211</v>
-      </c>
-      <c r="B63" s="211"/>
-      <c r="C63" s="150"/>
-      <c r="D63" s="205">
+      <c r="A63" s="200" t="s">
+        <v>204</v>
+      </c>
+      <c r="B63" s="201"/>
+      <c r="C63" s="144"/>
+      <c r="D63" s="192">
         <v>210000</v>
       </c>
       <c r="E63" s="97"/>
       <c r="F63" s="38"/>
     </row>
     <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="210" t="s">
-        <v>221</v>
-      </c>
-      <c r="B64" s="211"/>
-      <c r="C64" s="150"/>
-      <c r="D64" s="206">
+      <c r="A64" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="B64" s="201"/>
+      <c r="C64" s="144"/>
+      <c r="D64" s="193">
         <v>0</v>
       </c>
       <c r="E64" s="97"/>
       <c r="F64" s="38"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="158"/>
-      <c r="C65" s="150"/>
-      <c r="D65" s="271">
+      <c r="A65" s="153" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" s="152"/>
+      <c r="C65" s="144"/>
+      <c r="D65" s="198">
         <v>50000</v>
       </c>
       <c r="E65" s="97" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F65" s="38"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="151" t="s">
+      <c r="A66" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="151"/>
-      <c r="C66" s="151"/>
+      <c r="B66" s="145"/>
+      <c r="C66" s="145"/>
       <c r="D66" s="22"/>
       <c r="E66" s="98">
         <f>SUM(D63:D65)</f>
@@ -3156,19 +3120,19 @@
       <c r="A67" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B67" s="160"/>
-      <c r="C67" s="151"/>
+      <c r="B67" s="154"/>
+      <c r="C67" s="145"/>
       <c r="D67" s="30"/>
       <c r="E67" s="32"/>
       <c r="F67" s="38"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="161"/>
-      <c r="C68" s="161"/>
-      <c r="D68" s="162">
+        <v>68</v>
+      </c>
+      <c r="B68" s="155"/>
+      <c r="C68" s="155"/>
+      <c r="D68" s="156">
         <v>69000</v>
       </c>
       <c r="E68" s="105"/>
@@ -3176,11 +3140,11 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="B69" s="161"/>
-      <c r="C69" s="161"/>
-      <c r="D69" s="162">
+        <v>174</v>
+      </c>
+      <c r="B69" s="155"/>
+      <c r="C69" s="155"/>
+      <c r="D69" s="156">
         <f>114820.43-36</f>
         <v>114784.43</v>
       </c>
@@ -3188,11 +3152,11 @@
       <c r="F69" s="38"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="163" t="s">
+      <c r="A70" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="B70" s="163"/>
-      <c r="C70" s="163"/>
+      <c r="B70" s="157"/>
+      <c r="C70" s="157"/>
       <c r="D70" s="31"/>
       <c r="E70" s="32">
         <f>SUM(D68:D69)</f>
@@ -3209,35 +3173,35 @@
       <c r="F71" s="38"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="164" t="s">
+      <c r="A72" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="B72" s="164"/>
-      <c r="C72" s="164"/>
+      <c r="B72" s="158"/>
+      <c r="C72" s="158"/>
       <c r="D72" s="35"/>
       <c r="E72" s="36"/>
       <c r="F72" s="38"/>
     </row>
     <row r="73" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="165"/>
+      <c r="A73" s="159"/>
       <c r="B73" s="38"/>
       <c r="C73" s="38"/>
       <c r="D73" s="38"/>
       <c r="E73" s="39"/>
-      <c r="F73" s="132"/>
+      <c r="F73" s="126"/>
     </row>
     <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="166" t="s">
+      <c r="A74" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="167"/>
+      <c r="B74" s="161"/>
       <c r="C74" s="41"/>
       <c r="D74" s="41"/>
       <c r="E74" s="42">
         <f>(SUM(E21:E72))</f>
         <v>7638187.1179999989</v>
       </c>
-      <c r="F74" s="168"/>
+      <c r="F74" s="162"/>
       <c r="G74" s="40"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -3258,21 +3222,21 @@
       <c r="H76" s="44"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="169" t="s">
+      <c r="A77" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="B77" s="170"/>
-      <c r="C77" s="171"/>
+      <c r="B77" s="164"/>
+      <c r="C77" s="165"/>
       <c r="D77" s="45"/>
       <c r="E77" s="46"/>
       <c r="F77" s="38"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="213"/>
-      <c r="B78" s="214"/>
+      <c r="A78" s="203"/>
+      <c r="B78" s="204"/>
       <c r="C78" s="33"/>
-      <c r="D78" s="172"/>
-      <c r="E78" s="119"/>
+      <c r="D78" s="166"/>
+      <c r="E78" s="113"/>
       <c r="F78" s="38"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3284,19 +3248,19 @@
       <c r="F79" s="38"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="173"/>
-      <c r="B80" s="174"/>
+      <c r="A80" s="167"/>
+      <c r="B80" s="168"/>
       <c r="C80" s="33"/>
       <c r="D80" s="28"/>
       <c r="E80" s="47"/>
       <c r="F80" s="38"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="175" t="s">
+      <c r="A81" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="B81" s="176"/>
-      <c r="C81" s="176"/>
+      <c r="B81" s="170"/>
+      <c r="C81" s="170"/>
       <c r="D81" s="80"/>
       <c r="E81" s="106">
         <f>SUM(D78:D80)</f>
@@ -3313,11 +3277,11 @@
       <c r="F82" s="38"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="164" t="s">
+      <c r="A83" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="B83" s="164"/>
-      <c r="C83" s="164"/>
+      <c r="B83" s="158"/>
+      <c r="C83" s="158"/>
       <c r="D83" s="35"/>
       <c r="E83" s="109">
         <v>0</v>
@@ -3333,10 +3297,10 @@
       <c r="F84" s="38"/>
     </row>
     <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="166" t="s">
+      <c r="A85" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B85" s="167"/>
+      <c r="B85" s="161"/>
       <c r="C85" s="41"/>
       <c r="D85" s="41"/>
       <c r="E85" s="42">
@@ -3354,10 +3318,10 @@
       <c r="F86" s="38"/>
     </row>
     <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="177" t="s">
+      <c r="A87" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="B87" s="178">
+      <c r="B87" s="172">
         <f>E74</f>
         <v>7638187.1179999989</v>
       </c>
@@ -3367,10 +3331,10 @@
       <c r="F87" s="38"/>
     </row>
     <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="177" t="s">
+      <c r="A88" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="B88" s="178">
+      <c r="B88" s="172">
         <f>E74-E72</f>
         <v>7638187.1179999989</v>
       </c>
@@ -3380,10 +3344,10 @@
       <c r="F88" s="38"/>
     </row>
     <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="177" t="s">
+      <c r="A89" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="B89" s="178">
+      <c r="B89" s="172">
         <f>E85-E83</f>
         <v>0</v>
       </c>
@@ -3393,10 +3357,10 @@
       <c r="F89" s="38"/>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="177" t="s">
+      <c r="A90" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="B90" s="178">
+      <c r="B90" s="172">
         <f>E85</f>
         <v>0</v>
       </c>
@@ -3423,9 +3387,9 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="B93" s="179">
+        <v>180</v>
+      </c>
+      <c r="B93" s="173">
         <v>0</v>
       </c>
       <c r="C93" s="38"/>
@@ -3434,10 +3398,10 @@
       <c r="F93" s="38"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="154" t="s">
-        <v>188</v>
-      </c>
-      <c r="B94" s="180">
+      <c r="A94" s="148" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="174">
         <v>5125397.67</v>
       </c>
       <c r="C94" s="38"/>
@@ -3446,10 +3410,10 @@
       <c r="F94" s="38"/>
     </row>
     <row r="95" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="154" t="s">
-        <v>214</v>
-      </c>
-      <c r="B95" s="203">
+      <c r="A95" s="148" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="190">
         <v>-2000574.76</v>
       </c>
       <c r="C95" s="38"/>
@@ -3458,10 +3422,10 @@
       <c r="F95" s="38"/>
     </row>
     <row r="96" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="154" t="s">
-        <v>187</v>
-      </c>
-      <c r="B96" s="133">
+      <c r="A96" s="148" t="s">
+        <v>186</v>
+      </c>
+      <c r="B96" s="127">
         <f>B97-(B94+B95)</f>
         <v>66737.25</v>
       </c>
@@ -3471,10 +3435,10 @@
       <c r="F96" s="38"/>
     </row>
     <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="181" t="s">
-        <v>177</v>
-      </c>
-      <c r="B97" s="182">
+      <c r="A97" s="175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="176">
         <v>3191560.16</v>
       </c>
       <c r="C97" s="38"/>
@@ -3483,16 +3447,16 @@
       <c r="F97" s="38"/>
     </row>
     <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="183"/>
-      <c r="B98" s="184"/>
+      <c r="A98" s="177"/>
+      <c r="B98" s="178"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
     <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="183"/>
-      <c r="B99" s="184"/>
+      <c r="A99" s="177"/>
+      <c r="B99" s="178"/>
       <c r="C99" s="38"/>
       <c r="D99" s="38"/>
       <c r="E99" s="38"/>
@@ -3500,7 +3464,7 @@
     </row>
     <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B100" s="51">
         <v>231400</v>
@@ -3511,10 +3475,10 @@
       <c r="F100" s="38"/>
     </row>
     <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="154" t="s">
-        <v>161</v>
-      </c>
-      <c r="B101" s="180">
+      <c r="A101" s="148" t="s">
+        <v>160</v>
+      </c>
+      <c r="B101" s="174">
         <v>0</v>
       </c>
       <c r="C101" s="38"/>
@@ -3523,20 +3487,20 @@
       <c r="F101" s="38"/>
     </row>
     <row r="102" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="154" t="s">
-        <v>162</v>
-      </c>
-      <c r="B102" s="133"/>
+      <c r="A102" s="148" t="s">
+        <v>161</v>
+      </c>
+      <c r="B102" s="127"/>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
       <c r="F102" s="38"/>
     </row>
     <row r="103" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="181" t="s">
-        <v>177</v>
-      </c>
-      <c r="B103" s="182">
+      <c r="A103" s="175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B103" s="176">
         <f>SUM(B100:B102)</f>
         <v>231400</v>
       </c>
@@ -3546,8 +3510,8 @@
       <c r="F103" s="38"/>
     </row>
     <row r="104" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="183"/>
-      <c r="B104" s="184"/>
+      <c r="A104" s="177"/>
+      <c r="B104" s="178"/>
       <c r="C104" s="38"/>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
@@ -3555,7 +3519,7 @@
     </row>
     <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="111" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B105" s="51">
         <v>58418</v>
@@ -3566,10 +3530,10 @@
       <c r="F105" s="38"/>
     </row>
     <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="154" t="s">
-        <v>161</v>
-      </c>
-      <c r="B106" s="180">
+      <c r="A106" s="148" t="s">
+        <v>160</v>
+      </c>
+      <c r="B106" s="174">
         <v>0</v>
       </c>
       <c r="C106" s="38"/>
@@ -3578,10 +3542,10 @@
       <c r="F106" s="38"/>
     </row>
     <row r="107" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="181" t="s">
-        <v>177</v>
-      </c>
-      <c r="B107" s="182">
+      <c r="A107" s="175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B107" s="176">
         <f>SUM(B105:B106)</f>
         <v>58418</v>
       </c>
@@ -3599,7 +3563,7 @@
     </row>
     <row r="109" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="111" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B109" s="51">
         <v>-62147.730000001146</v>
@@ -3612,7 +3576,7 @@
       <c r="A110" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B110" s="134">
+      <c r="B110" s="128">
         <f>-B88-B89</f>
         <v>-7638187.1179999989</v>
       </c>
@@ -3645,9 +3609,9 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="B113" s="203">
+        <v>211</v>
+      </c>
+      <c r="B113" s="190">
         <v>-160000</v>
       </c>
       <c r="D113" s="38"/>
@@ -3656,24 +3620,24 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B114" s="203">
+        <v>179</v>
+      </c>
+      <c r="B114" s="190">
         <v>-16162</v>
       </c>
       <c r="D114" s="38"/>
-      <c r="E114" s="132"/>
+      <c r="E114" s="126"/>
       <c r="F114" s="48"/>
     </row>
     <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B115" s="208">
+        <v>184</v>
+      </c>
+      <c r="B115" s="195">
         <f>-B95</f>
         <v>2000574.76</v>
       </c>
-      <c r="D115" s="132"/>
+      <c r="D115" s="126"/>
       <c r="E115" s="38"/>
       <c r="F115" s="48"/>
     </row>
@@ -3693,10 +3657,10 @@
       <c r="E117" s="40"/>
     </row>
     <row r="118" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="135" t="s">
-        <v>164</v>
-      </c>
-      <c r="B118" s="136">
+      <c r="A118" s="129" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" s="130">
         <f>B116+B103</f>
         <v>321752.31200000015</v>
       </c>
@@ -3705,16 +3669,16 @@
     </row>
     <row r="119" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="212" t="s">
+      <c r="A120" s="202" t="s">
         <v>25</v>
       </c>
-      <c r="B120" s="212"/>
-      <c r="C120" s="212"/>
+      <c r="B120" s="202"/>
+      <c r="C120" s="202"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="212"/>
-      <c r="B121" s="212"/>
-      <c r="C121" s="212"/>
+      <c r="A121" s="202"/>
+      <c r="B121" s="202"/>
+      <c r="C121" s="202"/>
     </row>
     <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="56"/>
@@ -3792,108 +3756,108 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="66"/>
-      <c r="B1" s="126"/>
+      <c r="B1" s="120"/>
       <c r="C1" s="67"/>
       <c r="D1" s="67"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="227" t="str">
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="245" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="228"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="245"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="245"/>
+      <c r="P1" s="246"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="138">
+        <v>164</v>
+      </c>
+      <c r="B2" s="121"/>
+      <c r="C2" s="132">
         <f>D2-C4-C5</f>
         <v>5827100.4799999995</v>
       </c>
-      <c r="D2" s="209">
+      <c r="D2" s="196">
         <v>7736519.879999999</v>
       </c>
       <c r="E2" s="68"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="237"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="230"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="M2" s="247"/>
+      <c r="N2" s="247"/>
+      <c r="O2" s="247"/>
+      <c r="P2" s="248"/>
       <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="138">
+      <c r="B3" s="121"/>
+      <c r="C3" s="132">
         <v>0</v>
       </c>
       <c r="D3" s="68"/>
       <c r="E3" s="68"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="229"/>
-      <c r="M3" s="229"/>
-      <c r="N3" s="229"/>
-      <c r="O3" s="229"/>
-      <c r="P3" s="230"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="M3" s="247"/>
+      <c r="N3" s="247"/>
+      <c r="O3" s="247"/>
+      <c r="P3" s="248"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="138">
+        <v>170</v>
+      </c>
+      <c r="B4" s="121"/>
+      <c r="C4" s="132">
         <v>182823.01</v>
       </c>
       <c r="D4" s="68"/>
       <c r="E4" s="68"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="230"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="M4" s="247"/>
+      <c r="N4" s="247"/>
+      <c r="O4" s="247"/>
+      <c r="P4" s="248"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="137" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="139">
+      <c r="A5" s="131" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="122"/>
+      <c r="C5" s="133">
         <v>1726596.39</v>
       </c>
       <c r="D5" s="69"/>
@@ -3902,211 +3866,211 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="232"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="M5" s="249"/>
+      <c r="N5" s="249"/>
+      <c r="O5" s="249"/>
+      <c r="P5" s="250"/>
       <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="239" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="240"/>
-      <c r="C6" s="241"/>
-      <c r="D6" s="241"/>
-      <c r="E6" s="241"/>
-      <c r="F6" s="241"/>
-      <c r="G6" s="241"/>
-      <c r="H6" s="241"/>
-      <c r="I6" s="241"/>
-      <c r="J6" s="241"/>
-      <c r="K6" s="241"/>
-      <c r="L6" s="241"/>
-      <c r="M6" s="241"/>
-      <c r="N6" s="241"/>
-      <c r="O6" s="241"/>
-      <c r="P6" s="242"/>
+      <c r="A6" s="218" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="219"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="220"/>
+      <c r="F6" s="220"/>
+      <c r="G6" s="220"/>
+      <c r="H6" s="220"/>
+      <c r="I6" s="220"/>
+      <c r="J6" s="220"/>
+      <c r="K6" s="220"/>
+      <c r="L6" s="220"/>
+      <c r="M6" s="220"/>
+      <c r="N6" s="220"/>
+      <c r="O6" s="220"/>
+      <c r="P6" s="221"/>
       <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="244"/>
-      <c r="J7" s="244"/>
-      <c r="K7" s="244"/>
-      <c r="L7" s="244"/>
-      <c r="M7" s="244"/>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="245"/>
+      <c r="A7" s="222"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="223"/>
+      <c r="O7" s="223"/>
+      <c r="P7" s="224"/>
       <c r="Q7" s="62"/>
     </row>
     <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="243"/>
-      <c r="B8" s="244"/>
-      <c r="C8" s="244"/>
-      <c r="D8" s="244"/>
-      <c r="E8" s="244"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="244"/>
-      <c r="J8" s="244"/>
-      <c r="K8" s="244"/>
-      <c r="L8" s="244"/>
-      <c r="M8" s="244"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="245"/>
+      <c r="A8" s="222"/>
+      <c r="B8" s="223"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="224"/>
       <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="243"/>
-      <c r="B9" s="244"/>
-      <c r="C9" s="244"/>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
-      <c r="M9" s="244"/>
-      <c r="N9" s="244"/>
-      <c r="O9" s="244"/>
-      <c r="P9" s="245"/>
+      <c r="A9" s="222"/>
+      <c r="B9" s="223"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="223"/>
+      <c r="O9" s="223"/>
+      <c r="P9" s="224"/>
       <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="246"/>
-      <c r="B10" s="247"/>
-      <c r="C10" s="247"/>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="247"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="247"/>
-      <c r="M10" s="247"/>
-      <c r="N10" s="247"/>
-      <c r="O10" s="247"/>
-      <c r="P10" s="248"/>
+      <c r="A10" s="225"/>
+      <c r="B10" s="226"/>
+      <c r="C10" s="226"/>
+      <c r="D10" s="226"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="226"/>
+      <c r="H10" s="226"/>
+      <c r="I10" s="226"/>
+      <c r="J10" s="226"/>
+      <c r="K10" s="226"/>
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="226"/>
+      <c r="O10" s="226"/>
+      <c r="P10" s="227"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="257" t="s">
+      <c r="A11" s="238" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="258"/>
-      <c r="C11" s="258"/>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
-      <c r="M11" s="258"/>
-      <c r="N11" s="258"/>
-      <c r="O11" s="258"/>
-      <c r="P11" s="259"/>
+      <c r="B11" s="239"/>
+      <c r="C11" s="239"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+      <c r="N11" s="239"/>
+      <c r="O11" s="239"/>
+      <c r="P11" s="240"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="249" t="s">
+      <c r="A12" s="228" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="262" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="251" t="s">
+      <c r="B12" s="243" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="230" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="251" t="s">
+      <c r="D12" s="230" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="251" t="s">
+      <c r="E12" s="230" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="233" t="s">
+      <c r="F12" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="253" t="s">
+      <c r="G12" s="234" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="255" t="s">
+      <c r="H12" s="236" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="233" t="s">
+      <c r="I12" s="232" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="233" t="s">
+      <c r="J12" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="233" t="s">
+      <c r="K12" s="232" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="262" t="s">
-        <v>170</v>
-      </c>
-      <c r="M12" s="233" t="s">
-        <v>167</v>
-      </c>
-      <c r="N12" s="260" t="s">
-        <v>182</v>
+      <c r="L12" s="243" t="s">
+        <v>169</v>
+      </c>
+      <c r="M12" s="232" t="s">
+        <v>166</v>
+      </c>
+      <c r="N12" s="241" t="s">
+        <v>181</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="235" t="s">
+      <c r="P12" s="251" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="250"/>
-      <c r="B13" s="263"/>
-      <c r="C13" s="252"/>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="254"/>
-      <c r="H13" s="256"/>
-      <c r="I13" s="234"/>
-      <c r="J13" s="234"/>
-      <c r="K13" s="234"/>
-      <c r="L13" s="263"/>
-      <c r="M13" s="234"/>
-      <c r="N13" s="261"/>
+      <c r="A13" s="229"/>
+      <c r="B13" s="244"/>
+      <c r="C13" s="231"/>
+      <c r="D13" s="231"/>
+      <c r="E13" s="231"/>
+      <c r="F13" s="233"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="244"/>
+      <c r="M13" s="233"/>
+      <c r="N13" s="242"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P13" s="236"/>
+      <c r="P13" s="252"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="83">
         <v>1</v>
       </c>
-      <c r="B14" s="129" t="s">
-        <v>71</v>
+      <c r="B14" s="123" t="s">
+        <v>70</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14" s="72"/>
       <c r="E14" s="74">
@@ -4160,14 +4124,14 @@
       <c r="A15" s="83">
         <v>2</v>
       </c>
-      <c r="B15" s="129" t="s">
-        <v>74</v>
+      <c r="B15" s="123" t="s">
+        <v>73</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" s="74">
         <v>3.4</v>
@@ -4218,14 +4182,14 @@
       <c r="A16" s="83">
         <v>3</v>
       </c>
-      <c r="B16" s="129" t="s">
-        <v>75</v>
+      <c r="B16" s="123" t="s">
+        <v>74</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E16" s="74">
         <v>2.54</v>
@@ -4274,21 +4238,21 @@
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="83">
         <v>4</v>
       </c>
-      <c r="B17" s="129" t="s">
-        <v>76</v>
+      <c r="B17" s="123" t="s">
+        <v>75</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="74">
         <v>5.19</v>
@@ -4340,21 +4304,21 @@
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="83">
         <v>5</v>
       </c>
-      <c r="B18" s="129" t="s">
-        <v>72</v>
+      <c r="B18" s="123" t="s">
+        <v>71</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E18" s="74">
         <v>3.4</v>
@@ -4407,14 +4371,14 @@
       <c r="A19" s="83">
         <v>6</v>
       </c>
-      <c r="B19" s="129" t="s">
-        <v>77</v>
+      <c r="B19" s="123" t="s">
+        <v>76</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
@@ -4468,11 +4432,11 @@
       <c r="A20" s="83">
         <v>7</v>
       </c>
-      <c r="B20" s="129" t="s">
-        <v>78</v>
+      <c r="B20" s="123" t="s">
+        <v>77</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D20" s="72"/>
       <c r="E20" s="74">
@@ -4527,11 +4491,11 @@
       <c r="A21" s="83">
         <v>8</v>
       </c>
-      <c r="B21" s="129" t="s">
-        <v>79</v>
+      <c r="B21" s="123" t="s">
+        <v>78</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D21" s="77"/>
       <c r="E21" s="74">
@@ -4586,14 +4550,14 @@
       <c r="A22" s="83">
         <v>9</v>
       </c>
-      <c r="B22" s="129" t="s">
-        <v>73</v>
+      <c r="B22" s="123" t="s">
+        <v>72</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="74">
         <v>2.54</v>
@@ -4647,11 +4611,11 @@
       <c r="A23" s="83">
         <v>10</v>
       </c>
-      <c r="B23" s="129" t="s">
-        <v>80</v>
+      <c r="B23" s="123" t="s">
+        <v>79</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D23" s="77"/>
       <c r="E23" s="74">
@@ -4706,14 +4670,14 @@
       <c r="A24" s="83">
         <v>11</v>
       </c>
-      <c r="B24" s="129" t="s">
-        <v>81</v>
+      <c r="B24" s="123" t="s">
+        <v>80</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E24" s="74">
         <v>3.4</v>
@@ -4767,14 +4731,14 @@
       <c r="A25" s="83">
         <v>12</v>
       </c>
-      <c r="B25" s="129" t="s">
-        <v>82</v>
+      <c r="B25" s="123" t="s">
+        <v>81</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" s="74">
         <v>2.54</v>
@@ -4828,11 +4792,11 @@
       <c r="A26" s="83">
         <v>13</v>
       </c>
-      <c r="B26" s="129" t="s">
-        <v>83</v>
+      <c r="B26" s="123" t="s">
+        <v>82</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D26" s="77"/>
       <c r="E26" s="74">
@@ -4884,56 +4848,56 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="140">
+      <c r="A27" s="134">
         <v>14</v>
       </c>
-      <c r="B27" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="142" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="143"/>
-      <c r="E27" s="144">
+      <c r="B27" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="136" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138">
         <v>3.4</v>
       </c>
-      <c r="F27" s="145">
+      <c r="F27" s="139">
         <v>235999.14</v>
       </c>
-      <c r="G27" s="145">
+      <c r="G27" s="139">
         <f>314895.52-G51</f>
         <v>245171.14</v>
       </c>
-      <c r="H27" s="146">
+      <c r="H27" s="140">
         <f t="shared" si="1"/>
         <v>-9172</v>
       </c>
-      <c r="I27" s="146">
+      <c r="I27" s="140">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="147">
+      <c r="J27" s="141">
         <f t="shared" si="5"/>
         <v>198121.41631999999</v>
       </c>
-      <c r="K27" s="147">
+      <c r="K27" s="141">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="147">
+      <c r="L27" s="141">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="147">
+      <c r="M27" s="141">
         <f t="shared" si="7"/>
         <v>58704.277259999995</v>
       </c>
-      <c r="N27" s="147"/>
-      <c r="O27" s="148">
+      <c r="N27" s="141"/>
+      <c r="O27" s="142">
         <f t="shared" si="8"/>
         <v>253870.14</v>
       </c>
-      <c r="P27" s="149">
+      <c r="P27" s="143">
         <f t="shared" si="3"/>
         <v>261486.14</v>
       </c>
@@ -4946,14 +4910,14 @@
       <c r="A28" s="83">
         <v>15</v>
       </c>
-      <c r="B28" s="129" t="s">
-        <v>85</v>
+      <c r="B28" s="123" t="s">
+        <v>84</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="74">
         <v>2.54</v>
@@ -5007,11 +4971,11 @@
       <c r="A29" s="83">
         <v>16</v>
       </c>
-      <c r="B29" s="129" t="s">
-        <v>86</v>
+      <c r="B29" s="123" t="s">
+        <v>85</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" s="72"/>
       <c r="E29" s="74">
@@ -5066,14 +5030,14 @@
       <c r="A30" s="83">
         <v>17</v>
       </c>
-      <c r="B30" s="129" t="s">
-        <v>87</v>
+      <c r="B30" s="123" t="s">
+        <v>86</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D30" s="77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="74">
         <v>3.4</v>
@@ -5124,14 +5088,14 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="83">
+      <c r="A31" s="262">
         <v>18</v>
       </c>
-      <c r="B31" s="129" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="72" t="s">
-        <v>132</v>
+      <c r="B31" s="263" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="264" t="s">
+        <v>131</v>
       </c>
       <c r="D31" s="73"/>
       <c r="E31" s="74">
@@ -5183,11 +5147,11 @@
       <c r="A32" s="83">
         <v>19</v>
       </c>
-      <c r="B32" s="129" t="s">
-        <v>89</v>
+      <c r="B32" s="123" t="s">
+        <v>88</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" s="77"/>
       <c r="E32" s="74">
@@ -5238,53 +5202,53 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="140">
+      <c r="A33" s="134">
         <v>20</v>
       </c>
-      <c r="B33" s="141" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="142" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="186"/>
-      <c r="E33" s="187">
+      <c r="B33" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="136" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="179"/>
+      <c r="E33" s="180">
         <v>3.4</v>
       </c>
-      <c r="F33" s="188">
+      <c r="F33" s="181">
         <v>237260.2</v>
       </c>
-      <c r="G33" s="188">
+      <c r="G33" s="181">
         <f>249002-G47</f>
         <v>243251.66</v>
       </c>
-      <c r="H33" s="189">
+      <c r="H33" s="182">
         <f t="shared" si="1"/>
         <v>-5991.4599999999919</v>
       </c>
-      <c r="I33" s="189"/>
-      <c r="J33" s="190">
+      <c r="I33" s="182"/>
+      <c r="J33" s="183">
         <f t="shared" si="5"/>
         <v>198121.41631999999</v>
       </c>
-      <c r="K33" s="190">
+      <c r="K33" s="183">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="190">
+      <c r="L33" s="183">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="190">
+      <c r="M33" s="183">
         <f t="shared" si="7"/>
         <v>58704.277259999995</v>
       </c>
-      <c r="N33" s="190"/>
-      <c r="O33" s="191">
+      <c r="N33" s="183"/>
+      <c r="O33" s="184">
         <f t="shared" si="8"/>
         <v>257050.2</v>
       </c>
-      <c r="P33" s="192">
+      <c r="P33" s="185">
         <f t="shared" si="3"/>
         <v>264762.2</v>
       </c>
@@ -5297,14 +5261,14 @@
       <c r="A34" s="83">
         <v>21</v>
       </c>
-      <c r="B34" s="129" t="s">
-        <v>91</v>
+      <c r="B34" s="123" t="s">
+        <v>90</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D34" s="77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="74">
         <v>2.54</v>
@@ -5359,14 +5323,14 @@
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="129" t="s">
-        <v>92</v>
+      <c r="B35" s="123" t="s">
+        <v>91</v>
       </c>
       <c r="C35" s="78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D35" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E35" s="74">
         <v>4.9400000000000004</v>
@@ -5421,14 +5385,14 @@
         <f t="shared" ref="A36:A59" si="15">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="129" t="s">
-        <v>93</v>
+      <c r="B36" s="123" t="s">
+        <v>92</v>
       </c>
       <c r="C36" s="78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D36" s="77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E36" s="74">
         <v>3.28</v>
@@ -5483,11 +5447,11 @@
         <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="B37" s="129" t="s">
-        <v>94</v>
+      <c r="B37" s="123" t="s">
+        <v>93</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D37" s="77"/>
       <c r="E37" s="74">
@@ -5536,17 +5500,20 @@
         <f t="shared" si="12"/>
         <v>0.24000000000000007</v>
       </c>
+      <c r="R37" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="83">
         <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="B38" s="129" t="s">
-        <v>95</v>
+      <c r="B38" s="123" t="s">
+        <v>94</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D38" s="77"/>
       <c r="E38" s="74">
@@ -5597,7 +5564,7 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -5605,11 +5572,11 @@
         <f t="shared" si="15"/>
         <v>26</v>
       </c>
-      <c r="B39" s="129" t="s">
-        <v>97</v>
+      <c r="B39" s="123" t="s">
+        <v>96</v>
       </c>
       <c r="C39" s="78" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D39" s="77"/>
       <c r="E39" s="74">
@@ -5664,11 +5631,11 @@
         <f t="shared" si="15"/>
         <v>27</v>
       </c>
-      <c r="B40" s="129" t="s">
-        <v>96</v>
+      <c r="B40" s="123" t="s">
+        <v>95</v>
       </c>
       <c r="C40" s="78" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D40" s="77"/>
       <c r="E40" s="74">
@@ -5724,14 +5691,14 @@
         <f t="shared" si="15"/>
         <v>28</v>
       </c>
-      <c r="B41" s="129" t="s">
-        <v>98</v>
+      <c r="B41" s="123" t="s">
+        <v>97</v>
       </c>
       <c r="C41" s="78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="74">
         <v>0.28999999999999998</v>
@@ -5783,14 +5750,14 @@
         <f t="shared" si="15"/>
         <v>29</v>
       </c>
-      <c r="B42" s="129" t="s">
-        <v>99</v>
+      <c r="B42" s="123" t="s">
+        <v>98</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D42" s="77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E42" s="74">
         <v>0.08</v>
@@ -5845,11 +5812,11 @@
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="B43" s="129" t="s">
-        <v>100</v>
+      <c r="B43" s="123" t="s">
+        <v>99</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D43" s="77"/>
       <c r="E43" s="74">
@@ -5905,14 +5872,14 @@
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
-      <c r="B44" s="129" t="s">
-        <v>101</v>
+      <c r="B44" s="123" t="s">
+        <v>100</v>
       </c>
       <c r="C44" s="78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D44" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E44" s="74">
         <v>0.08</v>
@@ -5962,7 +5929,7 @@
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -5970,11 +5937,11 @@
         <f t="shared" si="15"/>
         <v>32</v>
       </c>
-      <c r="B45" s="129" t="s">
-        <v>102</v>
+      <c r="B45" s="123" t="s">
+        <v>101</v>
       </c>
       <c r="C45" s="78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D45" s="77"/>
       <c r="E45" s="74">
@@ -6030,11 +5997,11 @@
         <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="B46" s="129" t="s">
-        <v>103</v>
+      <c r="B46" s="123" t="s">
+        <v>102</v>
       </c>
       <c r="C46" s="78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D46" s="77"/>
       <c r="E46" s="74">
@@ -6084,11 +6051,11 @@
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="B47" s="129" t="s">
-        <v>104</v>
+      <c r="B47" s="123" t="s">
+        <v>103</v>
       </c>
       <c r="C47" s="78" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D47" s="77"/>
       <c r="E47" s="74">
@@ -6140,18 +6107,18 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="120">
+      <c r="A48" s="114">
         <f t="shared" si="15"/>
         <v>35</v>
       </c>
-      <c r="B48" s="129" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="121" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="122"/>
-      <c r="E48" s="123">
+      <c r="B48" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="115" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="116"/>
+      <c r="E48" s="117">
         <v>0.09</v>
       </c>
       <c r="F48" s="63">
@@ -6161,11 +6128,11 @@
         <f>12776.35</f>
         <v>12776.35</v>
       </c>
-      <c r="H48" s="124">
+      <c r="H48" s="118">
         <f t="shared" si="1"/>
         <v>-372</v>
       </c>
-      <c r="I48" s="124">
+      <c r="I48" s="118">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6173,7 +6140,7 @@
         <f t="shared" si="5"/>
         <v>5244.3904319999992</v>
       </c>
-      <c r="K48" s="125">
+      <c r="K48" s="119">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -6185,7 +6152,7 @@
         <f t="shared" si="7"/>
         <v>1553.936751</v>
       </c>
-      <c r="N48" s="125"/>
+      <c r="N48" s="119"/>
       <c r="O48" s="76">
         <f t="shared" si="8"/>
         <v>6591.35</v>
@@ -6204,11 +6171,11 @@
         <f t="shared" si="15"/>
         <v>36</v>
       </c>
-      <c r="B49" s="129" t="s">
-        <v>106</v>
+      <c r="B49" s="123" t="s">
+        <v>105</v>
       </c>
       <c r="C49" s="78" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D49" s="77"/>
       <c r="E49" s="74">
@@ -6264,11 +6231,11 @@
         <f t="shared" si="15"/>
         <v>37</v>
       </c>
-      <c r="B50" s="129" t="s">
-        <v>107</v>
+      <c r="B50" s="123" t="s">
+        <v>106</v>
       </c>
       <c r="C50" s="78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D50" s="77"/>
       <c r="E50" s="74">
@@ -6321,11 +6288,11 @@
         <f t="shared" si="15"/>
         <v>38</v>
       </c>
-      <c r="B51" s="129" t="s">
-        <v>108</v>
+      <c r="B51" s="123" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D51" s="77"/>
       <c r="E51" s="74">
@@ -6381,11 +6348,11 @@
         <f t="shared" si="15"/>
         <v>39</v>
       </c>
-      <c r="B52" s="129" t="s">
-        <v>109</v>
+      <c r="B52" s="123" t="s">
+        <v>108</v>
       </c>
       <c r="C52" s="78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D52" s="77"/>
       <c r="E52" s="74">
@@ -6436,7 +6403,7 @@
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -6444,14 +6411,14 @@
         <f t="shared" si="15"/>
         <v>40</v>
       </c>
-      <c r="B53" s="129" t="s">
-        <v>110</v>
+      <c r="B53" s="123" t="s">
+        <v>109</v>
       </c>
       <c r="C53" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E53" s="74">
         <v>0.77</v>
@@ -6506,14 +6473,14 @@
         <f t="shared" si="15"/>
         <v>41</v>
       </c>
-      <c r="B54" s="129" t="s">
-        <v>111</v>
+      <c r="B54" s="123" t="s">
+        <v>110</v>
       </c>
       <c r="C54" s="78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D54" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E54" s="74">
         <v>0.81</v>
@@ -6567,14 +6534,14 @@
         <f t="shared" si="15"/>
         <v>42</v>
       </c>
-      <c r="B55" s="129" t="s">
-        <v>112</v>
+      <c r="B55" s="123" t="s">
+        <v>111</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E55" s="74">
         <v>0.77</v>
@@ -6621,7 +6588,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
@@ -6629,11 +6596,11 @@
         <f t="shared" si="15"/>
         <v>43</v>
       </c>
-      <c r="B56" s="129" t="s">
-        <v>113</v>
+      <c r="B56" s="123" t="s">
+        <v>112</v>
       </c>
       <c r="C56" s="78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D56" s="77"/>
       <c r="E56" s="74">
@@ -6686,11 +6653,11 @@
         <f t="shared" si="15"/>
         <v>44</v>
       </c>
-      <c r="B57" s="129" t="s">
-        <v>114</v>
+      <c r="B57" s="123" t="s">
+        <v>113</v>
       </c>
       <c r="C57" s="78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D57" s="77"/>
       <c r="E57" s="74">
@@ -6743,14 +6710,14 @@
         <f t="shared" si="15"/>
         <v>45</v>
       </c>
-      <c r="B58" s="129" t="s">
-        <v>115</v>
+      <c r="B58" s="123" t="s">
+        <v>114</v>
       </c>
       <c r="C58" s="78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D58" s="77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E58" s="74">
         <v>0.77</v>
@@ -6805,11 +6772,11 @@
         <f t="shared" si="15"/>
         <v>46</v>
       </c>
-      <c r="B59" s="129" t="s">
-        <v>116</v>
+      <c r="B59" s="123" t="s">
+        <v>115</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D59" s="77"/>
       <c r="E59" s="74">
@@ -6860,12 +6827,12 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="83"/>
-      <c r="B60" s="129"/>
+      <c r="B60" s="123"/>
       <c r="C60" s="72"/>
       <c r="D60" s="77"/>
       <c r="E60" s="74"/>
@@ -6884,7 +6851,7 @@
     </row>
     <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="84"/>
-      <c r="B61" s="130"/>
+      <c r="B61" s="124"/>
       <c r="C61" s="85"/>
       <c r="D61" s="85"/>
       <c r="E61" s="86">
@@ -6939,103 +6906,99 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="238" t="s">
+      <c r="C64" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="238"/>
-      <c r="E64" s="238"/>
-      <c r="F64" s="238"/>
-      <c r="G64" s="238"/>
-      <c r="H64" s="238"/>
-      <c r="I64" s="238"/>
-      <c r="J64" s="238"/>
-      <c r="K64" s="238"/>
-      <c r="L64" s="238"/>
-      <c r="M64" s="238"/>
-      <c r="N64" s="238"/>
-      <c r="O64" s="238"/>
+      <c r="D64" s="217"/>
+      <c r="E64" s="217"/>
+      <c r="F64" s="217"/>
+      <c r="G64" s="217"/>
+      <c r="H64" s="217"/>
+      <c r="I64" s="217"/>
+      <c r="J64" s="217"/>
+      <c r="K64" s="217"/>
+      <c r="L64" s="217"/>
+      <c r="M64" s="217"/>
+      <c r="N64" s="217"/>
+      <c r="O64" s="217"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="238"/>
-      <c r="D65" s="238"/>
-      <c r="E65" s="238"/>
-      <c r="F65" s="238"/>
-      <c r="G65" s="238"/>
-      <c r="H65" s="238"/>
-      <c r="I65" s="238"/>
-      <c r="J65" s="238"/>
-      <c r="K65" s="238"/>
-      <c r="L65" s="238"/>
-      <c r="M65" s="238"/>
-      <c r="N65" s="238"/>
-      <c r="O65" s="238"/>
+      <c r="C65" s="217"/>
+      <c r="D65" s="217"/>
+      <c r="E65" s="217"/>
+      <c r="F65" s="217"/>
+      <c r="G65" s="217"/>
+      <c r="H65" s="217"/>
+      <c r="I65" s="217"/>
+      <c r="J65" s="217"/>
+      <c r="K65" s="217"/>
+      <c r="L65" s="217"/>
+      <c r="M65" s="217"/>
+      <c r="N65" s="217"/>
+      <c r="O65" s="217"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="238"/>
-      <c r="D66" s="238"/>
-      <c r="E66" s="238"/>
-      <c r="F66" s="238"/>
-      <c r="G66" s="238"/>
-      <c r="H66" s="238"/>
-      <c r="I66" s="238"/>
-      <c r="J66" s="238"/>
-      <c r="K66" s="238"/>
-      <c r="L66" s="238"/>
-      <c r="M66" s="238"/>
-      <c r="N66" s="238"/>
-      <c r="O66" s="238"/>
+      <c r="C66" s="217"/>
+      <c r="D66" s="217"/>
+      <c r="E66" s="217"/>
+      <c r="F66" s="217"/>
+      <c r="G66" s="217"/>
+      <c r="H66" s="217"/>
+      <c r="I66" s="217"/>
+      <c r="J66" s="217"/>
+      <c r="K66" s="217"/>
+      <c r="L66" s="217"/>
+      <c r="M66" s="217"/>
+      <c r="N66" s="217"/>
+      <c r="O66" s="217"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="238"/>
-      <c r="D67" s="238"/>
-      <c r="E67" s="238"/>
-      <c r="F67" s="238"/>
-      <c r="G67" s="238"/>
-      <c r="H67" s="238"/>
-      <c r="I67" s="238"/>
-      <c r="J67" s="238"/>
-      <c r="K67" s="238"/>
-      <c r="L67" s="238"/>
-      <c r="M67" s="238"/>
-      <c r="N67" s="238"/>
-      <c r="O67" s="238"/>
+      <c r="C67" s="217"/>
+      <c r="D67" s="217"/>
+      <c r="E67" s="217"/>
+      <c r="F67" s="217"/>
+      <c r="G67" s="217"/>
+      <c r="H67" s="217"/>
+      <c r="I67" s="217"/>
+      <c r="J67" s="217"/>
+      <c r="K67" s="217"/>
+      <c r="L67" s="217"/>
+      <c r="M67" s="217"/>
+      <c r="N67" s="217"/>
+      <c r="O67" s="217"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="238"/>
-      <c r="D68" s="238"/>
-      <c r="E68" s="238"/>
-      <c r="F68" s="238"/>
-      <c r="G68" s="238"/>
-      <c r="H68" s="238"/>
-      <c r="I68" s="238"/>
-      <c r="J68" s="238"/>
-      <c r="K68" s="238"/>
-      <c r="L68" s="238"/>
-      <c r="M68" s="238"/>
-      <c r="N68" s="238"/>
-      <c r="O68" s="238"/>
+      <c r="C68" s="217"/>
+      <c r="D68" s="217"/>
+      <c r="E68" s="217"/>
+      <c r="F68" s="217"/>
+      <c r="G68" s="217"/>
+      <c r="H68" s="217"/>
+      <c r="I68" s="217"/>
+      <c r="J68" s="217"/>
+      <c r="K68" s="217"/>
+      <c r="L68" s="217"/>
+      <c r="M68" s="217"/>
+      <c r="N68" s="217"/>
+      <c r="O68" s="217"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="238"/>
-      <c r="D69" s="238"/>
-      <c r="E69" s="238"/>
-      <c r="F69" s="238"/>
-      <c r="G69" s="238"/>
-      <c r="H69" s="238"/>
-      <c r="I69" s="238"/>
-      <c r="J69" s="238"/>
-      <c r="K69" s="238"/>
-      <c r="L69" s="238"/>
-      <c r="M69" s="238"/>
-      <c r="N69" s="238"/>
-      <c r="O69" s="238"/>
+      <c r="C69" s="217"/>
+      <c r="D69" s="217"/>
+      <c r="E69" s="217"/>
+      <c r="F69" s="217"/>
+      <c r="G69" s="217"/>
+      <c r="H69" s="217"/>
+      <c r="I69" s="217"/>
+      <c r="J69" s="217"/>
+      <c r="K69" s="217"/>
+      <c r="L69" s="217"/>
+      <c r="M69" s="217"/>
+      <c r="N69" s="217"/>
+      <c r="O69" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -7052,6 +7015,10 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7061,252 +7028,75 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:L23"/>
+  <dimension ref="C4:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="115" t="s">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="260" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="116">
-        <v>1</v>
-      </c>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-    </row>
-    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="117" t="s">
+      <c r="D4" s="261"/>
+      <c r="E4" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="118"/>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="112"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="260" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="261" t="s">
+        <v>55</v>
+      </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="114"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="202"/>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="117" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="112"/>
+    </row>
+    <row r="6" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>190</v>
-      </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="201"/>
-      <c r="L6" s="202"/>
-    </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="114"/>
-      <c r="K7" s="201"/>
-      <c r="L7" s="202"/>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="264" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
-      <c r="H8" s="265"/>
-      <c r="I8" s="265"/>
-      <c r="J8" s="266"/>
-      <c r="K8" s="201"/>
-      <c r="L8" s="202"/>
-    </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="267"/>
-      <c r="D9" s="268"/>
-      <c r="E9" s="268"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
-      <c r="H9" s="268"/>
-      <c r="I9" s="268"/>
-      <c r="J9" s="269"/>
-      <c r="K9" s="185"/>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="196" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="197"/>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" t="s">
-        <v>191</v>
-      </c>
-      <c r="J12" s="114"/>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="196" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="197" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="114"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="202"/>
-    </row>
-    <row r="14" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="114"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="264" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="265"/>
-      <c r="E15" s="265"/>
-      <c r="F15" s="265"/>
-      <c r="G15" s="265"/>
-      <c r="H15" s="265"/>
-      <c r="I15" s="265"/>
-      <c r="J15" s="266"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-    </row>
-    <row r="16" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="267"/>
-      <c r="D16" s="268"/>
-      <c r="E16" s="268"/>
-      <c r="F16" s="268"/>
-      <c r="G16" s="268"/>
-      <c r="H16" s="268"/>
-      <c r="I16" s="268"/>
-      <c r="J16" s="269"/>
-      <c r="K16" s="202"/>
-      <c r="L16" s="202"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="K18" s="202"/>
-      <c r="L18" s="202"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C19" s="198" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="199"/>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="114"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="202"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C20" s="198" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="199" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" t="s">
-        <v>193</v>
-      </c>
-      <c r="J20" s="114"/>
-      <c r="K20" s="202"/>
-      <c r="L20" s="202"/>
-    </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="114"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C22" s="264" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="265"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="265"/>
-      <c r="G22" s="265"/>
-      <c r="H22" s="265"/>
-      <c r="I22" s="265"/>
-      <c r="J22" s="266"/>
-      <c r="K22" s="202"/>
-      <c r="L22" s="202"/>
-    </row>
-    <row r="23" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="267"/>
-      <c r="D23" s="268"/>
-      <c r="E23" s="268"/>
-      <c r="F23" s="268"/>
-      <c r="G23" s="268"/>
-      <c r="H23" s="268"/>
-      <c r="I23" s="268"/>
-      <c r="J23" s="269"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="202"/>
+      <c r="J6" s="112"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="254" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="255"/>
+      <c r="I7" s="255"/>
+      <c r="J7" s="256"/>
+    </row>
+    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="257"/>
+      <c r="D8" s="258"/>
+      <c r="E8" s="258"/>
+      <c r="F8" s="258"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="258"/>
+      <c r="I8" s="258"/>
+      <c r="J8" s="259"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C8:J9"/>
-    <mergeCell ref="C15:J16"/>
-    <mergeCell ref="C22:J23"/>
+  <mergeCells count="1">
+    <mergeCell ref="C7:J8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15804FC2-C2F8-4EB2-A67B-51C92B5B11D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFC4527-336A-4A0D-B594-102021A972CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="211">
   <si>
     <t>TOTAL</t>
   </si>
@@ -558,9 +563,6 @@
     <t>Myryam Martinez Del Valle</t>
   </si>
   <si>
-    <t>Abono de 2 meses</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gastos bancarios </t>
   </si>
   <si>
@@ -574,9 +576,6 @@
   </si>
   <si>
     <t>Brisa Agüero</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados</t>
   </si>
   <si>
     <t>FCI Super ahorro plus</t>
@@ -604,87 +603,18 @@
     <t>Inicio del mes</t>
   </si>
   <si>
-    <t>Transf 17/8</t>
-  </si>
-  <si>
-    <t>Palazzo Andres - Reparacion de camaras (fuente, cajas, conectores)</t>
-  </si>
-  <si>
-    <t>Transf 07/08</t>
-  </si>
-  <si>
-    <t>Transf 10/08</t>
-  </si>
-  <si>
-    <t>Transf 06/08</t>
-  </si>
-  <si>
-    <t>Gabriel Chiantori - Se realizó el retiro de la bomba sumergible quemada, instalación de una nueva bomba con rejilla protectora anti-sedimentos y reacondicionamiento integral de la instalación eléctrica, incluyendo nuevo cableado y conexión hasta la caja del techo del subsuelo.</t>
-  </si>
-  <si>
-    <t>Galvan Zaffalon - Visita de guardia por saltado de termica baja</t>
-  </si>
-  <si>
-    <t>Galvan Zaffalon - Instalacion de pedrollo de su propiedad</t>
-  </si>
-  <si>
-    <t>Debito 10/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Abono ascensor - ADS - Se abona mes de mayo</t>
-  </si>
-  <si>
-    <t>Duplicacion de pago</t>
-  </si>
-  <si>
     <t>Abono ascensor - ADS - Se abona el mes de junio</t>
   </si>
   <si>
-    <t>Cuota 17/24</t>
-  </si>
-  <si>
-    <t>Debito 18/08</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Mitad de MAYO adeudada</t>
-  </si>
-  <si>
-    <t>Transf 26/08</t>
-  </si>
-  <si>
-    <t>Transf 28/08</t>
-  </si>
-  <si>
-    <t>Rescate 12/08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Haberes </t>
   </si>
   <si>
-    <t>Transf 31/08</t>
-  </si>
-  <si>
-    <t>Cambio de semaforo - Materiales y mano de obra</t>
-  </si>
-  <si>
-    <t>Deposito ya identificado 29/6</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
     <t>PERÍODO: SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se debe agosto y SEPTIEMBRE ($420.000 c/u)</t>
-  </si>
-  <si>
     <t>Transf 19/09</t>
   </si>
   <si>
@@ -694,9 +624,6 @@
     <t>Casa Ruan - Compra de 6 dicroicas</t>
   </si>
   <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gustavo Padron -  Sr. Contador - Mes 8 </t>
   </si>
   <si>
@@ -719,6 +646,36 @@
   </si>
   <si>
     <t>6C $251.908 el 16/09 y $923.325 el 29/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se abona JULIO Y AGOSTO - Se adeuda Septiembre ($420.000)</t>
+  </si>
+  <si>
+    <t>Transf 05/09  - 10/09</t>
+  </si>
+  <si>
+    <t>Debito 14/09</t>
+  </si>
+  <si>
+    <t>Cuota 18/24</t>
+  </si>
+  <si>
+    <t>Debito 16/09</t>
+  </si>
+  <si>
+    <t>Forlini Nora - Desagote de camara</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>Transferencia 09/09 Vazquez Miguel Angel</t>
+  </si>
+  <si>
+    <t>Transferencia 15/09 Molina Soledad</t>
+  </si>
+  <si>
+    <t>Deposito 23/09</t>
   </si>
 </sst>
 </file>
@@ -735,7 +692,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,6 +856,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1494,7 +1458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1799,20 +1763,7 @@
     <xf numFmtId="8" fontId="12" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1827,191 +1778,208 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2095,9 +2063,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2135,9 +2103,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2170,9 +2138,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2205,9 +2190,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2381,32 +2383,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M118"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="207" t="s">
+      <c r="B1" s="202" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="208"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="203"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>45</v>
@@ -2415,16 +2417,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="206" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="210"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2435,12 +2437,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2448,9 +2450,9 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2459,62 +2461,62 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="211" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="211"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="211"/>
-      <c r="C9" s="211"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="211"/>
-      <c r="C10" s="211"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="208" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="208"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="212" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="212"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="212"/>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="209"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2523,7 +2525,7 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>60</v>
       </c>
@@ -2532,43 +2534,43 @@
       <c r="D21" s="81"/>
       <c r="E21" s="96"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="213" t="s">
-        <v>208</v>
-      </c>
-      <c r="B22" s="214"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="210" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="211"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="194">
-        <v>1460357.72</v>
+      <c r="D22" s="189">
+        <v>1448764.03</v>
       </c>
       <c r="E22" s="97"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="200" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="201"/>
+      <c r="B23" s="205"/>
       <c r="C23" s="144"/>
-      <c r="D23" s="194">
-        <v>-317627.71999999997</v>
+      <c r="D23" s="189">
+        <v>-315106.03000000003</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="38"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="200" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="201"/>
+      <c r="B24" s="205"/>
       <c r="C24" s="144"/>
       <c r="D24" s="187"/>
       <c r="E24" s="21"/>
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="145" t="s">
         <v>8</v>
       </c>
@@ -2577,11 +2579,11 @@
       <c r="D25" s="22"/>
       <c r="E25" s="98">
         <f>SUM(D22:D24)</f>
-        <v>1142730</v>
+        <v>1133658</v>
       </c>
       <c r="F25" s="38"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="145" t="s">
         <v>50</v>
       </c>
@@ -2591,7 +2593,7 @@
       <c r="E26" s="99"/>
       <c r="F26" s="38"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="144"/>
       <c r="B27" s="144"/>
       <c r="C27" s="144"/>
@@ -2599,7 +2601,7 @@
       <c r="E27" s="110"/>
       <c r="F27" s="38"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="144"/>
       <c r="B28" s="144"/>
       <c r="C28" s="144"/>
@@ -2607,7 +2609,7 @@
       <c r="E28" s="110"/>
       <c r="F28" s="38"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="144"/>
       <c r="B29" s="144"/>
       <c r="C29" s="144"/>
@@ -2615,7 +2617,7 @@
       <c r="E29" s="110"/>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="145" t="s">
         <v>8</v>
       </c>
@@ -2628,7 +2630,7 @@
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>38</v>
       </c>
@@ -2638,85 +2640,85 @@
       <c r="E31" s="99"/>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="144" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="147"/>
       <c r="C32" s="147"/>
-      <c r="D32" s="199">
+      <c r="D32" s="194">
         <v>718331.03</v>
       </c>
-      <c r="E32" s="100" t="s">
-        <v>196</v>
+      <c r="E32" s="27" t="s">
+        <v>198</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="144" t="s">
         <v>146</v>
       </c>
       <c r="B33" s="144" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C33" s="147"/>
-      <c r="D33" s="28">
+      <c r="D33" s="194">
         <v>182823.01</v>
       </c>
       <c r="E33" s="100" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="144" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="147"/>
       <c r="C34" s="147"/>
-      <c r="D34" s="199">
+      <c r="D34" s="194">
         <v>65716.08</v>
       </c>
       <c r="E34" s="100" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="144" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="147"/>
       <c r="C35" s="147"/>
-      <c r="D35" s="199">
+      <c r="D35" s="194">
         <v>7301.79</v>
       </c>
       <c r="E35" s="100" t="str">
         <f>E34</f>
-        <v>Debito 12/08</v>
+        <v>Debito 14/09</v>
       </c>
       <c r="F35" s="38"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="144" t="s">
         <v>41</v>
       </c>
       <c r="B36" s="147"/>
       <c r="C36" s="147"/>
-      <c r="D36" s="199">
+      <c r="D36" s="194">
         <v>116816.78</v>
       </c>
       <c r="E36" s="100" t="str">
         <f>E34</f>
-        <v>Debito 12/08</v>
+        <v>Debito 14/09</v>
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="145" t="s">
         <v>39</v>
       </c>
@@ -2729,7 +2731,7 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
@@ -2739,13 +2741,13 @@
       <c r="E38" s="101"/>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="215" t="s">
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="212" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="216"/>
+      <c r="B39" s="213"/>
       <c r="C39" s="148"/>
-      <c r="D39" s="188">
+      <c r="D39" s="262">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2753,14 +2755,14 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="212" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="216"/>
+      <c r="B40" s="213"/>
       <c r="C40" s="148"/>
-      <c r="D40" s="188">
-        <v>0</v>
+      <c r="D40" s="262">
+        <v>1426.62</v>
       </c>
       <c r="E40" s="21" t="str">
         <f>E39</f>
@@ -2768,7 +2770,7 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="145" t="s">
         <v>10</v>
       </c>
@@ -2777,11 +2779,11 @@
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
-        <v>205033.71</v>
+        <v>206460.33</v>
       </c>
       <c r="F41" s="38"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
@@ -2791,81 +2793,73 @@
       <c r="E42" s="102"/>
       <c r="F42" s="38"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>144</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="197">
+      <c r="D43" s="192">
         <v>2001312.7</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="F43" s="38"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>64</v>
       </c>
       <c r="B44" s="149"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="191">
-        <v>6637.89</v>
-      </c>
-      <c r="E44" s="27" t="s">
-        <v>191</v>
-      </c>
+      <c r="D44" s="188">
+        <v>0</v>
+      </c>
+      <c r="E44" s="27"/>
       <c r="F44" s="38"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="149" t="s">
-        <v>200</v>
-      </c>
+      <c r="B45" s="149"/>
       <c r="C45" s="33"/>
-      <c r="D45" s="197">
+      <c r="D45" s="192">
         <v>883.29</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="F45" s="38"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="215" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="212" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="216"/>
+      <c r="B46" s="213"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="191">
-        <v>542877.21</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>198</v>
-      </c>
+      <c r="D46" s="188">
+        <v>0</v>
+      </c>
+      <c r="E46" s="27"/>
       <c r="F46" s="38"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="150" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="151" t="s">
-        <v>173</v>
-      </c>
+      <c r="B47" s="151"/>
       <c r="C47" s="33"/>
-      <c r="D47" s="197">
+      <c r="D47" s="192">
         <v>42239.197999999997</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="F47" s="38"/>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="145" t="s">
         <v>12</v>
       </c>
@@ -2874,11 +2868,11 @@
       <c r="D48" s="26"/>
       <c r="E48" s="103">
         <f>SUM(D43:D47)</f>
-        <v>2593950.2879999997</v>
+        <v>2044435.1880000001</v>
       </c>
       <c r="F48" s="38"/>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>62</v>
       </c>
@@ -2888,407 +2882,389 @@
       <c r="E49" s="104"/>
       <c r="F49" s="38"/>
     </row>
-    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="200" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="201"/>
+    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="204" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="205"/>
       <c r="C50" s="33"/>
-      <c r="D50" s="191">
-        <v>250600</v>
+      <c r="D50" s="192">
+        <v>298200</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F50" s="38"/>
     </row>
-    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="200" t="s">
+    <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="214" t="s">
+        <v>195</v>
+      </c>
+      <c r="B51" s="215"/>
+      <c r="C51" s="144"/>
+      <c r="D51" s="192">
+        <v>50000</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="126"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="195" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="196"/>
+      <c r="C52" s="144"/>
+      <c r="D52" s="192">
+        <v>180000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="F52" s="126"/>
+    </row>
+    <row r="53" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="186" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="152"/>
+      <c r="C53" s="144"/>
+      <c r="D53" s="192">
+        <v>117400</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" s="126"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="32">
+        <f>SUM(D50:D53)</f>
+        <v>645600</v>
+      </c>
+      <c r="F54" s="38"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="96"/>
+      <c r="F55" s="38"/>
+    </row>
+    <row r="56" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="204" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="201"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="197">
-        <v>298200</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="F51" s="38"/>
-    </row>
-    <row r="52" spans="1:6" ht="106.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="215" t="s">
+      <c r="B56" s="205"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="193">
+        <f>420000*2</f>
+        <v>840000</v>
+      </c>
+      <c r="E56" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="38"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="153" t="s">
         <v>193</v>
       </c>
-      <c r="B52" s="216"/>
-      <c r="C52" s="144"/>
-      <c r="D52" s="191">
-        <v>300000</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="F52" s="126"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="205" t="s">
+      <c r="B57" s="152"/>
+      <c r="C57" s="144"/>
+      <c r="D57" s="193">
+        <v>50000</v>
+      </c>
+      <c r="E57" s="97" t="s">
         <v>194</v>
       </c>
-      <c r="B53" s="206"/>
-      <c r="C53" s="144"/>
-      <c r="D53" s="191">
-        <v>150000</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F53" s="126"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="205" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="206"/>
-      <c r="C54" s="144"/>
-      <c r="D54" s="191">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F54" s="126"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="150" t="s">
-        <v>210</v>
-      </c>
-      <c r="B55" s="189"/>
-      <c r="C55" s="144"/>
-      <c r="D55" s="191">
-        <v>240000</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F55" s="126"/>
-    </row>
-    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="205" t="s">
-        <v>221</v>
-      </c>
-      <c r="B56" s="206"/>
-      <c r="C56" s="144"/>
-      <c r="D56" s="197">
-        <v>50000</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="F56" s="126"/>
-    </row>
-    <row r="57" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="215" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="216"/>
-      <c r="C57" s="144"/>
-      <c r="D57" s="197">
-        <v>8400</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>218</v>
-      </c>
       <c r="F57" s="38"/>
     </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="200" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" s="201"/>
-      <c r="C58" s="144"/>
-      <c r="D58" s="191">
-        <v>265200</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>190</v>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="145"/>
+      <c r="C58" s="145"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="98">
+        <f>SUM(D56:D57)</f>
+        <v>890000</v>
       </c>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="186" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" s="152"/>
-      <c r="C59" s="144"/>
-      <c r="D59" s="191">
-        <v>130500</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>205</v>
-      </c>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="154"/>
+      <c r="C59" s="145"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="32"/>
       <c r="F59" s="38"/>
     </row>
-    <row r="60" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="186" t="s">
-        <v>185</v>
-      </c>
-      <c r="B60" s="152"/>
-      <c r="C60" s="144"/>
-      <c r="D60" s="191">
-        <v>118800</v>
-      </c>
-      <c r="E60" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="F60" s="126"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="32">
-        <f>SUM(D50:D60)</f>
-        <v>2161700</v>
-      </c>
-      <c r="F61" s="38"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="96"/>
-      <c r="F62" s="38"/>
-    </row>
-    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="200" t="s">
-        <v>204</v>
-      </c>
-      <c r="B63" s="201"/>
-      <c r="C63" s="144"/>
-      <c r="D63" s="192">
-        <v>210000</v>
-      </c>
-      <c r="E63" s="97"/>
-      <c r="F63" s="38"/>
-    </row>
-    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="200" t="s">
-        <v>214</v>
-      </c>
-      <c r="B64" s="201"/>
-      <c r="C64" s="144"/>
-      <c r="D64" s="193">
-        <v>0</v>
-      </c>
-      <c r="E64" s="97"/>
-      <c r="F64" s="38"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="153" t="s">
-        <v>219</v>
-      </c>
-      <c r="B65" s="152"/>
-      <c r="C65" s="144"/>
-      <c r="D65" s="198">
-        <v>50000</v>
-      </c>
-      <c r="E65" s="97" t="s">
-        <v>220</v>
-      </c>
-      <c r="F65" s="38"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="145" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="145"/>
-      <c r="C66" s="145"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="98">
-        <f>SUM(D63:D65)</f>
-        <v>260000</v>
-      </c>
-      <c r="F66" s="38"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="154"/>
-      <c r="C67" s="145"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="38"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="33" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="155"/>
-      <c r="C68" s="155"/>
-      <c r="D68" s="156">
+      <c r="B60" s="155"/>
+      <c r="C60" s="155"/>
+      <c r="D60" s="263">
         <v>69000</v>
       </c>
-      <c r="E68" s="105"/>
-      <c r="F68" s="38"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="B69" s="155"/>
-      <c r="C69" s="155"/>
-      <c r="D69" s="156">
+      <c r="E60" s="105"/>
+      <c r="F60" s="38"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" s="155"/>
+      <c r="C61" s="155"/>
+      <c r="D61" s="156">
         <f>114820.43-36</f>
         <v>114784.43</v>
       </c>
-      <c r="E69" s="105"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="38"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="157"/>
+      <c r="C62" s="157"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="32">
+        <f>SUM(D60:D61)</f>
+        <v>183784.43</v>
+      </c>
+      <c r="F62" s="38"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="33"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="38"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="158"/>
+      <c r="C64" s="158"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="38"/>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="159"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="126"/>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="160" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" s="161"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="42">
+        <f>(SUM(E21:E64))</f>
+        <v>6194926.6380000003</v>
+      </c>
+      <c r="F66" s="162"/>
+      <c r="G66" s="40"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="38"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="38"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="H68" s="44"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="163" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="164"/>
+      <c r="C69" s="165"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="46"/>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70" s="157"/>
-      <c r="C70" s="157"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="32">
-        <f>SUM(D68:D69)</f>
-        <v>183784.43</v>
-      </c>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="217"/>
+      <c r="B70" s="218"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="166"/>
+      <c r="E70" s="113"/>
       <c r="F70" s="38"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
+    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
       <c r="D71" s="33"/>
-      <c r="E71" s="34"/>
+      <c r="E71" s="33"/>
       <c r="F71" s="38"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" s="158"/>
-      <c r="C72" s="158"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="36"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="167"/>
+      <c r="B72" s="168"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="47"/>
       <c r="F72" s="38"/>
     </row>
-    <row r="73" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="159"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="126"/>
-    </row>
-    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="160" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="161"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="42">
-        <f>(SUM(E21:E72))</f>
-        <v>7638187.1179999989</v>
-      </c>
-      <c r="F74" s="162"/>
-      <c r="G74" s="40"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="38"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="169" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="170"/>
+      <c r="C73" s="170"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="106">
+        <f>SUM(D70:D72)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="38"/>
+    </row>
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="38"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="158" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" s="158"/>
+      <c r="C75" s="158"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="109">
+        <v>0</v>
+      </c>
       <c r="F75" s="38"/>
     </row>
-    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="38"/>
       <c r="B76" s="38"/>
       <c r="C76" s="38"/>
       <c r="D76" s="38"/>
       <c r="E76" s="38"/>
       <c r="F76" s="38"/>
-      <c r="H76" s="44"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="163" t="s">
-        <v>17</v>
-      </c>
-      <c r="B77" s="164"/>
-      <c r="C77" s="165"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="46"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="160" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="161"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="42">
+        <f>E73+E75</f>
+        <v>0</v>
+      </c>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="203"/>
-      <c r="B78" s="204"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="166"/>
-      <c r="E78" s="113"/>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="171" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79" s="172">
+        <f>E66</f>
+        <v>6194926.6380000003</v>
+      </c>
       <c r="C79" s="38"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
       <c r="F79" s="38"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="167"/>
-      <c r="B80" s="168"/>
-      <c r="C80" s="33"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="47"/>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="171" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="172">
+        <f>E66-E64</f>
+        <v>6194926.6380000003</v>
+      </c>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="169" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="170"/>
-      <c r="C81" s="170"/>
-      <c r="D81" s="80"/>
-      <c r="E81" s="106">
-        <f>SUM(D78:D80)</f>
-        <v>0</v>
-      </c>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="171" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="172">
+        <f>E77-E75</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="38"/>
-      <c r="B82" s="38"/>
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="171" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" s="172">
+        <f>E77</f>
+        <v>0</v>
+      </c>
       <c r="C82" s="38"/>
       <c r="D82" s="38"/>
       <c r="E82" s="38"/>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="158" t="s">
-        <v>18</v>
-      </c>
-      <c r="B83" s="158"/>
-      <c r="C83" s="158"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="109">
-        <v>0</v>
-      </c>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="38"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
       <c r="F83" s="38"/>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="38"/>
       <c r="B84" s="38"/>
       <c r="C84" s="38"/>
@@ -3296,414 +3272,345 @@
       <c r="E84" s="38"/>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="160" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" s="161"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="42">
-        <f>E81+E83</f>
-        <v>0</v>
-      </c>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="111" t="s">
+        <v>178</v>
+      </c>
+      <c r="B85" s="173">
+        <v>0</v>
+      </c>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="38"/>
-      <c r="B86" s="38"/>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="148" t="s">
+        <v>185</v>
+      </c>
+      <c r="B86" s="174">
+        <v>3191560.16</v>
+      </c>
       <c r="C86" s="38"/>
       <c r="D86" s="38"/>
       <c r="E86" s="38"/>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="171" t="s">
-        <v>20</v>
-      </c>
-      <c r="B87" s="172">
-        <f>E74</f>
-        <v>7638187.1179999989</v>
-      </c>
+    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="148" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" s="127"/>
       <c r="C87" s="38"/>
       <c r="D87" s="38"/>
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="171" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="172">
-        <f>E74-E72</f>
-        <v>7638187.1179999989</v>
+    <row r="88" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" s="176">
+        <v>3191560.16</v>
       </c>
       <c r="C88" s="38"/>
       <c r="D88" s="38"/>
       <c r="E88" s="38"/>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="171" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="172">
-        <f>E85-E83</f>
-        <v>0</v>
-      </c>
+    <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="177"/>
+      <c r="B89" s="178"/>
       <c r="C89" s="38"/>
       <c r="D89" s="38"/>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="171" t="s">
-        <v>23</v>
-      </c>
-      <c r="B90" s="172">
-        <f>E85</f>
-        <v>0</v>
-      </c>
+    <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="177"/>
+      <c r="B90" s="178"/>
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="38"/>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="38"/>
-      <c r="B91" s="38"/>
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="51">
+        <v>231400</v>
+      </c>
       <c r="C91" s="38"/>
       <c r="D91" s="38"/>
       <c r="E91" s="38"/>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="38"/>
-      <c r="B92" s="38"/>
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="148" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" s="174">
+        <v>0</v>
+      </c>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="111" t="s">
-        <v>180</v>
-      </c>
-      <c r="B93" s="173">
-        <v>0</v>
-      </c>
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="148" t="s">
+        <v>161</v>
+      </c>
+      <c r="B93" s="127"/>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="148" t="s">
-        <v>187</v>
-      </c>
-      <c r="B94" s="174">
-        <v>5125397.67</v>
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94" s="176">
+        <f>SUM(B91:B93)</f>
+        <v>231400</v>
       </c>
       <c r="C94" s="38"/>
       <c r="D94" s="38"/>
       <c r="E94" s="38"/>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="148" t="s">
-        <v>207</v>
-      </c>
-      <c r="B95" s="190">
-        <v>-2000574.76</v>
-      </c>
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="177"/>
+      <c r="B95" s="178"/>
       <c r="C95" s="38"/>
       <c r="D95" s="38"/>
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="148" t="s">
-        <v>186</v>
-      </c>
-      <c r="B96" s="127">
-        <f>B97-(B94+B95)</f>
-        <v>66737.25</v>
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="111" t="s">
+        <v>162</v>
+      </c>
+      <c r="B96" s="51">
+        <v>58418</v>
       </c>
       <c r="C96" s="38"/>
       <c r="D96" s="38"/>
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="175" t="s">
-        <v>176</v>
-      </c>
-      <c r="B97" s="176">
-        <v>3191560.16</v>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="148" t="s">
+        <v>160</v>
+      </c>
+      <c r="B97" s="174">
+        <v>0</v>
       </c>
       <c r="C97" s="38"/>
       <c r="D97" s="38"/>
       <c r="E97" s="38"/>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="177"/>
-      <c r="B98" s="178"/>
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="148" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="128">
+        <v>-8400</v>
+      </c>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="177"/>
-      <c r="B99" s="178"/>
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B99" s="176">
+        <f>SUM(B96:B98)</f>
+        <v>50018</v>
+      </c>
       <c r="C99" s="38"/>
       <c r="D99" s="38"/>
       <c r="E99" s="38"/>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="B100" s="51">
-        <v>231400</v>
-      </c>
-      <c r="C100" s="38"/>
-      <c r="D100" s="38"/>
-      <c r="E100" s="38"/>
-      <c r="F100" s="38"/>
-    </row>
-    <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="148" t="s">
-        <v>160</v>
-      </c>
-      <c r="B101" s="174">
-        <v>0</v>
-      </c>
-      <c r="C101" s="38"/>
-      <c r="D101" s="38"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38"/>
-    </row>
-    <row r="102" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="148" t="s">
-        <v>161</v>
-      </c>
-      <c r="B102" s="127"/>
-      <c r="C102" s="38"/>
+    <row r="100" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="107"/>
+      <c r="E100" s="107"/>
+    </row>
+    <row r="101" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="111" t="s">
+        <v>174</v>
+      </c>
+      <c r="B101" s="51">
+        <v>-7980.4499999999534</v>
+      </c>
+      <c r="C101" s="49"/>
+      <c r="D101" s="108"/>
+      <c r="E101" s="108"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="128">
+        <f>-B80-B81</f>
+        <v>-6194926.6380000003</v>
+      </c>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-    </row>
-    <row r="103" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="175" t="s">
-        <v>176</v>
-      </c>
-      <c r="B103" s="176">
-        <f>SUM(B100:B102)</f>
-        <v>231400</v>
-      </c>
-      <c r="C103" s="38"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="52">
+        <f>B117</f>
+        <v>971106</v>
+      </c>
       <c r="D103" s="38"/>
       <c r="E103" s="38"/>
-      <c r="F103" s="38"/>
-    </row>
-    <row r="104" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="177"/>
-      <c r="B104" s="178"/>
-      <c r="C104" s="38"/>
+      <c r="F103" s="48"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B104" s="53">
+        <f>PRORRATEO!G61</f>
+        <v>10127798.860000001</v>
+      </c>
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
-      <c r="F104" s="38"/>
-    </row>
-    <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="111" t="s">
-        <v>162</v>
-      </c>
-      <c r="B105" s="51">
-        <v>58418</v>
-      </c>
-      <c r="C105" s="38"/>
-      <c r="D105" s="38"/>
+      <c r="F104" s="48"/>
+    </row>
+    <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B105" s="190">
+        <v>0</v>
+      </c>
+      <c r="D105" s="126"/>
       <c r="E105" s="38"/>
-      <c r="F105" s="38"/>
-    </row>
-    <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="148" t="s">
-        <v>160</v>
-      </c>
-      <c r="B106" s="174">
-        <v>0</v>
-      </c>
-      <c r="C106" s="38"/>
-      <c r="D106" s="38"/>
-      <c r="E106" s="38"/>
-      <c r="F106" s="38"/>
-    </row>
-    <row r="107" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="175" t="s">
-        <v>176</v>
-      </c>
-      <c r="B107" s="176">
-        <f>SUM(B105:B106)</f>
-        <v>58418</v>
-      </c>
-      <c r="C107" s="38"/>
-      <c r="D107" s="38"/>
-      <c r="E107" s="38"/>
-      <c r="F107" s="38"/>
-    </row>
-    <row r="108" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A108"/>
-      <c r="B108" s="48"/>
-      <c r="C108" s="49"/>
-      <c r="D108" s="107"/>
-      <c r="E108" s="107"/>
-    </row>
-    <row r="109" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="111" t="s">
-        <v>175</v>
-      </c>
-      <c r="B109" s="51">
-        <v>-62147.730000001146</v>
-      </c>
-      <c r="C109" s="49"/>
-      <c r="D109" s="108"/>
-      <c r="E109" s="108"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B110" s="128">
-        <f>-B88-B89</f>
-        <v>-7638187.1179999989</v>
-      </c>
-      <c r="D110" s="38"/>
-      <c r="E110" s="38"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B111" s="52">
-        <f>B123</f>
-        <v>0</v>
-      </c>
-      <c r="D111" s="38"/>
-      <c r="E111" s="38"/>
-      <c r="F111" s="48"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B112" s="53">
-        <f>PRORRATEO!G61</f>
-        <v>5966274.4000000004</v>
-      </c>
-      <c r="D112" s="38"/>
-      <c r="E112" s="38"/>
-      <c r="F112" s="48"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="B113" s="190">
-        <v>-160000</v>
-      </c>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="48"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B114" s="190">
-        <v>-16162</v>
-      </c>
-      <c r="D114" s="38"/>
-      <c r="E114" s="126"/>
-      <c r="F114" s="48"/>
-    </row>
-    <row r="115" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B115" s="195">
-        <f>-B95</f>
-        <v>2000574.76</v>
-      </c>
-      <c r="D115" s="126"/>
-      <c r="E115" s="38"/>
-      <c r="F115" s="48"/>
-    </row>
-    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="54" t="s">
+      <c r="F105" s="48"/>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="B116" s="55">
-        <f>SUM(B109:C115)</f>
-        <v>90352.312000000151</v>
-      </c>
-      <c r="D116" s="48"/>
-      <c r="E116" s="40"/>
-      <c r="F116" s="40"/>
-    </row>
-    <row r="117" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E117" s="40"/>
-    </row>
-    <row r="118" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="129" t="s">
+      <c r="B106" s="55">
+        <f>SUM(B101:C105)</f>
+        <v>4895997.7720000008</v>
+      </c>
+      <c r="D106" s="48"/>
+      <c r="E106" s="40"/>
+      <c r="F106" s="40"/>
+    </row>
+    <row r="107" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="40"/>
+    </row>
+    <row r="108" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="129" t="s">
         <v>163</v>
       </c>
-      <c r="B118" s="130">
-        <f>B116+B103</f>
-        <v>321752.31200000015</v>
-      </c>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
-    </row>
-    <row r="119" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="202" t="s">
+      <c r="B108" s="130">
+        <f>B106+B94</f>
+        <v>5127397.7720000008</v>
+      </c>
+      <c r="D108" s="40"/>
+      <c r="E108" s="40"/>
+    </row>
+    <row r="109" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="216" t="s">
         <v>25</v>
       </c>
-      <c r="B120" s="202"/>
-      <c r="C120" s="202"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="202"/>
-      <c r="B121" s="202"/>
-      <c r="C121" s="202"/>
-    </row>
-    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="56"/>
-      <c r="B122" s="79"/>
-      <c r="C122" s="57"/>
-      <c r="D122" s="43"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="59">
-        <f>SUM(B122:B122)</f>
-        <v>0</v>
-      </c>
-      <c r="C123" s="60"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M124" s="61"/>
+      <c r="B110" s="216"/>
+      <c r="C110" s="216"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="216"/>
+      <c r="B111" s="216"/>
+      <c r="C111" s="216"/>
+    </row>
+    <row r="112" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="B112" s="79">
+        <v>269232</v>
+      </c>
+      <c r="C112" s="57"/>
+      <c r="D112" s="43"/>
+    </row>
+    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B113" s="79">
+        <v>21606</v>
+      </c>
+      <c r="C113" s="57"/>
+      <c r="D113" s="43"/>
+    </row>
+    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" s="79">
+        <v>262068</v>
+      </c>
+      <c r="C114" s="57"/>
+      <c r="D114" s="43"/>
+    </row>
+    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" s="79">
+        <v>376000</v>
+      </c>
+      <c r="C115" s="57"/>
+      <c r="D115" s="43"/>
+    </row>
+    <row r="116" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" s="79">
+        <v>42200</v>
+      </c>
+      <c r="C116" s="57"/>
+      <c r="D116" s="43"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" s="59">
+        <f>SUM(B112:B116)</f>
+        <v>971106</v>
+      </c>
+      <c r="C117" s="60"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M118" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="15">
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A110:C111"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A63:B63"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
@@ -3712,17 +3619,8 @@
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A120:C121"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3733,28 +3631,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="66"/>
       <c r="B1" s="120"/>
       <c r="C1" s="67"/>
@@ -3764,21 +3661,21 @@
       <c r="G1" s="120"/>
       <c r="H1" s="120"/>
       <c r="I1" s="120"/>
-      <c r="J1" s="245" t="str">
+      <c r="J1" s="219" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="245"/>
-      <c r="L1" s="245"/>
-      <c r="M1" s="245"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="245"/>
-      <c r="P1" s="246"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="220"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>164</v>
       </c>
@@ -3787,24 +3684,24 @@
         <f>D2-C4-C5</f>
         <v>5827100.4799999995</v>
       </c>
-      <c r="D2" s="196">
+      <c r="D2" s="191">
         <v>7736519.879999999</v>
       </c>
       <c r="E2" s="68"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="229"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="M2" s="247"/>
-      <c r="N2" s="247"/>
-      <c r="O2" s="247"/>
-      <c r="P2" s="248"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="222"/>
       <c r="Q2" s="62"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -3818,17 +3715,17 @@
       <c r="G3" s="125"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="M3" s="247"/>
-      <c r="N3" s="247"/>
-      <c r="O3" s="247"/>
-      <c r="P3" s="248"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
+      <c r="M3" s="221"/>
+      <c r="N3" s="221"/>
+      <c r="O3" s="221"/>
+      <c r="P3" s="222"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -3842,17 +3739,17 @@
       <c r="G4" s="125"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="247"/>
-      <c r="L4" s="247"/>
-      <c r="M4" s="247"/>
-      <c r="N4" s="247"/>
-      <c r="O4" s="247"/>
-      <c r="P4" s="248"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="222"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="131" t="s">
         <v>165</v>
       </c>
@@ -3866,203 +3763,203 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="M5" s="249"/>
-      <c r="N5" s="249"/>
-      <c r="O5" s="249"/>
-      <c r="P5" s="250"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="223"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="224"/>
       <c r="Q5" s="62"/>
     </row>
-    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="218" t="s">
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="231" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="219"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="220"/>
-      <c r="H6" s="220"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="220"/>
-      <c r="L6" s="220"/>
-      <c r="M6" s="220"/>
-      <c r="N6" s="220"/>
-      <c r="O6" s="220"/>
-      <c r="P6" s="221"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+      <c r="I6" s="233"/>
+      <c r="J6" s="233"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="233"/>
+      <c r="O6" s="233"/>
+      <c r="P6" s="234"/>
       <c r="Q6" s="62"/>
     </row>
-    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="223"/>
-      <c r="P7" s="224"/>
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="235"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="237"/>
       <c r="Q7" s="62"/>
     </row>
-    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="222"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
-      <c r="K8" s="223"/>
-      <c r="L8" s="223"/>
-      <c r="M8" s="223"/>
-      <c r="N8" s="223"/>
-      <c r="O8" s="223"/>
-      <c r="P8" s="224"/>
+    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="235"/>
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="236"/>
+      <c r="E8" s="236"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="237"/>
       <c r="Q8" s="62"/>
     </row>
-    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="222"/>
-      <c r="B9" s="223"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
-      <c r="K9" s="223"/>
-      <c r="L9" s="223"/>
-      <c r="M9" s="223"/>
-      <c r="N9" s="223"/>
-      <c r="O9" s="223"/>
-      <c r="P9" s="224"/>
+    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="235"/>
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="237"/>
       <c r="Q9" s="62"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="225"/>
-      <c r="B10" s="226"/>
-      <c r="C10" s="226"/>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="226"/>
-      <c r="I10" s="226"/>
-      <c r="J10" s="226"/>
-      <c r="K10" s="226"/>
-      <c r="L10" s="226"/>
-      <c r="M10" s="226"/>
-      <c r="N10" s="226"/>
-      <c r="O10" s="226"/>
-      <c r="P10" s="227"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="238" t="s">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="238"/>
+      <c r="B10" s="239"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="240"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="249" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="239"/>
-      <c r="C11" s="239"/>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
-      <c r="N11" s="239"/>
-      <c r="O11" s="239"/>
-      <c r="P11" s="240"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="228" t="s">
+      <c r="B11" s="250"/>
+      <c r="C11" s="250"/>
+      <c r="D11" s="250"/>
+      <c r="E11" s="250"/>
+      <c r="F11" s="250"/>
+      <c r="G11" s="250"/>
+      <c r="H11" s="250"/>
+      <c r="I11" s="250"/>
+      <c r="J11" s="250"/>
+      <c r="K11" s="250"/>
+      <c r="L11" s="250"/>
+      <c r="M11" s="250"/>
+      <c r="N11" s="250"/>
+      <c r="O11" s="250"/>
+      <c r="P11" s="251"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="241" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="243" t="s">
+      <c r="B12" s="254" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="230" t="s">
+      <c r="C12" s="243" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="230" t="s">
+      <c r="D12" s="243" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="230" t="s">
+      <c r="E12" s="243" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="232" t="s">
+      <c r="F12" s="225" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="234" t="s">
+      <c r="G12" s="245" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="236" t="s">
+      <c r="H12" s="247" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="232" t="s">
+      <c r="I12" s="225" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="232" t="s">
+      <c r="J12" s="225" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="232" t="s">
+      <c r="K12" s="225" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="243" t="s">
+      <c r="L12" s="254" t="s">
         <v>169</v>
       </c>
-      <c r="M12" s="232" t="s">
+      <c r="M12" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="N12" s="241" t="s">
-        <v>181</v>
+      <c r="N12" s="252" t="s">
+        <v>179</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="251" t="s">
+      <c r="P12" s="227" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="229"/>
-      <c r="B13" s="244"/>
-      <c r="C13" s="231"/>
-      <c r="D13" s="231"/>
-      <c r="E13" s="231"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="244"/>
-      <c r="M13" s="233"/>
-      <c r="N13" s="242"/>
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="242"/>
+      <c r="B13" s="255"/>
+      <c r="C13" s="244"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="226"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="226"/>
+      <c r="J13" s="226"/>
+      <c r="K13" s="226"/>
+      <c r="L13" s="255"/>
+      <c r="M13" s="226"/>
+      <c r="N13" s="253"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P13" s="252"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="228"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
         <v>1</v>
       </c>
@@ -4077,11 +3974,11 @@
         <v>5.22</v>
       </c>
       <c r="F14" s="63">
-        <v>375215.01</v>
-      </c>
-      <c r="G14" s="63">
+        <v>403846.01</v>
+      </c>
+      <c r="G14" s="264">
         <f t="shared" ref="G14" si="0">F14</f>
-        <v>375215.01</v>
+        <v>403846.01</v>
       </c>
       <c r="H14" s="75">
         <f t="shared" ref="H14:H59" si="1">F14-G14</f>
@@ -4120,65 +4017,67 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="83">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="265">
         <v>2</v>
       </c>
-      <c r="B15" s="123" t="s">
+      <c r="B15" s="266" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="267" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="180">
         <v>3.4</v>
       </c>
-      <c r="F15" s="63">
-        <v>278667.02</v>
-      </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="75">
+      <c r="F15" s="181">
+        <v>550069.02</v>
+      </c>
+      <c r="G15" s="268">
+        <v>288000</v>
+      </c>
+      <c r="H15" s="182">
         <f t="shared" si="1"/>
-        <v>278667.02</v>
-      </c>
-      <c r="I15" s="75">
+        <v>262069.02000000002</v>
+      </c>
+      <c r="I15" s="182">
         <f t="shared" ref="I15:I59" si="4">IF(H15&gt;0,H15*3%,0)</f>
-        <v>8360.0105999999996</v>
-      </c>
-      <c r="J15" s="82">
+        <v>7862.0706</v>
+      </c>
+      <c r="J15" s="183">
         <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
         <v>198121.41631999999</v>
       </c>
-      <c r="K15" s="82">
+      <c r="K15" s="183">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="82">
+      <c r="L15" s="183">
         <f t="shared" ref="L15:L59" si="6">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M15" s="82">
+      <c r="M15" s="183">
         <f t="shared" ref="M15:M59" si="7">C$5*E15/100</f>
         <v>58704.277259999995</v>
       </c>
-      <c r="N15" s="82"/>
-      <c r="O15" s="76">
+      <c r="N15" s="183"/>
+      <c r="O15" s="184">
         <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>550069.02</v>
-      </c>
-      <c r="P15" s="91">
+        <v>532973.02</v>
+      </c>
+      <c r="P15" s="185">
         <f t="shared" si="3"/>
-        <v>566571.02</v>
+        <v>548962.02</v>
       </c>
       <c r="Q15" s="40">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="83">
         <v>3</v>
       </c>
@@ -4195,14 +4094,14 @@
         <v>2.54</v>
       </c>
       <c r="F16" s="63">
-        <v>182576.03</v>
-      </c>
-      <c r="G16" s="63">
-        <v>183000</v>
+        <v>196084.03</v>
+      </c>
+      <c r="G16" s="264">
+        <v>198000</v>
       </c>
       <c r="H16" s="75">
         <f t="shared" si="1"/>
-        <v>-423.97000000000116</v>
+        <v>-1915.9700000000012</v>
       </c>
       <c r="I16" s="75">
         <f t="shared" si="4"/>
@@ -4227,11 +4126,11 @@
       <c r="N16" s="82"/>
       <c r="O16" s="76">
         <f t="shared" si="8"/>
-        <v>196084.03</v>
+        <v>194592.03</v>
       </c>
       <c r="P16" s="91">
         <f t="shared" si="3"/>
-        <v>201967.03</v>
+        <v>200430.03</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
@@ -4241,7 +4140,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="83">
         <v>4</v>
       </c>
@@ -4258,15 +4157,15 @@
         <v>5.19</v>
       </c>
       <c r="F17" s="63">
-        <v>361285.04</v>
-      </c>
-      <c r="G17" s="63">
-        <f>435125-G55-G44</f>
-        <v>374026.27</v>
+        <v>432284.04</v>
+      </c>
+      <c r="G17" s="264">
+        <f>498075-G55-G44</f>
+        <v>432314.27</v>
       </c>
       <c r="H17" s="75">
         <f t="shared" si="1"/>
-        <v>-12741.23000000004</v>
+        <v>-30.230000000039581</v>
       </c>
       <c r="I17" s="75">
         <f t="shared" si="4"/>
@@ -4293,11 +4192,11 @@
       </c>
       <c r="O17" s="76">
         <f t="shared" si="8"/>
-        <v>432284.04</v>
+        <v>444995.04</v>
       </c>
       <c r="P17" s="91">
         <f t="shared" si="3"/>
-        <v>445253.04</v>
+        <v>458345.04</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="9"/>
@@ -4307,7 +4206,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="83">
         <v>5</v>
       </c>
@@ -4324,18 +4223,18 @@
         <v>3.4</v>
       </c>
       <c r="F18" s="63">
-        <v>244044.05</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0</v>
+        <v>514407.05</v>
+      </c>
+      <c r="G18" s="264">
+        <v>336377.05</v>
       </c>
       <c r="H18" s="75">
         <f t="shared" si="1"/>
-        <v>244044.05</v>
+        <v>178030</v>
       </c>
       <c r="I18" s="75">
         <f t="shared" si="4"/>
-        <v>7321.3214999999991</v>
+        <v>5340.9</v>
       </c>
       <c r="J18" s="82">
         <f t="shared" si="5"/>
@@ -4356,18 +4255,18 @@
       <c r="N18" s="82"/>
       <c r="O18" s="76">
         <f t="shared" si="8"/>
-        <v>514407.05</v>
+        <v>446413.05</v>
       </c>
       <c r="P18" s="91">
         <f t="shared" si="3"/>
-        <v>529839.05000000005</v>
+        <v>459805.05</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="83">
         <v>6</v>
       </c>
@@ -4378,17 +4277,17 @@
         <v>117</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
       </c>
       <c r="F19" s="63">
-        <v>182576.06</v>
-      </c>
-      <c r="G19" s="63">
+        <v>196508.06</v>
+      </c>
+      <c r="G19" s="264">
         <f>F19</f>
-        <v>182576.06</v>
+        <v>196508.06</v>
       </c>
       <c r="H19" s="75">
         <f t="shared" si="1"/>
@@ -4428,7 +4327,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="83">
         <v>7</v>
       </c>
@@ -4443,11 +4342,11 @@
         <v>5.19</v>
       </c>
       <c r="F20" s="63">
-        <v>373058.07</v>
-      </c>
-      <c r="G20" s="63">
+        <v>401525.07</v>
+      </c>
+      <c r="G20" s="264">
         <f t="shared" ref="G20:G25" si="10">F20</f>
-        <v>373058.07</v>
+        <v>401525.07</v>
       </c>
       <c r="H20" s="75">
         <f t="shared" si="1"/>
@@ -4487,7 +4386,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="83">
         <v>8</v>
       </c>
@@ -4502,11 +4401,11 @@
         <v>3.4</v>
       </c>
       <c r="F21" s="63">
-        <v>244393.08</v>
-      </c>
-      <c r="G21" s="63">
+        <v>263042.08</v>
+      </c>
+      <c r="G21" s="264">
         <f t="shared" si="10"/>
-        <v>244393.08</v>
+        <v>263042.08</v>
       </c>
       <c r="H21" s="75">
         <f t="shared" si="1"/>
@@ -4546,59 +4445,59 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="83">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="265">
         <v>9</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="266" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="77" t="s">
+      <c r="D22" s="179" t="s">
         <v>151</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E22" s="180">
         <v>2.54</v>
       </c>
-      <c r="F22" s="63">
-        <v>182576.09</v>
-      </c>
-      <c r="G22" s="63">
+      <c r="F22" s="181">
+        <v>196508.09</v>
+      </c>
+      <c r="G22" s="268">
         <f t="shared" si="10"/>
-        <v>182576.09</v>
-      </c>
-      <c r="H22" s="75">
+        <v>196508.09</v>
+      </c>
+      <c r="H22" s="182">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="182">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="82">
+      <c r="J22" s="183">
         <f t="shared" si="5"/>
         <v>148008.35219199999</v>
       </c>
-      <c r="K22" s="82">
+      <c r="K22" s="183">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="82">
+      <c r="L22" s="183">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M22" s="82">
+      <c r="M22" s="183">
         <f t="shared" si="7"/>
         <v>43855.548305999997</v>
       </c>
-      <c r="N22" s="82"/>
-      <c r="O22" s="76">
+      <c r="N22" s="183"/>
+      <c r="O22" s="184">
         <f t="shared" si="8"/>
         <v>196508.09</v>
       </c>
-      <c r="P22" s="91">
+      <c r="P22" s="185">
         <f t="shared" si="3"/>
         <v>202403.09</v>
       </c>
@@ -4607,7 +4506,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="83">
         <v>10</v>
       </c>
@@ -4622,11 +4521,11 @@
         <v>5.19</v>
       </c>
       <c r="F23" s="63">
-        <v>373058.1</v>
-      </c>
-      <c r="G23" s="63">
+        <v>401525.1</v>
+      </c>
+      <c r="G23" s="264">
         <f t="shared" si="10"/>
-        <v>373058.1</v>
+        <v>401525.1</v>
       </c>
       <c r="H23" s="75">
         <f t="shared" si="1"/>
@@ -4666,7 +4565,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="83">
         <v>11</v>
       </c>
@@ -4683,19 +4582,16 @@
         <v>3.4</v>
       </c>
       <c r="F24" s="63">
-        <v>244393.11</v>
-      </c>
-      <c r="G24" s="63">
-        <f t="shared" si="10"/>
-        <v>244393.11</v>
-      </c>
+        <v>263042.11</v>
+      </c>
+      <c r="G24" s="63"/>
       <c r="H24" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>263042.11</v>
       </c>
       <c r="I24" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7891.2632999999996</v>
       </c>
       <c r="J24" s="82">
         <f t="shared" si="5"/>
@@ -4716,18 +4612,18 @@
       <c r="N24" s="82"/>
       <c r="O24" s="76">
         <f t="shared" si="8"/>
-        <v>263042.11</v>
+        <v>533975.11</v>
       </c>
       <c r="P24" s="91">
         <f t="shared" si="3"/>
-        <v>270933.11</v>
+        <v>549994.11</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83">
         <v>12</v>
       </c>
@@ -4744,11 +4640,11 @@
         <v>2.54</v>
       </c>
       <c r="F25" s="63">
-        <v>182576.12</v>
-      </c>
-      <c r="G25" s="63">
+        <v>196508.12</v>
+      </c>
+      <c r="G25" s="264">
         <f t="shared" si="10"/>
-        <v>182576.12</v>
+        <v>196508.12</v>
       </c>
       <c r="H25" s="75">
         <f t="shared" si="1"/>
@@ -4788,7 +4684,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="83">
         <v>13</v>
       </c>
@@ -4796,18 +4692,18 @@
         <v>82</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D26" s="77"/>
       <c r="E26" s="74">
         <v>5.19</v>
       </c>
       <c r="F26" s="63">
-        <v>363291.13</v>
-      </c>
-      <c r="G26" s="63">
+        <v>401525.13</v>
+      </c>
+      <c r="G26" s="264">
         <f>F26</f>
-        <v>363291.13</v>
+        <v>401525.13</v>
       </c>
       <c r="H26" s="75">
         <f t="shared" si="1"/>
@@ -4847,7 +4743,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="134">
         <v>14</v>
       </c>
@@ -4862,15 +4758,15 @@
         <v>3.4</v>
       </c>
       <c r="F27" s="139">
-        <v>235999.14</v>
-      </c>
-      <c r="G27" s="139">
-        <f>314895.52-G51</f>
-        <v>245171.14</v>
+        <v>253870.14</v>
+      </c>
+      <c r="G27" s="270">
+        <f>338781.52-G51</f>
+        <v>263737.14</v>
       </c>
       <c r="H27" s="140">
         <f t="shared" si="1"/>
-        <v>-9172</v>
+        <v>-9867</v>
       </c>
       <c r="I27" s="140">
         <f t="shared" si="4"/>
@@ -4895,18 +4791,18 @@
       <c r="N27" s="141"/>
       <c r="O27" s="142">
         <f t="shared" si="8"/>
-        <v>253870.14</v>
+        <v>253175.14</v>
       </c>
       <c r="P27" s="143">
         <f t="shared" si="3"/>
-        <v>261486.14</v>
+        <v>260770.14</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="83">
         <v>15</v>
       </c>
@@ -4923,11 +4819,11 @@
         <v>2.54</v>
       </c>
       <c r="F28" s="63">
-        <v>182576.15</v>
-      </c>
-      <c r="G28" s="63">
+        <v>196508.15</v>
+      </c>
+      <c r="G28" s="264">
         <f t="shared" ref="G28" si="11">F28</f>
-        <v>182576.15</v>
+        <v>196508.15</v>
       </c>
       <c r="H28" s="75">
         <f t="shared" si="1"/>
@@ -4967,7 +4863,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="83">
         <v>16</v>
       </c>
@@ -4982,11 +4878,11 @@
         <v>5.19</v>
       </c>
       <c r="F29" s="63">
-        <v>373058.16</v>
-      </c>
-      <c r="G29" s="63">
+        <v>401525.16</v>
+      </c>
+      <c r="G29" s="264">
         <f>F29</f>
-        <v>373058.16</v>
+        <v>401525.16</v>
       </c>
       <c r="H29" s="75">
         <f t="shared" si="1"/>
@@ -5026,75 +4922,74 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="83">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="265">
         <v>17</v>
       </c>
-      <c r="B30" s="123" t="s">
+      <c r="B30" s="266" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="72" t="s">
+      <c r="C30" s="267" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="179" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="180">
         <v>3.4</v>
       </c>
-      <c r="F30" s="63">
-        <v>242901.17</v>
-      </c>
-      <c r="G30" s="63">
-        <f>243901.17</f>
-        <v>243901.17</v>
-      </c>
-      <c r="H30" s="75">
+      <c r="F30" s="181">
+        <v>262042.17</v>
+      </c>
+      <c r="G30" s="268">
+        <v>269904</v>
+      </c>
+      <c r="H30" s="182">
         <f t="shared" si="1"/>
-        <v>-1000</v>
-      </c>
-      <c r="I30" s="75">
+        <v>-7861.8299999999872</v>
+      </c>
+      <c r="I30" s="182">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="82">
+      <c r="J30" s="183">
         <f t="shared" si="5"/>
         <v>198121.41631999999</v>
       </c>
-      <c r="K30" s="82">
+      <c r="K30" s="183">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="82">
+      <c r="L30" s="183">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M30" s="82">
+      <c r="M30" s="183">
         <f t="shared" si="7"/>
         <v>58704.277259999995</v>
       </c>
-      <c r="N30" s="82"/>
-      <c r="O30" s="76">
+      <c r="N30" s="183"/>
+      <c r="O30" s="184">
         <f t="shared" si="8"/>
-        <v>262042.17</v>
-      </c>
-      <c r="P30" s="91">
+        <v>255180.17</v>
+      </c>
+      <c r="P30" s="185">
         <f t="shared" si="3"/>
-        <v>269903.17000000004</v>
+        <v>262835.17000000004</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="262">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="199">
         <v>18</v>
       </c>
-      <c r="B31" s="263" t="s">
+      <c r="B31" s="200" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="264" t="s">
+      <c r="C31" s="201" t="s">
         <v>131</v>
       </c>
       <c r="D31" s="73"/>
@@ -5102,16 +4997,19 @@
         <v>2.54</v>
       </c>
       <c r="F31" s="63">
-        <v>1846650.18</v>
-      </c>
-      <c r="G31" s="63"/>
+        <v>2098557.1800000002</v>
+      </c>
+      <c r="G31" s="264">
+        <f>251908+923325</f>
+        <v>1175233</v>
+      </c>
       <c r="H31" s="75">
         <f t="shared" si="1"/>
-        <v>1846650.18</v>
+        <v>923324.18000000017</v>
       </c>
       <c r="I31" s="75">
         <f t="shared" si="4"/>
-        <v>55399.505399999995</v>
+        <v>27699.725400000003</v>
       </c>
       <c r="J31" s="82">
         <f t="shared" si="5"/>
@@ -5132,18 +5030,18 @@
       <c r="N31" s="82"/>
       <c r="O31" s="76">
         <f t="shared" si="8"/>
-        <v>2098557.1800000002</v>
+        <v>1147532.18</v>
       </c>
       <c r="P31" s="91">
         <f t="shared" si="3"/>
-        <v>2161514.1800000002</v>
+        <v>1181958.18</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="83">
         <v>19</v>
       </c>
@@ -5158,18 +5056,19 @@
         <v>5.19</v>
       </c>
       <c r="F32" s="63">
-        <v>1594507.19</v>
-      </c>
-      <c r="G32" s="63">
-        <v>0</v>
+        <v>2043868.19</v>
+      </c>
+      <c r="G32" s="264">
+        <f>2141620.52</f>
+        <v>2141620.52</v>
       </c>
       <c r="H32" s="75">
         <f t="shared" si="1"/>
-        <v>1594507.19</v>
+        <v>-97752.330000000075</v>
       </c>
       <c r="I32" s="75">
         <f t="shared" si="4"/>
-        <v>47835.215699999993</v>
+        <v>0</v>
       </c>
       <c r="J32" s="82">
         <f t="shared" si="5"/>
@@ -5190,74 +5089,74 @@
       <c r="N32" s="82"/>
       <c r="O32" s="76">
         <f t="shared" si="8"/>
-        <v>2043868.19</v>
+        <v>303773.19</v>
       </c>
       <c r="P32" s="91">
         <f t="shared" si="3"/>
-        <v>2105184.19</v>
+        <v>312886.19</v>
       </c>
       <c r="Q32" s="40">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="134">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="83">
         <v>20</v>
       </c>
-      <c r="B33" s="135" t="s">
+      <c r="B33" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="136" t="s">
+      <c r="C33" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="179"/>
-      <c r="E33" s="180">
+      <c r="D33" s="77"/>
+      <c r="E33" s="74">
         <v>3.4</v>
       </c>
-      <c r="F33" s="181">
-        <v>237260.2</v>
-      </c>
-      <c r="G33" s="181">
-        <f>249002-G47</f>
-        <v>243251.66</v>
-      </c>
-      <c r="H33" s="182">
+      <c r="F33" s="63">
+        <v>257050.2</v>
+      </c>
+      <c r="G33" s="264">
+        <f>264762.2</f>
+        <v>264762.2</v>
+      </c>
+      <c r="H33" s="75">
         <f t="shared" si="1"/>
-        <v>-5991.4599999999919</v>
-      </c>
-      <c r="I33" s="182"/>
-      <c r="J33" s="183">
+        <v>-7712</v>
+      </c>
+      <c r="I33" s="75"/>
+      <c r="J33" s="82">
         <f t="shared" si="5"/>
         <v>198121.41631999999</v>
       </c>
-      <c r="K33" s="183">
+      <c r="K33" s="82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="183">
+      <c r="L33" s="82">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="183">
+      <c r="M33" s="82">
         <f t="shared" si="7"/>
         <v>58704.277259999995</v>
       </c>
-      <c r="N33" s="183"/>
-      <c r="O33" s="184">
+      <c r="N33" s="82"/>
+      <c r="O33" s="76">
         <f t="shared" si="8"/>
-        <v>257050.2</v>
-      </c>
-      <c r="P33" s="185">
+        <v>255330.2</v>
+      </c>
+      <c r="P33" s="91">
         <f t="shared" si="3"/>
-        <v>264762.2</v>
+        <v>262990.2</v>
       </c>
       <c r="Q33" s="40">
         <f t="shared" ref="Q33:Q59" si="12">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="83">
         <v>21</v>
       </c>
@@ -5274,11 +5173,11 @@
         <v>2.54</v>
       </c>
       <c r="F34" s="63">
-        <v>182576.21</v>
-      </c>
-      <c r="G34" s="63">
+        <v>196508.21</v>
+      </c>
+      <c r="G34" s="264">
         <f t="shared" ref="G34:G35" si="13">F34</f>
-        <v>182576.21</v>
+        <v>196508.21</v>
       </c>
       <c r="H34" s="75">
         <f t="shared" si="1"/>
@@ -5318,7 +5217,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="83">
         <f>A34+1</f>
         <v>22</v>
@@ -5336,11 +5235,11 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="F35" s="63">
-        <v>355088.22</v>
-      </c>
-      <c r="G35" s="63">
+        <v>382184.22</v>
+      </c>
+      <c r="G35" s="264">
         <f t="shared" si="13"/>
-        <v>355088.22</v>
+        <v>382184.22</v>
       </c>
       <c r="H35" s="75">
         <f t="shared" si="1"/>
@@ -5380,7 +5279,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="83">
         <f t="shared" ref="A36:A59" si="15">A35+1</f>
         <v>23</v>
@@ -5398,19 +5297,18 @@
         <v>3.28</v>
       </c>
       <c r="F36" s="63">
-        <v>229421.23</v>
-      </c>
-      <c r="G36" s="63">
-        <f>229441</f>
-        <v>229441</v>
+        <v>253738.23</v>
+      </c>
+      <c r="G36" s="264">
+        <v>241350.23</v>
       </c>
       <c r="H36" s="75">
         <f t="shared" si="1"/>
-        <v>-19.769999999989523</v>
+        <v>12388</v>
       </c>
       <c r="I36" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>371.64</v>
       </c>
       <c r="J36" s="82">
         <f t="shared" si="5"/>
@@ -5431,18 +5329,18 @@
       <c r="N36" s="82"/>
       <c r="O36" s="76">
         <f t="shared" si="8"/>
-        <v>253738.23</v>
+        <v>266517.23</v>
       </c>
       <c r="P36" s="91">
         <f t="shared" si="14"/>
-        <v>261350.23</v>
+        <v>274513.23</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="12"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="83">
         <f t="shared" si="15"/>
         <v>24</v>
@@ -5458,18 +5356,19 @@
         <v>2.41</v>
       </c>
       <c r="F37" s="63">
-        <v>168602.23999999999</v>
-      </c>
-      <c r="G37" s="63">
-        <v>0</v>
+        <v>360110.24</v>
+      </c>
+      <c r="G37" s="264">
+        <f>197253+173660.24</f>
+        <v>370913.24</v>
       </c>
       <c r="H37" s="75">
         <f t="shared" si="1"/>
-        <v>168602.23999999999</v>
+        <v>-10803</v>
       </c>
       <c r="I37" s="75">
         <f t="shared" si="4"/>
-        <v>5058.0671999999995</v>
+        <v>0</v>
       </c>
       <c r="J37" s="82">
         <f t="shared" si="5"/>
@@ -5490,21 +5389,21 @@
       <c r="N37" s="82"/>
       <c r="O37" s="76">
         <f t="shared" si="8"/>
-        <v>360110.24</v>
+        <v>175647.24</v>
       </c>
       <c r="P37" s="91">
         <f t="shared" si="14"/>
-        <v>370913.24</v>
+        <v>180916.24</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="12"/>
         <v>0.24000000000000007</v>
       </c>
       <c r="R37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="83">
         <f t="shared" si="15"/>
         <v>25</v>
@@ -5520,15 +5419,14 @@
         <v>0.44</v>
       </c>
       <c r="F38" s="63">
-        <v>87050.25</v>
+        <v>-16625.75</v>
       </c>
       <c r="G38" s="63">
-        <f>16162+70888+(152000/3)</f>
-        <v>137716.66666666666</v>
+        <v>0</v>
       </c>
       <c r="H38" s="75">
         <f t="shared" si="1"/>
-        <v>-50666.416666666657</v>
+        <v>-16625.75</v>
       </c>
       <c r="I38" s="75">
         <f t="shared" si="4"/>
@@ -5553,11 +5451,11 @@
       <c r="N38" s="82"/>
       <c r="O38" s="76">
         <f t="shared" si="8"/>
-        <v>-16625.75</v>
+        <v>17415.25</v>
       </c>
       <c r="P38" s="91">
         <f t="shared" si="14"/>
-        <v>-17124.75</v>
+        <v>17937.25</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" si="12"/>
@@ -5567,7 +5465,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="83">
         <f t="shared" si="15"/>
         <v>26</v>
@@ -5583,18 +5481,19 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F39" s="63">
-        <v>39534.26</v>
-      </c>
-      <c r="G39" s="63">
-        <v>0</v>
+        <v>83271.259999999995</v>
+      </c>
+      <c r="G39" s="264">
+        <f>F39</f>
+        <v>83271.259999999995</v>
       </c>
       <c r="H39" s="75">
         <f t="shared" si="1"/>
-        <v>39534.26</v>
+        <v>0</v>
       </c>
       <c r="I39" s="75">
         <f t="shared" si="4"/>
-        <v>1186.0278000000001</v>
+        <v>0</v>
       </c>
       <c r="J39" s="82">
         <f t="shared" si="5"/>
@@ -5615,18 +5514,18 @@
       <c r="N39" s="82"/>
       <c r="O39" s="76">
         <f t="shared" si="8"/>
-        <v>83271.259999999995</v>
+        <v>42551.26</v>
       </c>
       <c r="P39" s="91">
         <f t="shared" si="14"/>
-        <v>85769.26</v>
+        <v>43828.26</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" si="12"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="83">
         <f t="shared" si="15"/>
         <v>27</v>
@@ -5642,11 +5541,11 @@
         <v>0.53</v>
       </c>
       <c r="F40" s="63">
-        <v>38097.269999999997</v>
-      </c>
-      <c r="G40" s="63">
+        <v>41004.269999999997</v>
+      </c>
+      <c r="G40" s="264">
         <f t="shared" ref="G40" si="16">F40</f>
-        <v>38097.269999999997</v>
+        <v>41004.269999999997</v>
       </c>
       <c r="H40" s="75">
         <f t="shared" si="1"/>
@@ -5686,66 +5585,68 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" s="83">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="265">
         <f t="shared" si="15"/>
         <v>28</v>
       </c>
-      <c r="B41" s="123" t="s">
+      <c r="B41" s="266" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="78" t="s">
+      <c r="C41" s="269" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="72" t="s">
+      <c r="D41" s="267" t="s">
         <v>154</v>
       </c>
-      <c r="E41" s="74">
+      <c r="E41" s="180">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F41" s="63">
-        <v>39971.279999999999</v>
-      </c>
-      <c r="G41" s="63"/>
-      <c r="H41" s="75">
+      <c r="F41" s="181">
+        <v>63606.28</v>
+      </c>
+      <c r="G41" s="268">
+        <v>42000</v>
+      </c>
+      <c r="H41" s="182">
         <f t="shared" si="1"/>
-        <v>39971.279999999999</v>
-      </c>
-      <c r="I41" s="75">
+        <v>21606.28</v>
+      </c>
+      <c r="I41" s="182">
         <f t="shared" si="4"/>
-        <v>1199.1383999999998</v>
-      </c>
-      <c r="J41" s="82">
+        <v>648.18839999999989</v>
+      </c>
+      <c r="J41" s="183">
         <f t="shared" si="5"/>
         <v>16898.591391999995</v>
       </c>
-      <c r="K41" s="82">
+      <c r="K41" s="183">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L41" s="82">
+      <c r="L41" s="183">
         <f t="shared" si="6"/>
         <v>530.18672900000001</v>
       </c>
-      <c r="M41" s="82">
+      <c r="M41" s="183">
         <f t="shared" si="7"/>
         <v>5007.1295309999996</v>
       </c>
-      <c r="N41" s="82"/>
-      <c r="O41" s="76">
+      <c r="N41" s="183"/>
+      <c r="O41" s="184">
         <f t="shared" si="8"/>
-        <v>63606.28</v>
-      </c>
-      <c r="P41" s="91">
+        <v>44690.28</v>
+      </c>
+      <c r="P41" s="185">
         <f t="shared" si="14"/>
-        <v>65514.28</v>
+        <v>46031.28</v>
       </c>
       <c r="Q41" s="40">
         <f t="shared" si="12"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="83">
         <f t="shared" si="15"/>
         <v>29</v>
@@ -5763,19 +5664,16 @@
         <v>0.08</v>
       </c>
       <c r="F42" s="63">
-        <v>5750.29</v>
-      </c>
-      <c r="G42" s="63">
-        <f t="shared" ref="G42:G43" si="17">F42</f>
-        <v>5750.29</v>
-      </c>
+        <v>6189.29</v>
+      </c>
+      <c r="G42" s="63"/>
       <c r="H42" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6189.29</v>
       </c>
       <c r="I42" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>185.67869999999999</v>
       </c>
       <c r="J42" s="82">
         <f t="shared" si="5"/>
@@ -5796,18 +5694,18 @@
       <c r="N42" s="82"/>
       <c r="O42" s="76">
         <f t="shared" si="8"/>
-        <v>6189.29</v>
+        <v>12564.29</v>
       </c>
       <c r="P42" s="91">
         <f t="shared" si="14"/>
-        <v>6375.29</v>
+        <v>12941.29</v>
       </c>
       <c r="Q42" s="40">
         <f t="shared" si="12"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="83">
         <f t="shared" si="15"/>
         <v>30</v>
@@ -5823,11 +5721,11 @@
         <v>0.08</v>
       </c>
       <c r="F43" s="63">
-        <v>5750.3</v>
-      </c>
-      <c r="G43" s="63">
-        <f t="shared" si="17"/>
-        <v>5750.3</v>
+        <v>6189.3</v>
+      </c>
+      <c r="G43" s="264">
+        <f t="shared" ref="G42:G43" si="17">F43</f>
+        <v>6189.3</v>
       </c>
       <c r="H43" s="75">
         <f t="shared" si="1"/>
@@ -5867,7 +5765,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="83">
         <f t="shared" si="15"/>
         <v>31</v>
@@ -5885,11 +5783,11 @@
         <v>0.08</v>
       </c>
       <c r="F44" s="63">
-        <v>5750.31</v>
-      </c>
-      <c r="G44" s="63">
+        <v>6189.31</v>
+      </c>
+      <c r="G44" s="264">
         <f>F44</f>
-        <v>5750.31</v>
+        <v>6189.31</v>
       </c>
       <c r="H44" s="75">
         <f t="shared" si="1"/>
@@ -5932,7 +5830,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="83">
         <f t="shared" si="15"/>
         <v>32</v>
@@ -5948,11 +5846,11 @@
         <v>0.08</v>
       </c>
       <c r="F45" s="63">
-        <v>5750.32</v>
-      </c>
-      <c r="G45" s="63">
+        <v>6189.32</v>
+      </c>
+      <c r="G45" s="264">
         <f>F45</f>
-        <v>5750.32</v>
+        <v>6189.32</v>
       </c>
       <c r="H45" s="75">
         <f t="shared" si="1"/>
@@ -5992,7 +5890,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="83">
         <f t="shared" si="15"/>
         <v>33</v>
@@ -6008,12 +5906,12 @@
         <v>0.08</v>
       </c>
       <c r="F46" s="63">
-        <v>29185.33</v>
+        <v>35375.33</v>
       </c>
       <c r="G46" s="63"/>
       <c r="H46" s="75">
         <f t="shared" si="1"/>
-        <v>29185.33</v>
+        <v>35375.33</v>
       </c>
       <c r="I46" s="75"/>
       <c r="J46" s="82">
@@ -6035,18 +5933,18 @@
       <c r="N46" s="82"/>
       <c r="O46" s="76">
         <f t="shared" si="8"/>
-        <v>35375.33</v>
+        <v>41565.33</v>
       </c>
       <c r="P46" s="91">
         <f t="shared" si="14"/>
-        <v>36436.33</v>
+        <v>42812.33</v>
       </c>
       <c r="Q46" s="40">
         <f t="shared" si="12"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="83">
         <f t="shared" si="15"/>
         <v>34</v>
@@ -6062,15 +5960,14 @@
         <v>0.08</v>
       </c>
       <c r="F47" s="63">
-        <v>5750.34</v>
-      </c>
-      <c r="G47" s="63">
-        <f>F47</f>
-        <v>5750.34</v>
+        <v>6189.34</v>
+      </c>
+      <c r="G47" s="264">
+        <v>6365.34</v>
       </c>
       <c r="H47" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-176</v>
       </c>
       <c r="I47" s="75">
         <f t="shared" si="4"/>
@@ -6095,18 +5992,18 @@
       <c r="N47" s="82"/>
       <c r="O47" s="76">
         <f t="shared" si="8"/>
-        <v>6189.34</v>
+        <v>6013.34</v>
       </c>
       <c r="P47" s="91">
         <f t="shared" si="14"/>
-        <v>6375.34</v>
+        <v>6193.34</v>
       </c>
       <c r="Q47" s="40">
         <f t="shared" si="12"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="114">
         <f t="shared" si="15"/>
         <v>35</v>
@@ -6122,19 +6019,16 @@
         <v>0.09</v>
       </c>
       <c r="F48" s="63">
-        <v>12404.35</v>
-      </c>
-      <c r="G48" s="63">
-        <f>12776.35</f>
-        <v>12776.35</v>
-      </c>
+        <v>6591.35</v>
+      </c>
+      <c r="G48" s="63"/>
       <c r="H48" s="118">
         <f t="shared" si="1"/>
-        <v>-372</v>
+        <v>6591.35</v>
       </c>
       <c r="I48" s="118">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>197.7405</v>
       </c>
       <c r="J48" s="82">
         <f t="shared" si="5"/>
@@ -6155,18 +6049,18 @@
       <c r="N48" s="119"/>
       <c r="O48" s="76">
         <f t="shared" si="8"/>
-        <v>6591.35</v>
+        <v>13752.35</v>
       </c>
       <c r="P48" s="91">
         <f t="shared" si="14"/>
-        <v>6789.35</v>
+        <v>14165.35</v>
       </c>
       <c r="Q48" s="40">
         <f t="shared" si="12"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="83">
         <f t="shared" si="15"/>
         <v>36</v>
@@ -6182,11 +6076,11 @@
         <v>0.79</v>
       </c>
       <c r="F49" s="63">
-        <v>56785.36</v>
-      </c>
-      <c r="G49" s="63">
+        <v>61119.360000000001</v>
+      </c>
+      <c r="G49" s="264">
         <f>F49</f>
-        <v>56785.36</v>
+        <v>61119.360000000001</v>
       </c>
       <c r="H49" s="75">
         <f t="shared" si="1"/>
@@ -6226,7 +6120,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="83">
         <f t="shared" si="15"/>
         <v>37</v>
@@ -6242,16 +6136,16 @@
         <v>1</v>
       </c>
       <c r="F50" s="63">
-        <v>385558.37</v>
+        <v>474490.37</v>
       </c>
       <c r="G50" s="63"/>
       <c r="H50" s="75">
         <f t="shared" si="1"/>
-        <v>385558.37</v>
+        <v>474490.37</v>
       </c>
       <c r="I50" s="75">
         <f t="shared" si="4"/>
-        <v>11566.751099999999</v>
+        <v>14234.711099999999</v>
       </c>
       <c r="J50" s="82">
         <f t="shared" si="5"/>
@@ -6272,18 +6166,18 @@
       <c r="N50" s="82"/>
       <c r="O50" s="76">
         <f t="shared" si="8"/>
-        <v>474490.37</v>
+        <v>566090.37</v>
       </c>
       <c r="P50" s="91">
         <f t="shared" si="14"/>
-        <v>488725.37</v>
+        <v>583073.37</v>
       </c>
       <c r="Q50" s="40">
         <f t="shared" si="12"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="83">
         <f t="shared" si="15"/>
         <v>38</v>
@@ -6299,11 +6193,11 @@
         <v>0.97</v>
       </c>
       <c r="F51" s="63">
-        <v>69724.38</v>
-      </c>
-      <c r="G51" s="63">
+        <v>75044.38</v>
+      </c>
+      <c r="G51" s="264">
         <f>F51</f>
-        <v>69724.38</v>
+        <v>75044.38</v>
       </c>
       <c r="H51" s="75">
         <f t="shared" si="1"/>
@@ -6343,7 +6237,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="83">
         <f t="shared" si="15"/>
         <v>39</v>
@@ -6359,19 +6253,16 @@
         <v>0.77</v>
       </c>
       <c r="F52" s="63">
-        <v>159501.39000000001</v>
-      </c>
-      <c r="G52" s="63">
-        <f>160000+(152000/3)</f>
-        <v>210666.66666666666</v>
-      </c>
+        <v>8406.39</v>
+      </c>
+      <c r="G52" s="63"/>
       <c r="H52" s="75">
         <f t="shared" si="1"/>
-        <v>-51165.276666666643</v>
+        <v>8406.39</v>
       </c>
       <c r="I52" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>252.19169999999997</v>
       </c>
       <c r="J52" s="82">
         <f t="shared" si="5"/>
@@ -6392,11 +6283,11 @@
       <c r="N52" s="82"/>
       <c r="O52" s="76">
         <f t="shared" si="8"/>
-        <v>8406.39</v>
+        <v>68230.39</v>
       </c>
       <c r="P52" s="91">
         <f t="shared" si="14"/>
-        <v>8658.39</v>
+        <v>70277.39</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" si="12"/>
@@ -6406,7 +6297,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="83">
         <f t="shared" si="15"/>
         <v>40</v>
@@ -6424,15 +6315,14 @@
         <v>0.77</v>
       </c>
       <c r="F53" s="63">
-        <v>55348.4</v>
-      </c>
-      <c r="G53" s="63">
-        <f>F53</f>
-        <v>55348.4</v>
+        <v>59571.4</v>
+      </c>
+      <c r="G53" s="264">
+        <v>61358.400000000001</v>
       </c>
       <c r="H53" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1787</v>
       </c>
       <c r="I53" s="75">
         <f t="shared" si="4"/>
@@ -6457,18 +6347,18 @@
       <c r="N53" s="82"/>
       <c r="O53" s="76">
         <f t="shared" si="8"/>
-        <v>59571.4</v>
+        <v>57784.4</v>
       </c>
       <c r="P53" s="91">
         <f t="shared" si="14"/>
-        <v>61358.400000000001</v>
+        <v>59518.400000000001</v>
       </c>
       <c r="Q53" s="40">
         <f t="shared" si="12"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="83">
         <f t="shared" si="15"/>
         <v>41</v>
@@ -6486,18 +6376,18 @@
         <v>0.81</v>
       </c>
       <c r="F54" s="63">
-        <v>111641.41</v>
+        <v>177656.41</v>
       </c>
       <c r="G54" s="63">
         <v>0</v>
       </c>
       <c r="H54" s="75">
         <f t="shared" si="1"/>
-        <v>111641.41</v>
+        <v>177656.41</v>
       </c>
       <c r="I54" s="75">
         <f t="shared" si="4"/>
-        <v>3349.2422999999999</v>
+        <v>5329.6922999999997</v>
       </c>
       <c r="J54" s="82">
         <f t="shared" si="5"/>
@@ -6518,18 +6408,18 @@
       <c r="N54" s="82"/>
       <c r="O54" s="76">
         <f t="shared" si="8"/>
-        <v>177656.41</v>
+        <v>245652.41</v>
       </c>
       <c r="P54" s="91">
         <f t="shared" si="14"/>
-        <v>182986.41</v>
+        <v>253022.41</v>
       </c>
       <c r="Q54" s="40">
         <f t="shared" si="12"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="83">
         <f t="shared" si="15"/>
         <v>42</v>
@@ -6547,11 +6437,11 @@
         <v>0.77</v>
       </c>
       <c r="F55" s="63">
-        <v>55348.42</v>
-      </c>
-      <c r="G55" s="63">
+        <v>59571.42</v>
+      </c>
+      <c r="G55" s="264">
         <f>F55</f>
-        <v>55348.42</v>
+        <v>59571.42</v>
       </c>
       <c r="H55" s="75">
         <f t="shared" si="1"/>
@@ -6591,7 +6481,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="83">
         <f t="shared" si="15"/>
         <v>43</v>
@@ -6607,16 +6497,16 @@
         <v>0.77</v>
       </c>
       <c r="F56" s="63">
-        <v>294804.43</v>
+        <v>363220.43</v>
       </c>
       <c r="G56" s="63"/>
       <c r="H56" s="75">
         <f t="shared" si="1"/>
-        <v>294804.43</v>
+        <v>363220.43</v>
       </c>
       <c r="I56" s="75">
         <f t="shared" si="4"/>
-        <v>8844.1328999999987</v>
+        <v>10896.6129</v>
       </c>
       <c r="J56" s="82">
         <f t="shared" si="5"/>
@@ -6637,18 +6527,18 @@
       <c r="N56" s="82"/>
       <c r="O56" s="76">
         <f t="shared" si="8"/>
-        <v>363220.43</v>
+        <v>433688.43</v>
       </c>
       <c r="P56" s="91">
         <f t="shared" si="14"/>
-        <v>374117.43</v>
+        <v>446699.43</v>
       </c>
       <c r="Q56" s="40">
         <f t="shared" si="12"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="83">
         <f t="shared" si="15"/>
         <v>44</v>
@@ -6664,16 +6554,16 @@
         <v>0.77</v>
       </c>
       <c r="F57" s="63">
-        <v>225547.44</v>
+        <v>291885.44</v>
       </c>
       <c r="G57" s="63"/>
       <c r="H57" s="75">
         <f t="shared" si="1"/>
-        <v>225547.44</v>
+        <v>291885.44</v>
       </c>
       <c r="I57" s="75">
         <f t="shared" si="4"/>
-        <v>6766.4232000000002</v>
+        <v>8756.5632000000005</v>
       </c>
       <c r="J57" s="82">
         <f t="shared" si="5"/>
@@ -6694,18 +6584,18 @@
       <c r="N57" s="82"/>
       <c r="O57" s="76">
         <f t="shared" si="8"/>
-        <v>291885.44</v>
+        <v>360213.44</v>
       </c>
       <c r="P57" s="91">
         <f t="shared" si="14"/>
-        <v>300642.44</v>
+        <v>371019.44</v>
       </c>
       <c r="Q57" s="40">
         <f t="shared" si="12"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="83">
         <f t="shared" si="15"/>
         <v>45</v>
@@ -6723,11 +6613,11 @@
         <v>0.77</v>
       </c>
       <c r="F58" s="63">
-        <v>55348.45</v>
-      </c>
-      <c r="G58" s="63">
+        <v>59571.45</v>
+      </c>
+      <c r="G58" s="264">
         <f t="shared" ref="G58" si="19">F58</f>
-        <v>55348.45</v>
+        <v>59571.45</v>
       </c>
       <c r="H58" s="75">
         <f t="shared" si="1"/>
@@ -6767,7 +6657,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="83">
         <f t="shared" si="15"/>
         <v>46</v>
@@ -6783,19 +6673,16 @@
         <v>0.86</v>
       </c>
       <c r="F59" s="63">
-        <v>61817.46</v>
-      </c>
-      <c r="G59" s="63">
-        <f>132705.46-70888+(152000/3)</f>
-        <v>112484.12666666665</v>
-      </c>
+        <v>15867.46</v>
+      </c>
+      <c r="G59" s="63"/>
       <c r="H59" s="75">
         <f t="shared" si="1"/>
-        <v>-50666.66666666665</v>
+        <v>15867.46</v>
       </c>
       <c r="I59" s="75">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>476.02379999999994</v>
       </c>
       <c r="J59" s="82">
         <f t="shared" si="5"/>
@@ -6816,11 +6703,11 @@
       <c r="N59" s="82"/>
       <c r="O59" s="76">
         <f t="shared" si="8"/>
-        <v>15867.46</v>
+        <v>82878.460000000006</v>
       </c>
       <c r="P59" s="91">
         <f t="shared" si="14"/>
-        <v>16343.46</v>
+        <v>85364.46</v>
       </c>
       <c r="Q59" s="40">
         <f t="shared" si="12"/>
@@ -6830,7 +6717,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="83"/>
       <c r="B60" s="123"/>
       <c r="C60" s="72"/>
@@ -6849,7 +6736,7 @@
       <c r="P60" s="91"/>
       <c r="Q60" s="40"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="84"/>
       <c r="B61" s="124"/>
       <c r="C61" s="85"/>
@@ -6860,19 +6747,19 @@
       </c>
       <c r="F61" s="87">
         <f t="shared" si="20"/>
-        <v>11042768.810000001</v>
+        <v>13013409.810000001</v>
       </c>
       <c r="G61" s="88">
         <f>SUM(G14:G60)</f>
-        <v>5966274.4000000004</v>
+        <v>10127798.860000001</v>
       </c>
       <c r="H61" s="88">
         <f t="shared" si="20"/>
-        <v>5076494.41</v>
+        <v>2885610.95</v>
       </c>
       <c r="I61" s="88">
         <f t="shared" si="20"/>
-        <v>156885.83609999999</v>
+        <v>90143.001900000003</v>
       </c>
       <c r="J61" s="89">
         <f t="shared" si="20"/>
@@ -6893,112 +6780,116 @@
       <c r="N61" s="90"/>
       <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>13013409.810000001</v>
+        <v>10755785.809999999</v>
       </c>
       <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>13403813.810000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11078459.809999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="64"/>
       <c r="D62" s="64"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="217" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
-      <c r="F64" s="217"/>
-      <c r="G64" s="217"/>
-      <c r="H64" s="217"/>
-      <c r="I64" s="217"/>
-      <c r="J64" s="217"/>
-      <c r="K64" s="217"/>
-      <c r="L64" s="217"/>
-      <c r="M64" s="217"/>
-      <c r="N64" s="217"/>
-      <c r="O64" s="217"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="217"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
-      <c r="F65" s="217"/>
-      <c r="G65" s="217"/>
-      <c r="H65" s="217"/>
-      <c r="I65" s="217"/>
-      <c r="J65" s="217"/>
-      <c r="K65" s="217"/>
-      <c r="L65" s="217"/>
-      <c r="M65" s="217"/>
-      <c r="N65" s="217"/>
-      <c r="O65" s="217"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="217"/>
-      <c r="D66" s="217"/>
-      <c r="E66" s="217"/>
-      <c r="F66" s="217"/>
-      <c r="G66" s="217"/>
-      <c r="H66" s="217"/>
-      <c r="I66" s="217"/>
-      <c r="J66" s="217"/>
-      <c r="K66" s="217"/>
-      <c r="L66" s="217"/>
-      <c r="M66" s="217"/>
-      <c r="N66" s="217"/>
-      <c r="O66" s="217"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="217"/>
-      <c r="D67" s="217"/>
-      <c r="E67" s="217"/>
-      <c r="F67" s="217"/>
-      <c r="G67" s="217"/>
-      <c r="H67" s="217"/>
-      <c r="I67" s="217"/>
-      <c r="J67" s="217"/>
-      <c r="K67" s="217"/>
-      <c r="L67" s="217"/>
-      <c r="M67" s="217"/>
-      <c r="N67" s="217"/>
-      <c r="O67" s="217"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="217"/>
-      <c r="D68" s="217"/>
-      <c r="E68" s="217"/>
-      <c r="F68" s="217"/>
-      <c r="G68" s="217"/>
-      <c r="H68" s="217"/>
-      <c r="I68" s="217"/>
-      <c r="J68" s="217"/>
-      <c r="K68" s="217"/>
-      <c r="L68" s="217"/>
-      <c r="M68" s="217"/>
-      <c r="N68" s="217"/>
-      <c r="O68" s="217"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="217"/>
-      <c r="D69" s="217"/>
-      <c r="E69" s="217"/>
-      <c r="F69" s="217"/>
-      <c r="G69" s="217"/>
-      <c r="H69" s="217"/>
-      <c r="I69" s="217"/>
-      <c r="J69" s="217"/>
-      <c r="K69" s="217"/>
-      <c r="L69" s="217"/>
-      <c r="M69" s="217"/>
-      <c r="N69" s="217"/>
-      <c r="O69" s="217"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="230"/>
+      <c r="G64" s="230"/>
+      <c r="H64" s="230"/>
+      <c r="I64" s="230"/>
+      <c r="J64" s="230"/>
+      <c r="K64" s="230"/>
+      <c r="L64" s="230"/>
+      <c r="M64" s="230"/>
+      <c r="N64" s="230"/>
+      <c r="O64" s="230"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="230"/>
+      <c r="D65" s="230"/>
+      <c r="E65" s="230"/>
+      <c r="F65" s="230"/>
+      <c r="G65" s="230"/>
+      <c r="H65" s="230"/>
+      <c r="I65" s="230"/>
+      <c r="J65" s="230"/>
+      <c r="K65" s="230"/>
+      <c r="L65" s="230"/>
+      <c r="M65" s="230"/>
+      <c r="N65" s="230"/>
+      <c r="O65" s="230"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="230"/>
+      <c r="D66" s="230"/>
+      <c r="E66" s="230"/>
+      <c r="F66" s="230"/>
+      <c r="G66" s="230"/>
+      <c r="H66" s="230"/>
+      <c r="I66" s="230"/>
+      <c r="J66" s="230"/>
+      <c r="K66" s="230"/>
+      <c r="L66" s="230"/>
+      <c r="M66" s="230"/>
+      <c r="N66" s="230"/>
+      <c r="O66" s="230"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="230"/>
+      <c r="D67" s="230"/>
+      <c r="E67" s="230"/>
+      <c r="F67" s="230"/>
+      <c r="G67" s="230"/>
+      <c r="H67" s="230"/>
+      <c r="I67" s="230"/>
+      <c r="J67" s="230"/>
+      <c r="K67" s="230"/>
+      <c r="L67" s="230"/>
+      <c r="M67" s="230"/>
+      <c r="N67" s="230"/>
+      <c r="O67" s="230"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="230"/>
+      <c r="D68" s="230"/>
+      <c r="E68" s="230"/>
+      <c r="F68" s="230"/>
+      <c r="G68" s="230"/>
+      <c r="H68" s="230"/>
+      <c r="I68" s="230"/>
+      <c r="J68" s="230"/>
+      <c r="K68" s="230"/>
+      <c r="L68" s="230"/>
+      <c r="M68" s="230"/>
+      <c r="N68" s="230"/>
+      <c r="O68" s="230"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
+      <c r="I69" s="230"/>
+      <c r="J69" s="230"/>
+      <c r="K69" s="230"/>
+      <c r="L69" s="230"/>
+      <c r="M69" s="230"/>
+      <c r="N69" s="230"/>
+      <c r="O69" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -7015,10 +6906,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7029,17 +6916,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C4:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="260" t="s">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="197" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="198"/>
       <c r="E4" t="s">
         <v>52</v>
       </c>
@@ -7048,11 +6935,11 @@
       </c>
       <c r="J4" s="112"/>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="260" t="s">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C5" s="197" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="261" t="s">
+      <c r="D5" s="198" t="s">
         <v>55</v>
       </c>
       <c r="E5" t="s">
@@ -7066,33 +6953,33 @@
       </c>
       <c r="J5" s="112"/>
     </row>
-    <row r="6" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" s="37" t="s">
         <v>57</v>
       </c>
       <c r="J6" s="112"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="254" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="255"/>
-      <c r="E7" s="255"/>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="255"/>
-      <c r="I7" s="255"/>
-      <c r="J7" s="256"/>
-    </row>
-    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="257"/>
-      <c r="D8" s="258"/>
-      <c r="E8" s="258"/>
-      <c r="F8" s="258"/>
-      <c r="G8" s="258"/>
-      <c r="H8" s="258"/>
-      <c r="I8" s="258"/>
-      <c r="J8" s="259"/>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="256" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="257"/>
+      <c r="E7" s="257"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="257"/>
+      <c r="I7" s="257"/>
+      <c r="J7" s="258"/>
+    </row>
+    <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="259"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="260"/>
+      <c r="G8" s="260"/>
+      <c r="H8" s="260"/>
+      <c r="I8" s="260"/>
+      <c r="J8" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFC4527-336A-4A0D-B594-102021A972CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD17D286-1F17-4330-AD99-82EBD5829BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$116</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="213">
   <si>
     <t>TOTAL</t>
   </si>
@@ -594,9 +594,6 @@
     <t>Rescate FCI</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Interes generados</t>
   </si>
   <si>
@@ -672,10 +669,19 @@
     <t>Transferencia 09/09 Vazquez Miguel Angel</t>
   </si>
   <si>
-    <t>Transferencia 15/09 Molina Soledad</t>
-  </si>
-  <si>
     <t>Deposito 23/09</t>
+  </si>
+  <si>
+    <t>Chade Monica  - Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Molina soledad</t>
+  </si>
+  <si>
+    <t>Transf 30/09</t>
+  </si>
+  <si>
+    <t>Ingresos correspondientes a caja SUM</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,14 +730,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -756,16 +754,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -857,8 +845,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1456,11 +1444,10 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1473,46 +1460,39 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="13" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="13" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1522,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1539,13 +1519,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="6" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1562,100 +1542,100 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="9" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="18" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="13" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="13" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="20" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="12" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="15" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="15" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="14" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1669,176 +1649,180 @@
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="13" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="13" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="13" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="13" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="11" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1858,16 +1842,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1906,16 +1884,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1924,10 +1896,16 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1939,18 +1917,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1969,17 +1935,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2383,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2400,80 +2367,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="202" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="196" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="203"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="197"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="206" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="198" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="207"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="199"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="208" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" s="208"/>
+      <c r="B8" s="200" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="200"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="208"/>
-      <c r="C10" s="208"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -2482,1132 +2449,1146 @@
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="209" t="s">
+      <c r="A13" s="248" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="248"/>
+      <c r="C13" s="248"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="209"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
+      <c r="A14" s="248"/>
+      <c r="B14" s="248"/>
+      <c r="C14" s="248"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
+      <c r="A15" s="248"/>
+      <c r="B15" s="248"/>
+      <c r="C15" s="248"/>
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A16" s="248"/>
+      <c r="B16" s="248"/>
+      <c r="C16" s="248"/>
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+    </row>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A18" s="249"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+    </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="16"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="96"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="88"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="210" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="211"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="189">
+      <c r="A22" s="191" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="192"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="177">
         <v>1448764.03</v>
       </c>
-      <c r="E22" s="97"/>
-      <c r="H22" s="20"/>
+      <c r="E22" s="89"/>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="204" t="s">
+      <c r="A23" s="191" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="205"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="189">
+      <c r="B23" s="192"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="177">
         <v>-315106.03000000003</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="38"/>
-      <c r="H23" s="20"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="30"/>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="204" t="s">
+      <c r="A24" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="205"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="187"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="38"/>
-      <c r="H24" s="20"/>
+      <c r="B24" s="192"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="30"/>
+      <c r="H24" s="12"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="145" t="s">
+      <c r="A25" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="145"/>
-      <c r="C25" s="145"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="98">
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="90">
         <f>SUM(D22:D24)</f>
         <v>1133658</v>
       </c>
-      <c r="F25" s="38"/>
+      <c r="F25" s="30"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="145"/>
-      <c r="C26" s="145"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="38"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="144"/>
-      <c r="B27" s="144"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="38"/>
+      <c r="A27" s="136"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="30"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="144"/>
-      <c r="B28" s="144"/>
-      <c r="C28" s="144"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="38"/>
+      <c r="A28" s="136"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="30"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="144"/>
-      <c r="B29" s="144"/>
-      <c r="C29" s="144"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="38"/>
+      <c r="A29" s="136"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="30"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="146"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="101">
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="93">
         <f>SUM(D27:D29)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="38"/>
+      <c r="F30" s="30"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="145"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="38"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="30"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="136" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="147"/>
-      <c r="C32" s="147"/>
-      <c r="D32" s="194">
+      <c r="B32" s="139"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="20">
         <v>718331.03</v>
       </c>
-      <c r="E32" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F32" s="38"/>
-      <c r="G32" s="48"/>
+      <c r="E32" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="30"/>
+      <c r="G32" s="40"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="136" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="144" t="s">
+      <c r="B33" s="136" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="139"/>
+      <c r="D33" s="20">
+        <v>182823.01</v>
+      </c>
+      <c r="E33" s="92" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="147"/>
-      <c r="D33" s="194">
-        <v>182823.01</v>
-      </c>
-      <c r="E33" s="100" t="s">
-        <v>205</v>
-      </c>
-      <c r="F33" s="38"/>
-      <c r="G33" s="48"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="144" t="s">
+      <c r="A34" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="147"/>
-      <c r="C34" s="147"/>
-      <c r="D34" s="194">
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="20">
         <v>65716.08</v>
       </c>
-      <c r="E34" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="F34" s="38"/>
-      <c r="G34" s="48"/>
+      <c r="E34" s="92" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="30"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="144" t="s">
+      <c r="A35" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="147"/>
-      <c r="C35" s="147"/>
-      <c r="D35" s="194">
+      <c r="B35" s="139"/>
+      <c r="C35" s="139"/>
+      <c r="D35" s="20">
         <v>7301.79</v>
       </c>
-      <c r="E35" s="100" t="str">
+      <c r="E35" s="92" t="str">
         <f>E34</f>
         <v>Debito 14/09</v>
       </c>
-      <c r="F35" s="38"/>
-      <c r="G35" s="40"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="32"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="147"/>
-      <c r="C36" s="147"/>
-      <c r="D36" s="194">
+      <c r="B36" s="139"/>
+      <c r="C36" s="139"/>
+      <c r="D36" s="20">
         <v>116816.78</v>
       </c>
-      <c r="E36" s="100" t="str">
+      <c r="E36" s="92" t="str">
         <f>E34</f>
         <v>Debito 14/09</v>
       </c>
-      <c r="F36" s="38"/>
+      <c r="F36" s="30"/>
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="145" t="s">
+      <c r="A37" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="145"/>
-      <c r="C37" s="145"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="32">
+      <c r="B37" s="137"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="24">
         <f>SUM(D32:D36)</f>
         <v>1090988.69</v>
       </c>
-      <c r="F37" s="38"/>
+      <c r="F37" s="30"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="145"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="38"/>
+      <c r="B38" s="137"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="212" t="s">
+      <c r="A39" s="201" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="213"/>
-      <c r="C39" s="148"/>
-      <c r="D39" s="262">
+      <c r="B39" s="202"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="250">
         <v>205033.71</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="38"/>
+      <c r="F39" s="30"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="212" t="s">
+      <c r="A40" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="213"/>
-      <c r="C40" s="148"/>
-      <c r="D40" s="262">
+      <c r="B40" s="202"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="250">
         <v>1426.62</v>
       </c>
-      <c r="E40" s="21" t="str">
+      <c r="E40" s="13" t="str">
         <f>E39</f>
         <v>Debito Autom.</v>
       </c>
-      <c r="F40" s="38"/>
+      <c r="F40" s="30"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="145" t="s">
+      <c r="A41" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="145"/>
-      <c r="C41" s="145"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="32">
+      <c r="B41" s="137"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="24">
         <f>SUM(D39:D40)</f>
         <v>206460.33</v>
       </c>
-      <c r="F41" s="38"/>
+      <c r="F41" s="30"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="146"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="102"/>
-      <c r="F42" s="38"/>
+      <c r="B42" s="138"/>
+      <c r="C42" s="138"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="30"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="33" t="s">
+      <c r="A43" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="192">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="176">
         <v>2001312.7</v>
       </c>
-      <c r="E43" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F43" s="38"/>
+      <c r="E43" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" s="30"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="33" t="s">
+      <c r="A44" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B44" s="149"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="188">
-        <v>0</v>
-      </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="38"/>
+      <c r="B44" s="141"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="176">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19"/>
+      <c r="F44" s="30"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="149"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="192">
+      <c r="B45" s="141"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="176">
         <v>883.29</v>
       </c>
-      <c r="E45" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F45" s="38"/>
+      <c r="E45" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="30"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="212" t="s">
+      <c r="A46" s="201" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="213"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="188">
-        <v>0</v>
-      </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="38"/>
+      <c r="B46" s="202"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="176">
+        <v>549962.86</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="F46" s="30"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="150" t="s">
+      <c r="A47" s="185" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="151"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="192">
+      <c r="B47" s="184"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="176">
         <v>42239.197999999997</v>
       </c>
-      <c r="E47" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F47" s="38"/>
+      <c r="E47" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="F47" s="30"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="145" t="s">
+      <c r="A48" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="145"/>
-      <c r="C48" s="145"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="103">
+      <c r="B48" s="137"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="95">
         <f>SUM(D43:D47)</f>
-        <v>2044435.1880000001</v>
-      </c>
-      <c r="F48" s="38"/>
+        <v>2594398.048</v>
+      </c>
+      <c r="F48" s="30"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="145"/>
-      <c r="C49" s="145"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="104"/>
-      <c r="F49" s="38"/>
+      <c r="B49" s="137"/>
+      <c r="C49" s="137"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="30"/>
     </row>
     <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="204" t="s">
-        <v>186</v>
-      </c>
-      <c r="B50" s="205"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="192">
+      <c r="A50" s="191" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="192"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="176">
         <v>298200</v>
       </c>
-      <c r="E50" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="F50" s="38"/>
+      <c r="E50" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="30"/>
     </row>
     <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="214" t="s">
+      <c r="A51" s="203" t="s">
+        <v>194</v>
+      </c>
+      <c r="B51" s="204"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="176">
+        <v>50000</v>
+      </c>
+      <c r="E51" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B51" s="215"/>
-      <c r="C51" s="144"/>
-      <c r="D51" s="192">
-        <v>50000</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="126"/>
+      <c r="F51" s="118"/>
     </row>
     <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="195" t="s">
+      <c r="A52" s="185" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="186"/>
+      <c r="C52" s="136"/>
+      <c r="D52" s="176">
+        <v>180000</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="196"/>
-      <c r="C52" s="144"/>
-      <c r="D52" s="192">
-        <v>180000</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="F52" s="126"/>
+      <c r="F52" s="118"/>
     </row>
     <row r="53" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="186" t="s">
-        <v>183</v>
-      </c>
-      <c r="B53" s="152"/>
-      <c r="C53" s="144"/>
-      <c r="D53" s="192">
+      <c r="A53" s="182" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="183"/>
+      <c r="C53" s="136"/>
+      <c r="D53" s="176">
         <v>117400</v>
       </c>
-      <c r="E53" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="F53" s="126"/>
+      <c r="E53" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="F53" s="118"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="32">
+      <c r="A54" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="24">
         <f>SUM(D50:D53)</f>
         <v>645600</v>
       </c>
-      <c r="F54" s="38"/>
+      <c r="F54" s="30"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="96"/>
-      <c r="F55" s="38"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="30"/>
     </row>
     <row r="56" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="204" t="s">
-        <v>201</v>
-      </c>
-      <c r="B56" s="205"/>
-      <c r="C56" s="144"/>
-      <c r="D56" s="193">
+      <c r="A56" s="191" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="192"/>
+      <c r="C56" s="136"/>
+      <c r="D56" s="251">
         <f>420000*2</f>
         <v>840000</v>
       </c>
-      <c r="E56" s="97" t="s">
-        <v>202</v>
-      </c>
-      <c r="F56" s="38"/>
+      <c r="E56" s="89" t="s">
+        <v>201</v>
+      </c>
+      <c r="F56" s="30"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="153" t="s">
+      <c r="A57" s="142" t="s">
+        <v>192</v>
+      </c>
+      <c r="B57" s="183"/>
+      <c r="C57" s="136"/>
+      <c r="D57" s="251">
+        <v>50000</v>
+      </c>
+      <c r="E57" s="89" t="s">
         <v>193</v>
       </c>
-      <c r="B57" s="152"/>
-      <c r="C57" s="144"/>
-      <c r="D57" s="193">
-        <v>50000</v>
-      </c>
-      <c r="E57" s="97" t="s">
-        <v>194</v>
-      </c>
-      <c r="F57" s="38"/>
+      <c r="F57" s="30"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="145" t="s">
+      <c r="A58" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="145"/>
-      <c r="C58" s="145"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="98">
+      <c r="B58" s="137"/>
+      <c r="C58" s="137"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="90">
         <f>SUM(D56:D57)</f>
         <v>890000</v>
       </c>
-      <c r="F58" s="38"/>
+      <c r="F58" s="30"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B59" s="154"/>
-      <c r="C59" s="145"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="38"/>
+      <c r="B59" s="143"/>
+      <c r="C59" s="137"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="30"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="33" t="s">
+      <c r="A60" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="155"/>
-      <c r="C60" s="155"/>
-      <c r="D60" s="263">
+      <c r="B60" s="144"/>
+      <c r="C60" s="144"/>
+      <c r="D60" s="145">
         <v>69000</v>
       </c>
-      <c r="E60" s="105"/>
-      <c r="F60" s="38"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="30"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="33" t="s">
+      <c r="A61" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="B61" s="155"/>
-      <c r="C61" s="155"/>
-      <c r="D61" s="156">
-        <f>114820.43-36</f>
-        <v>114784.43</v>
-      </c>
-      <c r="E61" s="105"/>
-      <c r="F61" s="38"/>
+      <c r="B61" s="144"/>
+      <c r="C61" s="144"/>
+      <c r="D61" s="145">
+        <f>145152.92-1438</f>
+        <v>143714.92000000001</v>
+      </c>
+      <c r="E61" s="97"/>
+      <c r="F61" s="30"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="157" t="s">
+      <c r="A62" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="157"/>
-      <c r="C62" s="157"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="32">
+      <c r="B62" s="146"/>
+      <c r="C62" s="146"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="24">
         <f>SUM(D60:D61)</f>
-        <v>183784.43</v>
-      </c>
-      <c r="F62" s="38"/>
+        <v>212714.92</v>
+      </c>
+      <c r="F62" s="30"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="33"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="38"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="30"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="158" t="s">
+      <c r="A64" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="B64" s="158"/>
-      <c r="C64" s="158"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="38"/>
+      <c r="B64" s="147"/>
+      <c r="C64" s="147"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="30"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="159"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="126"/>
+      <c r="A65" s="148"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="118"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="160" t="s">
+      <c r="A66" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="B66" s="161"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="42">
+      <c r="B66" s="150"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="34">
         <f>(SUM(E21:E64))</f>
-        <v>6194926.6380000003</v>
-      </c>
-      <c r="F66" s="162"/>
-      <c r="G66" s="40"/>
+        <v>6773819.9879999999</v>
+      </c>
+      <c r="F66" s="151"/>
+      <c r="G66" s="32"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="38"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="38"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="H68" s="44"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="H68" s="36"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="163" t="s">
+      <c r="A69" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="B69" s="164"/>
-      <c r="C69" s="165"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="38"/>
+      <c r="B69" s="153"/>
+      <c r="C69" s="154"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="30"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="217"/>
-      <c r="B70" s="218"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="166"/>
-      <c r="E70" s="113"/>
-      <c r="F70" s="38"/>
+      <c r="A70" s="194"/>
+      <c r="B70" s="195"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="155"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="30"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="38"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="38"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="30"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="167"/>
-      <c r="B72" s="168"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="38"/>
+      <c r="A72" s="156"/>
+      <c r="B72" s="157"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="30"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="169" t="s">
+      <c r="A73" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="B73" s="170"/>
-      <c r="C73" s="170"/>
-      <c r="D73" s="80"/>
-      <c r="E73" s="106">
+      <c r="B73" s="159"/>
+      <c r="C73" s="159"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="98">
         <f>SUM(D70:D72)</f>
         <v>0</v>
       </c>
-      <c r="F73" s="38"/>
+      <c r="F73" s="30"/>
     </row>
     <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="38"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="158" t="s">
+      <c r="A75" s="147" t="s">
         <v>18</v>
       </c>
-      <c r="B75" s="158"/>
-      <c r="C75" s="158"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="109">
-        <v>0</v>
-      </c>
-      <c r="F75" s="38"/>
+      <c r="B75" s="147"/>
+      <c r="C75" s="147"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="101">
+        <v>0</v>
+      </c>
+      <c r="F75" s="30"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="38"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="160" t="s">
+      <c r="A77" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="B77" s="161"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="42">
+      <c r="B77" s="150"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="34">
         <f>E73+E75</f>
         <v>0</v>
       </c>
-      <c r="F77" s="38"/>
+      <c r="F77" s="30"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="38"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="171" t="s">
+      <c r="A79" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="172">
+      <c r="B79" s="161">
         <f>E66</f>
-        <v>6194926.6380000003</v>
-      </c>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
+        <v>6773819.9879999999</v>
+      </c>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="171" t="s">
+      <c r="A80" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="172">
+      <c r="B80" s="161">
         <f>E66-E64</f>
-        <v>6194926.6380000003</v>
-      </c>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
+        <v>6773819.9879999999</v>
+      </c>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="171" t="s">
+      <c r="A81" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B81" s="172">
+      <c r="B81" s="161">
         <f>E77-E75</f>
         <v>0</v>
       </c>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
     </row>
     <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="171" t="s">
+      <c r="A82" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="B82" s="172">
+      <c r="B82" s="161">
         <f>E77</f>
         <v>0</v>
       </c>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="38"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="38"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="38"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="111" t="s">
+      <c r="A85" s="103" t="s">
         <v>178</v>
       </c>
-      <c r="B85" s="173">
-        <v>0</v>
-      </c>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
+      <c r="B85" s="162">
+        <v>0</v>
+      </c>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="148" t="s">
-        <v>185</v>
-      </c>
-      <c r="B86" s="174">
+      <c r="A86" s="140" t="s">
+        <v>184</v>
+      </c>
+      <c r="B86" s="163">
         <v>3191560.16</v>
       </c>
-      <c r="C86" s="38"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
     </row>
     <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="148" t="s">
-        <v>184</v>
-      </c>
-      <c r="B87" s="127"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38"/>
+      <c r="A87" s="140" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="119">
+        <f>B88-B86</f>
+        <v>53780.619999999646</v>
+      </c>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
     </row>
     <row r="88" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="175" t="s">
+      <c r="A88" s="164" t="s">
         <v>175</v>
       </c>
-      <c r="B88" s="176">
-        <v>3191560.16</v>
-      </c>
-      <c r="C88" s="38"/>
-      <c r="D88" s="38"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38"/>
+      <c r="B88" s="165">
+        <f>3245340.78</f>
+        <v>3245340.78</v>
+      </c>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
     </row>
     <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="177"/>
-      <c r="B89" s="178"/>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
+      <c r="A89" s="166"/>
+      <c r="B89" s="167"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
     </row>
     <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="177"/>
-      <c r="B90" s="178"/>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38"/>
+      <c r="A90" s="166"/>
+      <c r="B90" s="167"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
     </row>
     <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="111" t="s">
+      <c r="A91" s="103" t="s">
         <v>159</v>
       </c>
-      <c r="B91" s="51">
+      <c r="B91" s="43">
         <v>231400</v>
       </c>
-      <c r="C91" s="38"/>
-      <c r="D91" s="38"/>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
     </row>
     <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="148" t="s">
+      <c r="A92" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="B92" s="174">
-        <v>0</v>
-      </c>
-      <c r="C92" s="38"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38"/>
+      <c r="B92" s="163">
+        <v>43500</v>
+      </c>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
     </row>
     <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="148" t="s">
+      <c r="A93" s="140" t="s">
         <v>161</v>
       </c>
-      <c r="B93" s="127"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
+      <c r="B93" s="119"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
     </row>
     <row r="94" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="175" t="s">
+      <c r="A94" s="164" t="s">
         <v>175</v>
       </c>
-      <c r="B94" s="176">
+      <c r="B94" s="165">
         <f>SUM(B91:B93)</f>
-        <v>231400</v>
-      </c>
-      <c r="C94" s="38"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
+        <v>274900</v>
+      </c>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
     </row>
     <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="177"/>
-      <c r="B95" s="178"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
+      <c r="A95" s="166"/>
+      <c r="B95" s="167"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
     </row>
     <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="111" t="s">
+      <c r="A96" s="103" t="s">
         <v>162</v>
       </c>
-      <c r="B96" s="51">
+      <c r="B96" s="43">
         <v>58418</v>
       </c>
-      <c r="C96" s="38"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
     </row>
     <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="148" t="s">
+      <c r="A97" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="B97" s="174">
-        <v>0</v>
-      </c>
-      <c r="C97" s="38"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
+      <c r="B97" s="163">
+        <v>0</v>
+      </c>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
     </row>
     <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="148" t="s">
-        <v>192</v>
-      </c>
-      <c r="B98" s="128">
+      <c r="A98" s="140" t="s">
+        <v>191</v>
+      </c>
+      <c r="B98" s="120">
         <v>-8400</v>
       </c>
-      <c r="C98" s="38"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
     </row>
     <row r="99" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="175" t="s">
+      <c r="A99" s="164" t="s">
         <v>175</v>
       </c>
-      <c r="B99" s="176">
+      <c r="B99" s="165">
         <f>SUM(B96:B98)</f>
         <v>50018</v>
       </c>
-      <c r="C99" s="38"/>
-      <c r="D99" s="38"/>
-      <c r="E99" s="38"/>
-      <c r="F99" s="38"/>
-    </row>
-    <row r="100" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+    </row>
+    <row r="100" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="49"/>
-      <c r="D100" s="107"/>
-      <c r="E100" s="107"/>
-    </row>
-    <row r="101" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="111" t="s">
+      <c r="B100" s="40"/>
+      <c r="C100" s="41"/>
+      <c r="D100" s="99"/>
+      <c r="E100" s="99"/>
+    </row>
+    <row r="101" spans="1:6" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="103" t="s">
         <v>174</v>
       </c>
-      <c r="B101" s="51">
+      <c r="B101" s="43">
         <v>-7980.4499999999534</v>
       </c>
-      <c r="C101" s="49"/>
-      <c r="D101" s="108"/>
-      <c r="E101" s="108"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="100"/>
+      <c r="E101" s="100"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="24" t="s">
+      <c r="A102" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="128">
+      <c r="B102" s="120">
         <f>-B80-B81</f>
-        <v>-6194926.6380000003</v>
-      </c>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
+        <v>-6773819.9879999999</v>
+      </c>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="24" t="s">
+      <c r="A103" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B103" s="52">
-        <f>B117</f>
-        <v>971106</v>
-      </c>
-      <c r="D103" s="38"/>
-      <c r="E103" s="38"/>
-      <c r="F103" s="48"/>
+      <c r="B103" s="44">
+        <f>B116</f>
+        <v>687432</v>
+      </c>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="40"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="24" t="s">
+      <c r="A104" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B104" s="53">
+      <c r="B104" s="45">
         <f>PRORRATEO!G61</f>
-        <v>10127798.860000001</v>
-      </c>
-      <c r="D104" s="38"/>
-      <c r="E104" s="38"/>
-      <c r="F104" s="48"/>
-    </row>
-    <row r="105" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="24" t="s">
+        <v>10411472.860000003</v>
+      </c>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="40"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B105" s="252">
+        <f>-B92</f>
+        <v>-43500</v>
+      </c>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="40"/>
+    </row>
+    <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B105" s="190">
-        <v>0</v>
-      </c>
-      <c r="D105" s="126"/>
-      <c r="E105" s="38"/>
-      <c r="F105" s="48"/>
-    </row>
-    <row r="106" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="54" t="s">
+      <c r="B106" s="178">
+        <v>0</v>
+      </c>
+      <c r="D106" s="118"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="40"/>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B106" s="55">
-        <f>SUM(B101:C105)</f>
-        <v>4895997.7720000008</v>
-      </c>
-      <c r="D106" s="48"/>
-      <c r="E106" s="40"/>
-      <c r="F106" s="40"/>
-    </row>
-    <row r="107" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E107" s="40"/>
+      <c r="B107" s="47">
+        <f>SUM(B101:C106)</f>
+        <v>4273604.422000003</v>
+      </c>
+      <c r="D107" s="40"/>
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
     </row>
     <row r="108" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="129" t="s">
+      <c r="E108" s="32"/>
+    </row>
+    <row r="109" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="121" t="s">
         <v>163</v>
       </c>
-      <c r="B108" s="130">
-        <f>B106+B94</f>
-        <v>5127397.7720000008</v>
-      </c>
-      <c r="D108" s="40"/>
-      <c r="E108" s="40"/>
-    </row>
-    <row r="109" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="216" t="s">
+      <c r="B109" s="122">
+        <f>B107+B94</f>
+        <v>4548504.422000003</v>
+      </c>
+      <c r="D109" s="32"/>
+      <c r="E109" s="32"/>
+    </row>
+    <row r="110" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="193" t="s">
         <v>25</v>
       </c>
-      <c r="B110" s="216"/>
-      <c r="C110" s="216"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="216"/>
-      <c r="B111" s="216"/>
-      <c r="C111" s="216"/>
-    </row>
-    <row r="112" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="56" t="s">
+      <c r="B111" s="193"/>
+      <c r="C111" s="193"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="193"/>
+      <c r="B112" s="193"/>
+      <c r="C112" s="193"/>
+    </row>
+    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="B113" s="71">
+        <v>269232</v>
+      </c>
+      <c r="C113" s="49"/>
+      <c r="D113" s="35"/>
+    </row>
+    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="B112" s="79">
-        <v>269232</v>
-      </c>
-      <c r="C112" s="57"/>
-      <c r="D112" s="43"/>
-    </row>
-    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="B113" s="79">
-        <v>21606</v>
-      </c>
-      <c r="C113" s="57"/>
-      <c r="D113" s="43"/>
-    </row>
-    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="56" t="s">
-        <v>209</v>
-      </c>
-      <c r="B114" s="79">
-        <v>262068</v>
-      </c>
-      <c r="C114" s="57"/>
-      <c r="D114" s="43"/>
+      <c r="B114" s="71">
+        <v>376000</v>
+      </c>
+      <c r="C114" s="49"/>
+      <c r="D114" s="35"/>
     </row>
     <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="56" t="s">
-        <v>210</v>
-      </c>
-      <c r="B115" s="79">
-        <v>376000</v>
-      </c>
-      <c r="C115" s="57"/>
-      <c r="D115" s="43"/>
-    </row>
-    <row r="116" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="56" t="s">
-        <v>210</v>
-      </c>
-      <c r="B116" s="79">
+      <c r="A115" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="B115" s="71">
         <v>42200</v>
       </c>
-      <c r="C116" s="57"/>
-      <c r="D116" s="43"/>
+      <c r="C115" s="49"/>
+      <c r="D115" s="35"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="51">
+        <f>SUM(B113:B115)</f>
+        <v>687432</v>
+      </c>
+      <c r="C116" s="52"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B117" s="59">
-        <f>SUM(B112:B116)</f>
-        <v>971106</v>
-      </c>
-      <c r="C117" s="60"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M118" s="61"/>
+      <c r="M117" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A110:C111"/>
+    <mergeCell ref="A111:C112"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
@@ -3652,487 +3633,490 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66"/>
-      <c r="B1" s="120"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="219" t="str">
+      <c r="A1" s="58"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="211" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="219"/>
-      <c r="O1" s="219"/>
-      <c r="P1" s="220"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="212"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="132">
-        <f>D2-C4-C5</f>
-        <v>5827100.4799999995</v>
-      </c>
-      <c r="D2" s="191">
+      <c r="B2" s="113"/>
+      <c r="C2" s="124">
+        <v>4200000</v>
+      </c>
+      <c r="D2" s="179">
         <v>7736519.879999999</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="221"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="221"/>
-      <c r="M2" s="221"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="221"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="62"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="219"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
+      <c r="M2" s="213"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="213"/>
+      <c r="P2" s="214"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="132">
-        <v>0</v>
-      </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="221"/>
-      <c r="K3" s="221"/>
-      <c r="L3" s="221"/>
-      <c r="M3" s="221"/>
-      <c r="N3" s="221"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="222"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="40"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="124">
+        <v>0</v>
+      </c>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="213"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="213"/>
+      <c r="M3" s="213"/>
+      <c r="N3" s="213"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="214"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="121"/>
-      <c r="C4" s="132">
+      <c r="B4" s="113"/>
+      <c r="C4" s="124">
         <v>182823.01</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="221"/>
-      <c r="K4" s="221"/>
-      <c r="L4" s="221"/>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="222"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="40"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="123" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="122"/>
-      <c r="C5" s="133">
-        <v>1726596.39</v>
-      </c>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="223"/>
-      <c r="O5" s="223"/>
-      <c r="P5" s="224"/>
-      <c r="Q5" s="62"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="125">
+        <v>2001312.7</v>
+      </c>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="215"/>
+      <c r="L5" s="215"/>
+      <c r="M5" s="215"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="215"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="221" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="233"/>
-      <c r="G6" s="233"/>
-      <c r="H6" s="233"/>
-      <c r="I6" s="233"/>
-      <c r="J6" s="233"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="233"/>
-      <c r="O6" s="233"/>
-      <c r="P6" s="234"/>
-      <c r="Q6" s="62"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="223"/>
+      <c r="O6" s="223"/>
+      <c r="P6" s="224"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235"/>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="237"/>
-      <c r="Q7" s="62"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="226"/>
+      <c r="P7" s="227"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="235"/>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="237"/>
-      <c r="Q8" s="62"/>
+      <c r="A8" s="225"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="226"/>
+      <c r="O8" s="226"/>
+      <c r="P8" s="227"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="235"/>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="237"/>
-      <c r="Q9" s="62"/>
+      <c r="A9" s="225"/>
+      <c r="B9" s="226"/>
+      <c r="C9" s="226"/>
+      <c r="D9" s="226"/>
+      <c r="E9" s="226"/>
+      <c r="F9" s="226"/>
+      <c r="G9" s="226"/>
+      <c r="H9" s="226"/>
+      <c r="I9" s="226"/>
+      <c r="J9" s="226"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="226"/>
+      <c r="O9" s="226"/>
+      <c r="P9" s="227"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="238"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
-      <c r="N10" s="239"/>
-      <c r="O10" s="239"/>
-      <c r="P10" s="240"/>
+      <c r="A10" s="228"/>
+      <c r="B10" s="229"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="229"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="229"/>
+      <c r="I10" s="229"/>
+      <c r="J10" s="229"/>
+      <c r="K10" s="229"/>
+      <c r="L10" s="229"/>
+      <c r="M10" s="229"/>
+      <c r="N10" s="229"/>
+      <c r="O10" s="229"/>
+      <c r="P10" s="230"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="249" t="s">
+      <c r="A11" s="239" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="250"/>
-      <c r="C11" s="250"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="250"/>
-      <c r="G11" s="250"/>
-      <c r="H11" s="250"/>
-      <c r="I11" s="250"/>
-      <c r="J11" s="250"/>
-      <c r="K11" s="250"/>
-      <c r="L11" s="250"/>
-      <c r="M11" s="250"/>
-      <c r="N11" s="250"/>
-      <c r="O11" s="250"/>
-      <c r="P11" s="251"/>
+      <c r="B11" s="240"/>
+      <c r="C11" s="240"/>
+      <c r="D11" s="240"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="240"/>
+      <c r="G11" s="240"/>
+      <c r="H11" s="240"/>
+      <c r="I11" s="240"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="240"/>
+      <c r="L11" s="240"/>
+      <c r="M11" s="240"/>
+      <c r="N11" s="240"/>
+      <c r="O11" s="240"/>
+      <c r="P11" s="241"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="241" t="s">
+      <c r="A12" s="231" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="254" t="s">
+      <c r="B12" s="207" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="243" t="s">
+      <c r="C12" s="233" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="243" t="s">
+      <c r="D12" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="243" t="s">
+      <c r="E12" s="233" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="225" t="s">
+      <c r="F12" s="209" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="245" t="s">
+      <c r="G12" s="235" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="247" t="s">
+      <c r="H12" s="237" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="225" t="s">
+      <c r="I12" s="209" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="225" t="s">
+      <c r="J12" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="225" t="s">
+      <c r="K12" s="209" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="254" t="s">
+      <c r="L12" s="207" t="s">
         <v>169</v>
       </c>
-      <c r="M12" s="225" t="s">
+      <c r="M12" s="209" t="s">
         <v>166</v>
       </c>
-      <c r="N12" s="252" t="s">
+      <c r="N12" s="205" t="s">
         <v>179</v>
       </c>
-      <c r="O12" s="93" t="s">
+      <c r="O12" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="227" t="s">
+      <c r="P12" s="217" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="242"/>
-      <c r="B13" s="255"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="226"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="226"/>
-      <c r="J13" s="226"/>
-      <c r="K13" s="226"/>
-      <c r="L13" s="255"/>
-      <c r="M13" s="226"/>
-      <c r="N13" s="253"/>
-      <c r="O13" s="94" t="str">
+      <c r="A13" s="232"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="210"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="238"/>
+      <c r="I13" s="210"/>
+      <c r="J13" s="210"/>
+      <c r="K13" s="210"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="210"/>
+      <c r="N13" s="206"/>
+      <c r="O13" s="86" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P13" s="228"/>
+      <c r="P13" s="218"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83">
+      <c r="A14" s="75">
         <v>1</v>
       </c>
-      <c r="B14" s="123" t="s">
+      <c r="B14" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="74">
+      <c r="D14" s="64"/>
+      <c r="E14" s="66">
         <v>5.22</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="55">
         <v>403846.01</v>
       </c>
-      <c r="G14" s="264">
+      <c r="G14" s="55">
         <f t="shared" ref="G14" si="0">F14</f>
         <v>403846.01</v>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="67">
         <f t="shared" ref="H14:H59" si="1">F14-G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="75">
+      <c r="I14" s="67">
         <f>IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="82">
+      <c r="J14" s="74">
         <f>C$2*E14/100</f>
-        <v>304174.64505599992</v>
-      </c>
-      <c r="K14" s="82">
+        <v>219240</v>
+      </c>
+      <c r="K14" s="74">
         <f t="shared" ref="K14:K45" si="2">F$2*E14/100</f>
         <v>0</v>
       </c>
-      <c r="L14" s="82">
+      <c r="L14" s="74">
         <f>C$4*E14/100</f>
         <v>9543.3611220000003</v>
       </c>
-      <c r="M14" s="82">
+      <c r="M14" s="74">
         <f>C$5*E14/100</f>
-        <v>90128.331558000005</v>
-      </c>
-      <c r="N14" s="82"/>
-      <c r="O14" s="76">
+        <v>104468.52294</v>
+      </c>
+      <c r="N14" s="74"/>
+      <c r="O14" s="68">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
-        <v>403846.01</v>
-      </c>
-      <c r="P14" s="91">
+        <v>333252.01</v>
+      </c>
+      <c r="P14" s="83">
         <f t="shared" ref="P14:P34" si="3">ROUND(O14*3%,0) + O14</f>
-        <v>415961.01</v>
-      </c>
-      <c r="Q14" s="40">
+        <v>343250.01</v>
+      </c>
+      <c r="Q14" s="32">
         <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="265">
+      <c r="A15" s="187">
         <v>2</v>
       </c>
-      <c r="B15" s="266" t="s">
+      <c r="B15" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="267" t="s">
+      <c r="C15" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="267" t="s">
+      <c r="D15" s="189" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="180">
+      <c r="E15" s="169">
         <v>3.4</v>
       </c>
-      <c r="F15" s="181">
+      <c r="F15" s="170">
         <v>550069.02</v>
       </c>
-      <c r="G15" s="268">
-        <v>288000</v>
-      </c>
-      <c r="H15" s="182">
+      <c r="G15" s="170">
+        <f>262068+288000</f>
+        <v>550068</v>
+      </c>
+      <c r="H15" s="171">
         <f t="shared" si="1"/>
-        <v>262069.02000000002</v>
-      </c>
-      <c r="I15" s="182">
+        <v>1.0200000000186265</v>
+      </c>
+      <c r="I15" s="171">
         <f t="shared" ref="I15:I59" si="4">IF(H15&gt;0,H15*3%,0)</f>
-        <v>7862.0706</v>
-      </c>
-      <c r="J15" s="183">
+        <v>3.0600000000558791E-2</v>
+      </c>
+      <c r="J15" s="172">
         <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K15" s="183">
+        <v>142800</v>
+      </c>
+      <c r="K15" s="172">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="183">
+      <c r="L15" s="172">
         <f t="shared" ref="L15:L59" si="6">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M15" s="183">
+      <c r="M15" s="172">
         <f t="shared" ref="M15:M59" si="7">C$5*E15/100</f>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N15" s="183"/>
-      <c r="O15" s="184">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N15" s="172"/>
+      <c r="O15" s="173">
         <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>532973.02</v>
-      </c>
-      <c r="P15" s="185">
+        <v>217062.02</v>
+      </c>
+      <c r="P15" s="174">
         <f t="shared" si="3"/>
-        <v>548962.02</v>
-      </c>
-      <c r="Q15" s="40">
+        <v>223574.02</v>
+      </c>
+      <c r="Q15" s="32">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
+      <c r="R15" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="83">
+      <c r="A16" s="75">
         <v>3</v>
       </c>
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="74">
+      <c r="E16" s="66">
         <v>2.54</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="55">
         <v>196084.03</v>
       </c>
-      <c r="G16" s="264">
+      <c r="G16" s="55">
         <v>198000</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="67">
         <f t="shared" si="1"/>
         <v>-1915.9700000000012</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J16" s="82">
+      <c r="J16" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K16" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K16" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="82">
+      <c r="L16" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M16" s="82">
+      <c r="M16" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N16" s="82"/>
-      <c r="O16" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N16" s="74"/>
+      <c r="O16" s="68">
         <f t="shared" si="8"/>
-        <v>194592.03</v>
-      </c>
-      <c r="P16" s="91">
+        <v>160241.03</v>
+      </c>
+      <c r="P16" s="83">
         <f t="shared" si="3"/>
-        <v>200430.03</v>
-      </c>
-      <c r="Q16" s="40">
+        <v>165048.03</v>
+      </c>
+      <c r="Q16" s="32">
         <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
         <v>0.03</v>
       </c>
@@ -4141,64 +4125,62 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83">
+      <c r="A17" s="75">
         <v>4</v>
       </c>
-      <c r="B17" s="123" t="s">
+      <c r="B17" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="77" t="s">
+      <c r="D17" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="E17" s="74">
+      <c r="E17" s="66">
         <v>5.19</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="55">
         <v>432284.04</v>
       </c>
-      <c r="G17" s="264">
+      <c r="G17" s="55">
         <f>498075-G55-G44</f>
         <v>432314.27</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="67">
         <f t="shared" si="1"/>
         <v>-30.230000000039581</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="82">
+      <c r="J17" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K17" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K17" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="82">
+      <c r="L17" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M17" s="82">
+      <c r="M17" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N17" s="82">
-        <v>43500</v>
-      </c>
-      <c r="O17" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N17" s="74"/>
+      <c r="O17" s="68">
         <f t="shared" si="8"/>
-        <v>444995.04</v>
-      </c>
-      <c r="P17" s="91">
+        <v>331306.03999999998</v>
+      </c>
+      <c r="P17" s="83">
         <f t="shared" si="3"/>
-        <v>458345.04</v>
-      </c>
-      <c r="Q17" s="40">
+        <v>341245.04</v>
+      </c>
+      <c r="Q17" s="32">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
@@ -4207,1257 +4189,1257 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83">
+      <c r="A18" s="75">
         <v>5</v>
       </c>
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="115" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="77" t="s">
+      <c r="D18" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="66">
         <v>3.4</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="55">
         <v>514407.05</v>
       </c>
-      <c r="G18" s="264">
+      <c r="G18" s="55">
         <v>336377.05</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="67">
         <f t="shared" si="1"/>
         <v>178030</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="67">
         <f t="shared" si="4"/>
         <v>5340.9</v>
       </c>
-      <c r="J18" s="82">
+      <c r="J18" s="74">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K18" s="82">
+        <v>142800</v>
+      </c>
+      <c r="K18" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="82">
+      <c r="L18" s="74">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M18" s="82">
+      <c r="M18" s="74">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N18" s="82"/>
-      <c r="O18" s="76">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N18" s="74"/>
+      <c r="O18" s="68">
         <f t="shared" si="8"/>
-        <v>446413.05</v>
-      </c>
-      <c r="P18" s="91">
+        <v>400432.05</v>
+      </c>
+      <c r="P18" s="83">
         <f t="shared" si="3"/>
-        <v>459805.05</v>
-      </c>
-      <c r="Q18" s="40">
+        <v>412445.05</v>
+      </c>
+      <c r="Q18" s="32">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83">
+      <c r="A19" s="75">
         <v>6</v>
       </c>
-      <c r="B19" s="123" t="s">
+      <c r="B19" s="115" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="64" t="s">
         <v>177</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="66">
         <v>2.54</v>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="55">
         <v>196508.06</v>
       </c>
-      <c r="G19" s="264">
+      <c r="G19" s="55">
         <f>F19</f>
         <v>196508.06</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J19" s="82">
+      <c r="J19" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K19" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K19" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="82">
+      <c r="L19" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M19" s="82">
+      <c r="M19" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N19" s="82"/>
-      <c r="O19" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N19" s="74"/>
+      <c r="O19" s="68">
         <f t="shared" si="8"/>
-        <v>196508.06</v>
-      </c>
-      <c r="P19" s="91">
+        <v>162157.06</v>
+      </c>
+      <c r="P19" s="83">
         <f t="shared" si="3"/>
-        <v>202403.06</v>
-      </c>
-      <c r="Q19" s="40">
+        <v>167022.06</v>
+      </c>
+      <c r="Q19" s="32">
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83">
+      <c r="A20" s="75">
         <v>7</v>
       </c>
-      <c r="B20" s="123" t="s">
+      <c r="B20" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="74">
+      <c r="D20" s="64"/>
+      <c r="E20" s="66">
         <v>5.19</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="55">
         <v>401525.07</v>
       </c>
-      <c r="G20" s="264">
+      <c r="G20" s="55">
         <f t="shared" ref="G20:G25" si="10">F20</f>
         <v>401525.07</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J20" s="82">
+      <c r="J20" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K20" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K20" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="82">
+      <c r="L20" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M20" s="82">
+      <c r="M20" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N20" s="82"/>
-      <c r="O20" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N20" s="74"/>
+      <c r="O20" s="68">
         <f t="shared" si="8"/>
-        <v>401525.07</v>
-      </c>
-      <c r="P20" s="91">
+        <v>331337.07</v>
+      </c>
+      <c r="P20" s="83">
         <f t="shared" si="3"/>
-        <v>413571.07</v>
-      </c>
-      <c r="Q20" s="40">
+        <v>341277.07</v>
+      </c>
+      <c r="Q20" s="32">
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83">
+      <c r="A21" s="75">
         <v>8</v>
       </c>
-      <c r="B21" s="123" t="s">
+      <c r="B21" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="77"/>
-      <c r="E21" s="74">
+      <c r="D21" s="69"/>
+      <c r="E21" s="66">
         <v>3.4</v>
       </c>
-      <c r="F21" s="63">
+      <c r="F21" s="55">
         <v>263042.08</v>
       </c>
-      <c r="G21" s="264">
+      <c r="G21" s="55">
         <f t="shared" si="10"/>
         <v>263042.08</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J21" s="82">
+      <c r="J21" s="74">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K21" s="82">
+        <v>142800</v>
+      </c>
+      <c r="K21" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="82">
+      <c r="L21" s="74">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M21" s="82">
+      <c r="M21" s="74">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N21" s="82"/>
-      <c r="O21" s="76">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N21" s="74"/>
+      <c r="O21" s="68">
         <f t="shared" si="8"/>
-        <v>263042.08</v>
-      </c>
-      <c r="P21" s="91">
+        <v>217061.08</v>
+      </c>
+      <c r="P21" s="83">
         <f t="shared" si="3"/>
-        <v>270933.08</v>
-      </c>
-      <c r="Q21" s="40">
+        <v>223573.08</v>
+      </c>
+      <c r="Q21" s="32">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="265">
+      <c r="A22" s="187">
         <v>9</v>
       </c>
-      <c r="B22" s="266" t="s">
+      <c r="B22" s="188" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="267" t="s">
+      <c r="C22" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="179" t="s">
+      <c r="D22" s="168" t="s">
         <v>151</v>
       </c>
-      <c r="E22" s="180">
+      <c r="E22" s="169">
         <v>2.54</v>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="170">
         <v>196508.09</v>
       </c>
-      <c r="G22" s="268">
+      <c r="G22" s="170">
         <f t="shared" si="10"/>
         <v>196508.09</v>
       </c>
-      <c r="H22" s="182">
+      <c r="H22" s="171">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="182">
+      <c r="I22" s="171">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="183">
+      <c r="J22" s="172">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K22" s="183">
+        <v>106680</v>
+      </c>
+      <c r="K22" s="172">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="183">
+      <c r="L22" s="172">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M22" s="183">
+      <c r="M22" s="172">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N22" s="183"/>
-      <c r="O22" s="184">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N22" s="172"/>
+      <c r="O22" s="173">
         <f t="shared" si="8"/>
-        <v>196508.09</v>
-      </c>
-      <c r="P22" s="185">
+        <v>162157.09</v>
+      </c>
+      <c r="P22" s="174">
         <f t="shared" si="3"/>
-        <v>202403.09</v>
-      </c>
-      <c r="Q22" s="40">
+        <v>167022.09</v>
+      </c>
+      <c r="Q22" s="32">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="83">
+      <c r="A23" s="75">
         <v>10</v>
       </c>
-      <c r="B23" s="123" t="s">
+      <c r="B23" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="77"/>
-      <c r="E23" s="74">
+      <c r="D23" s="69"/>
+      <c r="E23" s="66">
         <v>5.19</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="55">
         <v>401525.1</v>
       </c>
-      <c r="G23" s="264">
+      <c r="G23" s="55">
         <f t="shared" si="10"/>
         <v>401525.1</v>
       </c>
-      <c r="H23" s="75">
+      <c r="H23" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J23" s="82">
+      <c r="J23" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K23" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K23" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="82">
+      <c r="L23" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M23" s="82">
+      <c r="M23" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N23" s="82"/>
-      <c r="O23" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N23" s="74"/>
+      <c r="O23" s="68">
         <f t="shared" si="8"/>
-        <v>401525.1</v>
-      </c>
-      <c r="P23" s="91">
+        <v>331337.09999999998</v>
+      </c>
+      <c r="P23" s="83">
         <f t="shared" si="3"/>
-        <v>413571.1</v>
-      </c>
-      <c r="Q23" s="40">
+        <v>341277.1</v>
+      </c>
+      <c r="Q23" s="32">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="83">
+      <c r="A24" s="75">
         <v>11</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="77" t="s">
+      <c r="D24" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="74">
+      <c r="E24" s="66">
         <v>3.4</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="55">
         <v>263042.11</v>
       </c>
-      <c r="G24" s="63"/>
-      <c r="H24" s="75">
+      <c r="G24" s="55"/>
+      <c r="H24" s="67">
         <f t="shared" si="1"/>
         <v>263042.11</v>
       </c>
-      <c r="I24" s="75">
+      <c r="I24" s="67">
         <f t="shared" si="4"/>
         <v>7891.2632999999996</v>
       </c>
-      <c r="J24" s="82">
+      <c r="J24" s="74">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K24" s="82">
+        <v>142800</v>
+      </c>
+      <c r="K24" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="82">
+      <c r="L24" s="74">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M24" s="82">
+      <c r="M24" s="74">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N24" s="82"/>
-      <c r="O24" s="76">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N24" s="74"/>
+      <c r="O24" s="68">
         <f t="shared" si="8"/>
-        <v>533975.11</v>
-      </c>
-      <c r="P24" s="91">
+        <v>487994.11</v>
+      </c>
+      <c r="P24" s="83">
         <f t="shared" si="3"/>
-        <v>549994.11</v>
-      </c>
-      <c r="Q24" s="40">
+        <v>502634.11</v>
+      </c>
+      <c r="Q24" s="32">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="83">
+      <c r="A25" s="75">
         <v>12</v>
       </c>
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="77" t="s">
+      <c r="D25" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="E25" s="74">
+      <c r="E25" s="66">
         <v>2.54</v>
       </c>
-      <c r="F25" s="63">
+      <c r="F25" s="55">
         <v>196508.12</v>
       </c>
-      <c r="G25" s="264">
+      <c r="G25" s="55">
         <f t="shared" si="10"/>
         <v>196508.12</v>
       </c>
-      <c r="H25" s="75">
+      <c r="H25" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="82">
+      <c r="J25" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K25" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K25" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="82">
+      <c r="L25" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M25" s="82">
+      <c r="M25" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N25" s="82"/>
-      <c r="O25" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="68">
         <f t="shared" si="8"/>
-        <v>196508.12</v>
-      </c>
-      <c r="P25" s="91">
+        <v>162157.12</v>
+      </c>
+      <c r="P25" s="83">
         <f t="shared" si="3"/>
-        <v>202403.12</v>
-      </c>
-      <c r="Q25" s="40">
+        <v>167022.12</v>
+      </c>
+      <c r="Q25" s="32">
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="83">
+      <c r="A26" s="75">
         <v>13</v>
       </c>
-      <c r="B26" s="123" t="s">
+      <c r="B26" s="115" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="D26" s="77"/>
-      <c r="E26" s="74">
+      <c r="D26" s="69"/>
+      <c r="E26" s="66">
         <v>5.19</v>
       </c>
-      <c r="F26" s="63">
+      <c r="F26" s="55">
         <v>401525.13</v>
       </c>
-      <c r="G26" s="264">
+      <c r="G26" s="55">
         <f>F26</f>
         <v>401525.13</v>
       </c>
-      <c r="H26" s="75">
+      <c r="H26" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="75">
+      <c r="I26" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="82">
+      <c r="J26" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K26" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K26" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="82">
+      <c r="L26" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="82">
+      <c r="M26" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N26" s="82"/>
-      <c r="O26" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N26" s="74"/>
+      <c r="O26" s="68">
         <f t="shared" si="8"/>
-        <v>401525.13</v>
-      </c>
-      <c r="P26" s="91">
+        <v>331337.13</v>
+      </c>
+      <c r="P26" s="83">
         <f t="shared" si="3"/>
-        <v>413571.13</v>
-      </c>
-      <c r="Q26" s="40">
+        <v>341277.13</v>
+      </c>
+      <c r="Q26" s="32">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="134">
+      <c r="A27" s="126">
         <v>14</v>
       </c>
-      <c r="B27" s="135" t="s">
+      <c r="B27" s="127" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="137"/>
-      <c r="E27" s="138">
+      <c r="D27" s="129"/>
+      <c r="E27" s="130">
         <v>3.4</v>
       </c>
-      <c r="F27" s="139">
+      <c r="F27" s="131">
         <v>253870.14</v>
       </c>
-      <c r="G27" s="270">
+      <c r="G27" s="131">
         <f>338781.52-G51</f>
         <v>263737.14</v>
       </c>
-      <c r="H27" s="140">
+      <c r="H27" s="132">
         <f t="shared" si="1"/>
         <v>-9867</v>
       </c>
-      <c r="I27" s="140">
+      <c r="I27" s="132">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="141">
+      <c r="J27" s="133">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K27" s="141">
+        <v>142800</v>
+      </c>
+      <c r="K27" s="133">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="141">
+      <c r="L27" s="133">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="141">
+      <c r="M27" s="133">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N27" s="141"/>
-      <c r="O27" s="142">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N27" s="133"/>
+      <c r="O27" s="134">
         <f t="shared" si="8"/>
-        <v>253175.14</v>
-      </c>
-      <c r="P27" s="143">
+        <v>207194.14</v>
+      </c>
+      <c r="P27" s="135">
         <f t="shared" si="3"/>
-        <v>260770.14</v>
-      </c>
-      <c r="Q27" s="40">
+        <v>213410.14</v>
+      </c>
+      <c r="Q27" s="32">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83">
+      <c r="A28" s="75">
         <v>15</v>
       </c>
-      <c r="B28" s="123" t="s">
+      <c r="B28" s="115" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="72" t="s">
+      <c r="D28" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="74">
+      <c r="E28" s="66">
         <v>2.54</v>
       </c>
-      <c r="F28" s="63">
+      <c r="F28" s="55">
         <v>196508.15</v>
       </c>
-      <c r="G28" s="264">
+      <c r="G28" s="55">
         <f t="shared" ref="G28" si="11">F28</f>
         <v>196508.15</v>
       </c>
-      <c r="H28" s="75">
+      <c r="H28" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J28" s="82">
+      <c r="J28" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K28" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K28" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="82">
+      <c r="L28" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M28" s="82">
+      <c r="M28" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N28" s="82"/>
-      <c r="O28" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N28" s="74"/>
+      <c r="O28" s="68">
         <f t="shared" si="8"/>
-        <v>196508.15</v>
-      </c>
-      <c r="P28" s="91">
+        <v>162157.15</v>
+      </c>
+      <c r="P28" s="83">
         <f t="shared" si="3"/>
-        <v>202403.15</v>
-      </c>
-      <c r="Q28" s="40">
+        <v>167022.15</v>
+      </c>
+      <c r="Q28" s="32">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83">
+      <c r="A29" s="75">
         <v>16</v>
       </c>
-      <c r="B29" s="123" t="s">
+      <c r="B29" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="72"/>
-      <c r="E29" s="74">
+      <c r="D29" s="64"/>
+      <c r="E29" s="66">
         <v>5.19</v>
       </c>
-      <c r="F29" s="63">
+      <c r="F29" s="55">
         <v>401525.16</v>
       </c>
-      <c r="G29" s="264">
+      <c r="G29" s="55">
         <f>F29</f>
         <v>401525.16</v>
       </c>
-      <c r="H29" s="75">
+      <c r="H29" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I29" s="75">
+      <c r="I29" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J29" s="82">
+      <c r="J29" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K29" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K29" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="82">
+      <c r="L29" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M29" s="82">
+      <c r="M29" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N29" s="82"/>
-      <c r="O29" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N29" s="74"/>
+      <c r="O29" s="68">
         <f t="shared" si="8"/>
-        <v>401525.16</v>
-      </c>
-      <c r="P29" s="91">
+        <v>331337.15999999997</v>
+      </c>
+      <c r="P29" s="83">
         <f t="shared" si="3"/>
-        <v>413571.16</v>
-      </c>
-      <c r="Q29" s="40">
+        <v>341277.16</v>
+      </c>
+      <c r="Q29" s="32">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="265">
+      <c r="A30" s="187">
         <v>17</v>
       </c>
-      <c r="B30" s="266" t="s">
+      <c r="B30" s="188" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="267" t="s">
+      <c r="C30" s="189" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="179" t="s">
+      <c r="D30" s="168" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="180">
+      <c r="E30" s="169">
         <v>3.4</v>
       </c>
-      <c r="F30" s="181">
+      <c r="F30" s="170">
         <v>262042.17</v>
       </c>
-      <c r="G30" s="268">
+      <c r="G30" s="170">
         <v>269904</v>
       </c>
-      <c r="H30" s="182">
+      <c r="H30" s="171">
         <f t="shared" si="1"/>
         <v>-7861.8299999999872</v>
       </c>
-      <c r="I30" s="182">
+      <c r="I30" s="171">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J30" s="183">
+      <c r="J30" s="172">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K30" s="183">
+        <v>142800</v>
+      </c>
+      <c r="K30" s="172">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="183">
+      <c r="L30" s="172">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M30" s="183">
+      <c r="M30" s="172">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N30" s="183"/>
-      <c r="O30" s="184">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N30" s="172"/>
+      <c r="O30" s="173">
         <f t="shared" si="8"/>
-        <v>255180.17</v>
-      </c>
-      <c r="P30" s="185">
+        <v>209199.17</v>
+      </c>
+      <c r="P30" s="174">
         <f t="shared" si="3"/>
-        <v>262835.17000000004</v>
-      </c>
-      <c r="Q30" s="40">
+        <v>215475.17</v>
+      </c>
+      <c r="Q30" s="32">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="199">
+      <c r="A31" s="75">
         <v>18</v>
       </c>
-      <c r="B31" s="200" t="s">
+      <c r="B31" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="201" t="s">
+      <c r="C31" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="74">
+      <c r="D31" s="65"/>
+      <c r="E31" s="66">
         <v>2.54</v>
       </c>
-      <c r="F31" s="63">
+      <c r="F31" s="55">
         <v>2098557.1800000002</v>
       </c>
-      <c r="G31" s="264">
+      <c r="G31" s="55">
         <f>251908+923325</f>
         <v>1175233</v>
       </c>
-      <c r="H31" s="75">
+      <c r="H31" s="67">
         <f t="shared" si="1"/>
         <v>923324.18000000017</v>
       </c>
-      <c r="I31" s="75">
+      <c r="I31" s="67">
         <f t="shared" si="4"/>
         <v>27699.725400000003</v>
       </c>
-      <c r="J31" s="82">
+      <c r="J31" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K31" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K31" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="82">
+      <c r="L31" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M31" s="82">
+      <c r="M31" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N31" s="82"/>
-      <c r="O31" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N31" s="74"/>
+      <c r="O31" s="68">
         <f t="shared" si="8"/>
-        <v>1147532.18</v>
-      </c>
-      <c r="P31" s="91">
+        <v>1113181.18</v>
+      </c>
+      <c r="P31" s="83">
         <f t="shared" si="3"/>
-        <v>1181958.18</v>
-      </c>
-      <c r="Q31" s="40">
+        <v>1146576.18</v>
+      </c>
+      <c r="Q31" s="32">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="83">
+      <c r="A32" s="75">
         <v>19</v>
       </c>
-      <c r="B32" s="123" t="s">
+      <c r="B32" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="77"/>
-      <c r="E32" s="74">
+      <c r="D32" s="69"/>
+      <c r="E32" s="66">
         <v>5.19</v>
       </c>
-      <c r="F32" s="63">
+      <c r="F32" s="55">
         <v>2043868.19</v>
       </c>
-      <c r="G32" s="264">
-        <f>2141620.52</f>
-        <v>2141620.52</v>
-      </c>
-      <c r="H32" s="75">
+      <c r="G32" s="55">
+        <f>2141620.52-G46</f>
+        <v>2106245.19</v>
+      </c>
+      <c r="H32" s="67">
         <f t="shared" si="1"/>
-        <v>-97752.330000000075</v>
-      </c>
-      <c r="I32" s="75">
+        <v>-62377</v>
+      </c>
+      <c r="I32" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J32" s="82">
+      <c r="J32" s="74">
         <f t="shared" si="5"/>
-        <v>302426.51491199998</v>
-      </c>
-      <c r="K32" s="82">
+        <v>217980</v>
+      </c>
+      <c r="K32" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="82">
+      <c r="L32" s="74">
         <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M32" s="82">
+      <c r="M32" s="74">
         <f t="shared" si="7"/>
-        <v>89610.352641000005</v>
-      </c>
-      <c r="N32" s="82"/>
-      <c r="O32" s="76">
+        <v>103868.12913</v>
+      </c>
+      <c r="N32" s="74"/>
+      <c r="O32" s="68">
         <f t="shared" si="8"/>
-        <v>303773.19</v>
-      </c>
-      <c r="P32" s="91">
+        <v>268960.19</v>
+      </c>
+      <c r="P32" s="83">
         <f t="shared" si="3"/>
-        <v>312886.19</v>
-      </c>
-      <c r="Q32" s="40">
+        <v>277029.19</v>
+      </c>
+      <c r="Q32" s="32">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="83">
+      <c r="A33" s="75">
         <v>20</v>
       </c>
-      <c r="B33" s="123" t="s">
+      <c r="B33" s="115" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="74">
+      <c r="D33" s="69"/>
+      <c r="E33" s="66">
         <v>3.4</v>
       </c>
-      <c r="F33" s="63">
+      <c r="F33" s="55">
         <v>257050.2</v>
       </c>
-      <c r="G33" s="264">
+      <c r="G33" s="55">
         <f>264762.2</f>
         <v>264762.2</v>
       </c>
-      <c r="H33" s="75">
+      <c r="H33" s="67">
         <f t="shared" si="1"/>
         <v>-7712</v>
       </c>
-      <c r="I33" s="75"/>
-      <c r="J33" s="82">
+      <c r="I33" s="67"/>
+      <c r="J33" s="74">
         <f t="shared" si="5"/>
-        <v>198121.41631999999</v>
-      </c>
-      <c r="K33" s="82">
+        <v>142800</v>
+      </c>
+      <c r="K33" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="82">
+      <c r="L33" s="74">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="82">
+      <c r="M33" s="74">
         <f t="shared" si="7"/>
-        <v>58704.277259999995</v>
-      </c>
-      <c r="N33" s="82"/>
-      <c r="O33" s="76">
+        <v>68044.631800000003</v>
+      </c>
+      <c r="N33" s="74"/>
+      <c r="O33" s="68">
         <f t="shared" si="8"/>
-        <v>255330.2</v>
-      </c>
-      <c r="P33" s="91">
+        <v>209349.2</v>
+      </c>
+      <c r="P33" s="83">
         <f t="shared" si="3"/>
-        <v>262990.2</v>
-      </c>
-      <c r="Q33" s="40">
+        <v>215629.2</v>
+      </c>
+      <c r="Q33" s="32">
         <f t="shared" ref="Q33:Q59" si="12">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="83">
+      <c r="A34" s="75">
         <v>21</v>
       </c>
-      <c r="B34" s="123" t="s">
+      <c r="B34" s="115" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="78" t="s">
+      <c r="C34" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="D34" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="E34" s="74">
+      <c r="E34" s="66">
         <v>2.54</v>
       </c>
-      <c r="F34" s="63">
+      <c r="F34" s="55">
         <v>196508.21</v>
       </c>
-      <c r="G34" s="264">
+      <c r="G34" s="55">
         <f t="shared" ref="G34:G35" si="13">F34</f>
         <v>196508.21</v>
       </c>
-      <c r="H34" s="75">
+      <c r="H34" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="75">
+      <c r="I34" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="82">
+      <c r="J34" s="74">
         <f t="shared" si="5"/>
-        <v>148008.35219199999</v>
-      </c>
-      <c r="K34" s="82">
+        <v>106680</v>
+      </c>
+      <c r="K34" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="82">
+      <c r="L34" s="74">
         <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M34" s="82">
+      <c r="M34" s="74">
         <f t="shared" si="7"/>
-        <v>43855.548305999997</v>
-      </c>
-      <c r="N34" s="82"/>
-      <c r="O34" s="76">
+        <v>50833.342580000004</v>
+      </c>
+      <c r="N34" s="74"/>
+      <c r="O34" s="68">
         <f t="shared" si="8"/>
-        <v>196508.21</v>
-      </c>
-      <c r="P34" s="91">
+        <v>162157.21</v>
+      </c>
+      <c r="P34" s="83">
         <f t="shared" si="3"/>
-        <v>202403.21</v>
-      </c>
-      <c r="Q34" s="40">
+        <v>167022.21</v>
+      </c>
+      <c r="Q34" s="32">
         <f t="shared" si="12"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="75">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="123" t="s">
+      <c r="B35" s="115" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="78" t="s">
+      <c r="C35" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="D35" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="E35" s="74">
+      <c r="E35" s="66">
         <v>4.9400000000000004</v>
       </c>
-      <c r="F35" s="63">
+      <c r="F35" s="55">
         <v>382184.22</v>
       </c>
-      <c r="G35" s="264">
+      <c r="G35" s="55">
         <f t="shared" si="13"/>
         <v>382184.22</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J35" s="82">
+      <c r="J35" s="74">
         <f t="shared" si="5"/>
-        <v>287858.76371199999</v>
-      </c>
-      <c r="K35" s="82">
+        <v>207480</v>
+      </c>
+      <c r="K35" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="82">
+      <c r="L35" s="74">
         <f t="shared" si="6"/>
         <v>9031.4566940000004</v>
       </c>
-      <c r="M35" s="82">
+      <c r="M35" s="74">
         <f t="shared" si="7"/>
-        <v>85293.861665999997</v>
-      </c>
-      <c r="N35" s="82"/>
-      <c r="O35" s="76">
+        <v>98864.847379999992</v>
+      </c>
+      <c r="N35" s="74"/>
+      <c r="O35" s="68">
         <f t="shared" si="8"/>
-        <v>382184.22</v>
-      </c>
-      <c r="P35" s="91">
+        <v>315376.21999999997</v>
+      </c>
+      <c r="P35" s="83">
         <f t="shared" ref="P35:P59" si="14">ROUND(O35*3%,0) + O35</f>
-        <v>393650.22</v>
-      </c>
-      <c r="Q35" s="40">
+        <v>324837.21999999997</v>
+      </c>
+      <c r="Q35" s="32">
         <f t="shared" si="12"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="83">
+      <c r="A36" s="75">
         <f t="shared" ref="A36:A59" si="15">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="78" t="s">
+      <c r="C36" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="D36" s="77" t="s">
+      <c r="D36" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="E36" s="74">
+      <c r="E36" s="66">
         <v>3.28</v>
       </c>
-      <c r="F36" s="63">
+      <c r="F36" s="55">
         <v>253738.23</v>
       </c>
-      <c r="G36" s="264">
+      <c r="G36" s="55">
         <v>241350.23</v>
       </c>
-      <c r="H36" s="75">
+      <c r="H36" s="67">
         <f t="shared" si="1"/>
         <v>12388</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="67">
         <f t="shared" si="4"/>
         <v>371.64</v>
       </c>
-      <c r="J36" s="82">
+      <c r="J36" s="74">
         <f t="shared" si="5"/>
-        <v>191128.89574399998</v>
-      </c>
-      <c r="K36" s="82">
+        <v>137760</v>
+      </c>
+      <c r="K36" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="82">
+      <c r="L36" s="74">
         <f t="shared" si="6"/>
         <v>5996.594728</v>
       </c>
-      <c r="M36" s="82">
+      <c r="M36" s="74">
         <f t="shared" si="7"/>
-        <v>56632.361591999994</v>
-      </c>
-      <c r="N36" s="82"/>
-      <c r="O36" s="76">
+        <v>65643.056559999997</v>
+      </c>
+      <c r="N36" s="74"/>
+      <c r="O36" s="68">
         <f t="shared" si="8"/>
-        <v>266517.23</v>
-      </c>
-      <c r="P36" s="91">
+        <v>222159.23</v>
+      </c>
+      <c r="P36" s="83">
         <f t="shared" si="14"/>
-        <v>274513.23</v>
-      </c>
-      <c r="Q36" s="40">
+        <v>228824.23</v>
+      </c>
+      <c r="Q36" s="32">
         <f t="shared" si="12"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="83">
+      <c r="A37" s="75">
         <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="B37" s="123" t="s">
+      <c r="B37" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="78" t="s">
+      <c r="C37" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="74">
+      <c r="D37" s="69"/>
+      <c r="E37" s="66">
         <v>2.41</v>
       </c>
-      <c r="F37" s="63">
+      <c r="F37" s="55">
         <v>360110.24</v>
       </c>
-      <c r="G37" s="264">
+      <c r="G37" s="55">
         <f>197253+173660.24</f>
         <v>370913.24</v>
       </c>
-      <c r="H37" s="75">
+      <c r="H37" s="67">
         <f t="shared" si="1"/>
         <v>-10803</v>
       </c>
-      <c r="I37" s="75">
+      <c r="I37" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J37" s="82">
+      <c r="J37" s="74">
         <f t="shared" si="5"/>
-        <v>140433.121568</v>
-      </c>
-      <c r="K37" s="82">
+        <v>101220</v>
+      </c>
+      <c r="K37" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L37" s="82">
+      <c r="L37" s="74">
         <f t="shared" si="6"/>
         <v>4406.034541</v>
       </c>
-      <c r="M37" s="82">
+      <c r="M37" s="74">
         <f t="shared" si="7"/>
-        <v>41610.972998999998</v>
-      </c>
-      <c r="N37" s="82"/>
-      <c r="O37" s="76">
+        <v>48231.63607</v>
+      </c>
+      <c r="N37" s="74"/>
+      <c r="O37" s="68">
         <f t="shared" si="8"/>
-        <v>175647.24</v>
-      </c>
-      <c r="P37" s="91">
+        <v>143055.24</v>
+      </c>
+      <c r="P37" s="83">
         <f t="shared" si="14"/>
-        <v>180916.24</v>
-      </c>
-      <c r="Q37" s="40">
+        <v>147347.24</v>
+      </c>
+      <c r="Q37" s="32">
         <f t="shared" si="12"/>
         <v>0.24000000000000007</v>
       </c>
       <c r="R37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="83">
+      <c r="A38" s="75">
         <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="B38" s="123" t="s">
+      <c r="B38" s="115" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="74">
+      <c r="D38" s="69"/>
+      <c r="E38" s="66">
         <v>0.44</v>
       </c>
-      <c r="F38" s="63">
+      <c r="F38" s="55">
         <v>-16625.75</v>
       </c>
-      <c r="G38" s="63">
-        <v>0</v>
-      </c>
-      <c r="H38" s="75">
+      <c r="G38" s="55">
+        <v>0</v>
+      </c>
+      <c r="H38" s="67">
         <f t="shared" si="1"/>
         <v>-16625.75</v>
       </c>
-      <c r="I38" s="75">
+      <c r="I38" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J38" s="82">
+      <c r="J38" s="74">
         <f t="shared" si="5"/>
-        <v>25639.242111999996</v>
-      </c>
-      <c r="K38" s="82">
+        <v>18480</v>
+      </c>
+      <c r="K38" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L38" s="82">
+      <c r="L38" s="74">
         <f t="shared" si="6"/>
         <v>804.421244</v>
       </c>
-      <c r="M38" s="82">
+      <c r="M38" s="74">
         <f t="shared" si="7"/>
-        <v>7597.0241159999996</v>
-      </c>
-      <c r="N38" s="82"/>
-      <c r="O38" s="76">
+        <v>8805.7758799999992</v>
+      </c>
+      <c r="N38" s="74"/>
+      <c r="O38" s="68">
         <f t="shared" si="8"/>
-        <v>17415.25</v>
-      </c>
-      <c r="P38" s="91">
+        <v>11464.25</v>
+      </c>
+      <c r="P38" s="83">
         <f t="shared" si="14"/>
-        <v>17937.25</v>
-      </c>
-      <c r="Q38" s="40">
+        <v>11808.25</v>
+      </c>
+      <c r="Q38" s="32">
         <f t="shared" si="12"/>
         <v>0.25000000000000006</v>
       </c>
@@ -5466,363 +5448,367 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="83">
+      <c r="A39" s="75">
         <f t="shared" si="15"/>
         <v>26</v>
       </c>
-      <c r="B39" s="123" t="s">
+      <c r="B39" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="78" t="s">
+      <c r="C39" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="77"/>
-      <c r="E39" s="74">
+      <c r="D39" s="69"/>
+      <c r="E39" s="66">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F39" s="63">
+      <c r="F39" s="55">
         <v>83271.259999999995</v>
       </c>
-      <c r="G39" s="264">
+      <c r="G39" s="55">
         <f>F39</f>
         <v>83271.259999999995</v>
       </c>
-      <c r="H39" s="75">
+      <c r="H39" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I39" s="75">
+      <c r="I39" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J39" s="82">
+      <c r="J39" s="74">
         <f t="shared" si="5"/>
-        <v>32049.052639999998</v>
-      </c>
-      <c r="K39" s="82">
+        <v>23100</v>
+      </c>
+      <c r="K39" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L39" s="82">
+      <c r="L39" s="74">
         <f t="shared" si="6"/>
         <v>1005.526555</v>
       </c>
-      <c r="M39" s="82">
+      <c r="M39" s="74">
         <f t="shared" si="7"/>
-        <v>9496.2801450000006</v>
-      </c>
-      <c r="N39" s="82"/>
-      <c r="O39" s="76">
+        <v>11007.219850000001</v>
+      </c>
+      <c r="N39" s="74"/>
+      <c r="O39" s="68">
         <f t="shared" si="8"/>
-        <v>42551.26</v>
-      </c>
-      <c r="P39" s="91">
+        <v>35113.26</v>
+      </c>
+      <c r="P39" s="83">
         <f t="shared" si="14"/>
-        <v>43828.26</v>
-      </c>
-      <c r="Q39" s="40">
+        <v>36166.26</v>
+      </c>
+      <c r="Q39" s="32">
         <f t="shared" si="12"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="83">
+      <c r="A40" s="75">
         <f t="shared" si="15"/>
         <v>27</v>
       </c>
-      <c r="B40" s="123" t="s">
+      <c r="B40" s="115" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="78" t="s">
+      <c r="C40" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="74">
+      <c r="D40" s="69"/>
+      <c r="E40" s="66">
         <v>0.53</v>
       </c>
-      <c r="F40" s="63">
+      <c r="F40" s="55">
         <v>41004.269999999997</v>
       </c>
-      <c r="G40" s="264">
+      <c r="G40" s="55">
         <f t="shared" ref="G40" si="16">F40</f>
         <v>41004.269999999997</v>
       </c>
-      <c r="H40" s="75">
+      <c r="H40" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="75">
+      <c r="I40" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J40" s="82">
+      <c r="J40" s="74">
         <f t="shared" si="5"/>
-        <v>30883.632544</v>
-      </c>
-      <c r="K40" s="82">
+        <v>22260</v>
+      </c>
+      <c r="K40" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L40" s="82">
+      <c r="L40" s="74">
         <f t="shared" si="6"/>
         <v>968.96195300000011</v>
       </c>
-      <c r="M40" s="82">
+      <c r="M40" s="74">
         <f t="shared" si="7"/>
-        <v>9150.9608669999998</v>
-      </c>
-      <c r="N40" s="82"/>
-      <c r="O40" s="76">
+        <v>10606.95731</v>
+      </c>
+      <c r="N40" s="74"/>
+      <c r="O40" s="68">
         <f t="shared" si="8"/>
-        <v>41004.269999999997</v>
-      </c>
-      <c r="P40" s="91">
+        <v>33836.269999999997</v>
+      </c>
+      <c r="P40" s="83">
         <f t="shared" si="14"/>
-        <v>42234.27</v>
-      </c>
-      <c r="Q40" s="40">
+        <v>34851.269999999997</v>
+      </c>
+      <c r="Q40" s="32">
         <f t="shared" si="12"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="265">
+      <c r="A41" s="187">
         <f t="shared" si="15"/>
         <v>28</v>
       </c>
-      <c r="B41" s="266" t="s">
+      <c r="B41" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="269" t="s">
+      <c r="C41" s="190" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="267" t="s">
+      <c r="D41" s="189" t="s">
         <v>154</v>
       </c>
-      <c r="E41" s="180">
+      <c r="E41" s="169">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F41" s="181">
+      <c r="F41" s="170">
         <v>63606.28</v>
       </c>
-      <c r="G41" s="268">
-        <v>42000</v>
-      </c>
-      <c r="H41" s="182">
+      <c r="G41" s="170">
+        <f>21606+42000</f>
+        <v>63606</v>
+      </c>
+      <c r="H41" s="171">
         <f t="shared" si="1"/>
-        <v>21606.28</v>
-      </c>
-      <c r="I41" s="182">
+        <v>0.27999999999883585</v>
+      </c>
+      <c r="I41" s="171">
         <f t="shared" si="4"/>
-        <v>648.18839999999989</v>
-      </c>
-      <c r="J41" s="183">
+        <v>8.3999999999650743E-3</v>
+      </c>
+      <c r="J41" s="172">
         <f t="shared" si="5"/>
-        <v>16898.591391999995</v>
-      </c>
-      <c r="K41" s="183">
+        <v>12180</v>
+      </c>
+      <c r="K41" s="172">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L41" s="183">
+      <c r="L41" s="172">
         <f t="shared" si="6"/>
         <v>530.18672900000001</v>
       </c>
-      <c r="M41" s="183">
+      <c r="M41" s="172">
         <f t="shared" si="7"/>
-        <v>5007.1295309999996</v>
-      </c>
-      <c r="N41" s="183"/>
-      <c r="O41" s="184">
+        <v>5803.8068299999995</v>
+      </c>
+      <c r="N41" s="172"/>
+      <c r="O41" s="173">
         <f t="shared" si="8"/>
-        <v>44690.28</v>
-      </c>
-      <c r="P41" s="185">
+        <v>18514.28</v>
+      </c>
+      <c r="P41" s="174">
         <f t="shared" si="14"/>
-        <v>46031.28</v>
-      </c>
-      <c r="Q41" s="40">
+        <v>19069.28</v>
+      </c>
+      <c r="Q41" s="32">
         <f t="shared" si="12"/>
         <v>0.28000000000000008</v>
       </c>
+      <c r="R41" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="83">
+      <c r="A42" s="75">
         <f t="shared" si="15"/>
         <v>29</v>
       </c>
-      <c r="B42" s="123" t="s">
+      <c r="B42" s="115" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="78" t="s">
+      <c r="C42" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="77" t="s">
+      <c r="D42" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="74">
+      <c r="E42" s="66">
         <v>0.08</v>
       </c>
-      <c r="F42" s="63">
+      <c r="F42" s="55">
         <v>6189.29</v>
       </c>
-      <c r="G42" s="63"/>
-      <c r="H42" s="75">
+      <c r="G42" s="55"/>
+      <c r="H42" s="67">
         <f t="shared" si="1"/>
         <v>6189.29</v>
       </c>
-      <c r="I42" s="75">
+      <c r="I42" s="67">
         <f t="shared" si="4"/>
         <v>185.67869999999999</v>
       </c>
-      <c r="J42" s="82">
+      <c r="J42" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K42" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K42" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L42" s="82">
+      <c r="L42" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M42" s="82">
+      <c r="M42" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N42" s="82"/>
-      <c r="O42" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N42" s="74"/>
+      <c r="O42" s="68">
         <f t="shared" si="8"/>
-        <v>12564.29</v>
-      </c>
-      <c r="P42" s="91">
+        <v>11482.29</v>
+      </c>
+      <c r="P42" s="83">
         <f t="shared" si="14"/>
-        <v>12941.29</v>
-      </c>
-      <c r="Q42" s="40">
+        <v>11826.29</v>
+      </c>
+      <c r="Q42" s="32">
         <f t="shared" si="12"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="83">
+      <c r="A43" s="75">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="B43" s="123" t="s">
+      <c r="B43" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="78" t="s">
+      <c r="C43" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="74">
+      <c r="D43" s="69"/>
+      <c r="E43" s="66">
         <v>0.08</v>
       </c>
-      <c r="F43" s="63">
+      <c r="F43" s="55">
         <v>6189.3</v>
       </c>
-      <c r="G43" s="264">
-        <f t="shared" ref="G42:G43" si="17">F43</f>
+      <c r="G43" s="55">
+        <f t="shared" ref="G43" si="17">F43</f>
         <v>6189.3</v>
       </c>
-      <c r="H43" s="75">
+      <c r="H43" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I43" s="75">
+      <c r="I43" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J43" s="82">
+      <c r="J43" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K43" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K43" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L43" s="82">
+      <c r="L43" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M43" s="82">
+      <c r="M43" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N43" s="82"/>
-      <c r="O43" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N43" s="74"/>
+      <c r="O43" s="68">
         <f t="shared" si="8"/>
-        <v>6189.3</v>
-      </c>
-      <c r="P43" s="91">
+        <v>5107.3</v>
+      </c>
+      <c r="P43" s="83">
         <f t="shared" si="14"/>
-        <v>6375.3</v>
-      </c>
-      <c r="Q43" s="40">
+        <v>5260.3</v>
+      </c>
+      <c r="Q43" s="32">
         <f t="shared" si="12"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="83">
+      <c r="A44" s="75">
         <f t="shared" si="15"/>
         <v>31</v>
       </c>
-      <c r="B44" s="123" t="s">
+      <c r="B44" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="78" t="s">
+      <c r="C44" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="77" t="s">
+      <c r="D44" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="E44" s="74">
+      <c r="E44" s="66">
         <v>0.08</v>
       </c>
-      <c r="F44" s="63">
+      <c r="F44" s="55">
         <v>6189.31</v>
       </c>
-      <c r="G44" s="264">
+      <c r="G44" s="55">
         <f>F44</f>
         <v>6189.31</v>
       </c>
-      <c r="H44" s="75">
+      <c r="H44" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="75">
+      <c r="I44" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J44" s="82">
+      <c r="J44" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K44" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K44" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L44" s="82">
+      <c r="L44" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M44" s="82">
+      <c r="M44" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N44" s="82"/>
-      <c r="O44" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N44" s="74"/>
+      <c r="O44" s="68">
         <f t="shared" si="8"/>
-        <v>6189.31</v>
-      </c>
-      <c r="P44" s="91">
+        <v>5107.3100000000004</v>
+      </c>
+      <c r="P44" s="83">
         <f t="shared" si="14"/>
-        <v>6375.31</v>
-      </c>
-      <c r="Q44" s="40">
+        <v>5260.31</v>
+      </c>
+      <c r="Q44" s="32">
         <f t="shared" si="12"/>
         <v>0.31000000000000011</v>
       </c>
@@ -5831,465 +5817,468 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="83">
+      <c r="A45" s="75">
         <f t="shared" si="15"/>
         <v>32</v>
       </c>
-      <c r="B45" s="123" t="s">
+      <c r="B45" s="115" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="78" t="s">
+      <c r="C45" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="D45" s="77"/>
-      <c r="E45" s="74">
+      <c r="D45" s="69"/>
+      <c r="E45" s="66">
         <v>0.08</v>
       </c>
-      <c r="F45" s="63">
+      <c r="F45" s="55">
         <v>6189.32</v>
       </c>
-      <c r="G45" s="264">
+      <c r="G45" s="55">
         <f>F45</f>
         <v>6189.32</v>
       </c>
-      <c r="H45" s="75">
+      <c r="H45" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="75">
+      <c r="I45" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J45" s="82">
+      <c r="J45" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K45" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K45" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L45" s="82">
+      <c r="L45" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M45" s="82">
+      <c r="M45" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N45" s="82"/>
-      <c r="O45" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N45" s="74"/>
+      <c r="O45" s="68">
         <f t="shared" si="8"/>
-        <v>6189.32</v>
-      </c>
-      <c r="P45" s="91">
+        <v>5107.32</v>
+      </c>
+      <c r="P45" s="83">
         <f t="shared" si="14"/>
-        <v>6375.32</v>
-      </c>
-      <c r="Q45" s="40">
+        <v>5260.32</v>
+      </c>
+      <c r="Q45" s="32">
         <f t="shared" si="12"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="83">
+      <c r="A46" s="75">
         <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="B46" s="123" t="s">
+      <c r="B46" s="115" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="78" t="s">
+      <c r="C46" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="77"/>
-      <c r="E46" s="74">
+      <c r="D46" s="69"/>
+      <c r="E46" s="66">
         <v>0.08</v>
       </c>
-      <c r="F46" s="63">
+      <c r="F46" s="55">
         <v>35375.33</v>
       </c>
-      <c r="G46" s="63"/>
-      <c r="H46" s="75">
+      <c r="G46" s="55">
+        <f>F46</f>
+        <v>35375.33</v>
+      </c>
+      <c r="H46" s="67">
         <f t="shared" si="1"/>
-        <v>35375.33</v>
-      </c>
-      <c r="I46" s="75"/>
-      <c r="J46" s="82">
+        <v>0</v>
+      </c>
+      <c r="I46" s="67"/>
+      <c r="J46" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K46" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K46" s="74">
         <f t="shared" ref="K46:K59" si="18">F$2*E46/100</f>
         <v>0</v>
       </c>
-      <c r="L46" s="82">
+      <c r="L46" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M46" s="82">
+      <c r="M46" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N46" s="82"/>
-      <c r="O46" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N46" s="74"/>
+      <c r="O46" s="68">
         <f t="shared" si="8"/>
-        <v>41565.33</v>
-      </c>
-      <c r="P46" s="91">
+        <v>5107.33</v>
+      </c>
+      <c r="P46" s="83">
         <f t="shared" si="14"/>
-        <v>42812.33</v>
-      </c>
-      <c r="Q46" s="40">
+        <v>5260.33</v>
+      </c>
+      <c r="Q46" s="32">
         <f t="shared" si="12"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="83">
+      <c r="A47" s="75">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="B47" s="123" t="s">
+      <c r="B47" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="78" t="s">
+      <c r="C47" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="77"/>
-      <c r="E47" s="74">
+      <c r="D47" s="69"/>
+      <c r="E47" s="66">
         <v>0.08</v>
       </c>
-      <c r="F47" s="63">
+      <c r="F47" s="55">
         <v>6189.34</v>
       </c>
-      <c r="G47" s="264">
+      <c r="G47" s="55">
         <v>6365.34</v>
       </c>
-      <c r="H47" s="75">
+      <c r="H47" s="67">
         <f t="shared" si="1"/>
         <v>-176</v>
       </c>
-      <c r="I47" s="75">
+      <c r="I47" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J47" s="82">
+      <c r="J47" s="74">
         <f t="shared" si="5"/>
-        <v>4661.6803839999993</v>
-      </c>
-      <c r="K47" s="82">
+        <v>3360</v>
+      </c>
+      <c r="K47" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L47" s="82">
+      <c r="L47" s="74">
         <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M47" s="82">
+      <c r="M47" s="74">
         <f t="shared" si="7"/>
-        <v>1381.277112</v>
-      </c>
-      <c r="N47" s="82"/>
-      <c r="O47" s="76">
+        <v>1601.05016</v>
+      </c>
+      <c r="N47" s="74"/>
+      <c r="O47" s="68">
         <f t="shared" si="8"/>
-        <v>6013.34</v>
-      </c>
-      <c r="P47" s="91">
+        <v>4931.34</v>
+      </c>
+      <c r="P47" s="83">
         <f t="shared" si="14"/>
-        <v>6193.34</v>
-      </c>
-      <c r="Q47" s="40">
+        <v>5079.34</v>
+      </c>
+      <c r="Q47" s="32">
         <f t="shared" si="12"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="114">
+      <c r="A48" s="106">
         <f t="shared" si="15"/>
         <v>35</v>
       </c>
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="115" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="115" t="s">
+      <c r="C48" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="D48" s="116"/>
-      <c r="E48" s="117">
+      <c r="D48" s="108"/>
+      <c r="E48" s="109">
         <v>0.09</v>
       </c>
-      <c r="F48" s="63">
+      <c r="F48" s="55">
         <v>6591.35</v>
       </c>
-      <c r="G48" s="63"/>
-      <c r="H48" s="118">
+      <c r="G48" s="55"/>
+      <c r="H48" s="110">
         <f t="shared" si="1"/>
         <v>6591.35</v>
       </c>
-      <c r="I48" s="118">
+      <c r="I48" s="110">
         <f t="shared" si="4"/>
         <v>197.7405</v>
       </c>
-      <c r="J48" s="82">
+      <c r="J48" s="74">
         <f t="shared" si="5"/>
-        <v>5244.3904319999992</v>
-      </c>
-      <c r="K48" s="119">
+        <v>3780</v>
+      </c>
+      <c r="K48" s="111">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L48" s="82">
+      <c r="L48" s="74">
         <f t="shared" si="6"/>
         <v>164.54070899999999</v>
       </c>
-      <c r="M48" s="82">
+      <c r="M48" s="74">
         <f t="shared" si="7"/>
-        <v>1553.936751</v>
-      </c>
-      <c r="N48" s="119"/>
-      <c r="O48" s="76">
+        <v>1801.1814299999999</v>
+      </c>
+      <c r="N48" s="111"/>
+      <c r="O48" s="68">
         <f t="shared" si="8"/>
-        <v>13752.35</v>
-      </c>
-      <c r="P48" s="91">
+        <v>12535.35</v>
+      </c>
+      <c r="P48" s="83">
         <f t="shared" si="14"/>
-        <v>14165.35</v>
-      </c>
-      <c r="Q48" s="40">
+        <v>12911.35</v>
+      </c>
+      <c r="Q48" s="32">
         <f t="shared" si="12"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="83">
+      <c r="A49" s="75">
         <f t="shared" si="15"/>
         <v>36</v>
       </c>
-      <c r="B49" s="123" t="s">
+      <c r="B49" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="78" t="s">
+      <c r="C49" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="77"/>
-      <c r="E49" s="74">
+      <c r="D49" s="69"/>
+      <c r="E49" s="66">
         <v>0.79</v>
       </c>
-      <c r="F49" s="63">
+      <c r="F49" s="55">
         <v>61119.360000000001</v>
       </c>
-      <c r="G49" s="264">
+      <c r="G49" s="55">
         <f>F49</f>
         <v>61119.360000000001</v>
       </c>
-      <c r="H49" s="75">
+      <c r="H49" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I49" s="75">
+      <c r="I49" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J49" s="82">
+      <c r="J49" s="74">
         <f t="shared" si="5"/>
-        <v>46034.093791999992</v>
-      </c>
-      <c r="K49" s="82">
+        <v>33180</v>
+      </c>
+      <c r="K49" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L49" s="82">
+      <c r="L49" s="74">
         <f t="shared" si="6"/>
         <v>1444.3017790000001</v>
       </c>
-      <c r="M49" s="82">
+      <c r="M49" s="74">
         <f t="shared" si="7"/>
-        <v>13640.111480999998</v>
-      </c>
-      <c r="N49" s="82"/>
-      <c r="O49" s="76">
+        <v>15810.37033</v>
+      </c>
+      <c r="N49" s="74"/>
+      <c r="O49" s="68">
         <f t="shared" si="8"/>
-        <v>61119.360000000001</v>
-      </c>
-      <c r="P49" s="91">
+        <v>50435.360000000001</v>
+      </c>
+      <c r="P49" s="83">
         <f t="shared" si="14"/>
-        <v>62953.36</v>
-      </c>
-      <c r="Q49" s="40">
+        <v>51948.36</v>
+      </c>
+      <c r="Q49" s="32">
         <f t="shared" si="12"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="83">
+      <c r="A50" s="75">
         <f t="shared" si="15"/>
         <v>37</v>
       </c>
-      <c r="B50" s="123" t="s">
+      <c r="B50" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="78" t="s">
+      <c r="C50" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="77"/>
-      <c r="E50" s="74">
+      <c r="D50" s="69"/>
+      <c r="E50" s="66">
         <v>1</v>
       </c>
-      <c r="F50" s="63">
+      <c r="F50" s="55">
         <v>474490.37</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="75">
+      <c r="G50" s="55"/>
+      <c r="H50" s="67">
         <f t="shared" si="1"/>
         <v>474490.37</v>
       </c>
-      <c r="I50" s="75">
+      <c r="I50" s="67">
         <f t="shared" si="4"/>
         <v>14234.711099999999</v>
       </c>
-      <c r="J50" s="82">
+      <c r="J50" s="74">
         <f t="shared" si="5"/>
-        <v>58271.004799999995</v>
-      </c>
-      <c r="K50" s="82">
+        <v>42000</v>
+      </c>
+      <c r="K50" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L50" s="82">
+      <c r="L50" s="74">
         <f t="shared" si="6"/>
         <v>1828.2301</v>
       </c>
-      <c r="M50" s="82">
+      <c r="M50" s="74">
         <f t="shared" si="7"/>
-        <v>17265.963899999999</v>
-      </c>
-      <c r="N50" s="82"/>
-      <c r="O50" s="76">
+        <v>20013.127</v>
+      </c>
+      <c r="N50" s="74"/>
+      <c r="O50" s="68">
         <f t="shared" si="8"/>
-        <v>566090.37</v>
-      </c>
-      <c r="P50" s="91">
+        <v>552566.37</v>
+      </c>
+      <c r="P50" s="83">
         <f t="shared" si="14"/>
-        <v>583073.37</v>
-      </c>
-      <c r="Q50" s="40">
+        <v>569143.37</v>
+      </c>
+      <c r="Q50" s="32">
         <f t="shared" si="12"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="83">
+      <c r="A51" s="75">
         <f t="shared" si="15"/>
         <v>38</v>
       </c>
-      <c r="B51" s="123" t="s">
+      <c r="B51" s="115" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="78" t="s">
+      <c r="C51" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="D51" s="77"/>
-      <c r="E51" s="74">
+      <c r="D51" s="69"/>
+      <c r="E51" s="66">
         <v>0.97</v>
       </c>
-      <c r="F51" s="63">
+      <c r="F51" s="55">
         <v>75044.38</v>
       </c>
-      <c r="G51" s="264">
+      <c r="G51" s="55">
         <f>F51</f>
         <v>75044.38</v>
       </c>
-      <c r="H51" s="75">
+      <c r="H51" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I51" s="75">
+      <c r="I51" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J51" s="82">
+      <c r="J51" s="74">
         <f t="shared" si="5"/>
-        <v>56522.874656</v>
-      </c>
-      <c r="K51" s="82">
+        <v>40740</v>
+      </c>
+      <c r="K51" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L51" s="82">
+      <c r="L51" s="74">
         <f t="shared" si="6"/>
         <v>1773.3831969999999</v>
       </c>
-      <c r="M51" s="82">
+      <c r="M51" s="74">
         <f t="shared" si="7"/>
-        <v>16747.984982999998</v>
-      </c>
-      <c r="N51" s="82"/>
-      <c r="O51" s="76">
+        <v>19412.733189999999</v>
+      </c>
+      <c r="N51" s="74"/>
+      <c r="O51" s="68">
         <f t="shared" si="8"/>
-        <v>75044.38</v>
-      </c>
-      <c r="P51" s="91">
+        <v>61926.38</v>
+      </c>
+      <c r="P51" s="83">
         <f t="shared" si="14"/>
-        <v>77295.38</v>
-      </c>
-      <c r="Q51" s="40">
+        <v>63784.38</v>
+      </c>
+      <c r="Q51" s="32">
         <f t="shared" si="12"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="83">
+      <c r="A52" s="75">
         <f t="shared" si="15"/>
         <v>39</v>
       </c>
-      <c r="B52" s="123" t="s">
+      <c r="B52" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="78" t="s">
+      <c r="C52" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="D52" s="77"/>
-      <c r="E52" s="74">
+      <c r="D52" s="69"/>
+      <c r="E52" s="66">
         <v>0.77</v>
       </c>
-      <c r="F52" s="63">
+      <c r="F52" s="55">
         <v>8406.39</v>
       </c>
-      <c r="G52" s="63"/>
-      <c r="H52" s="75">
+      <c r="G52" s="55"/>
+      <c r="H52" s="67">
         <f t="shared" si="1"/>
         <v>8406.39</v>
       </c>
-      <c r="I52" s="75">
+      <c r="I52" s="67">
         <f t="shared" si="4"/>
         <v>252.19169999999997</v>
       </c>
-      <c r="J52" s="82">
+      <c r="J52" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K52" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K52" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L52" s="82">
+      <c r="L52" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M52" s="82">
+      <c r="M52" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N52" s="82"/>
-      <c r="O52" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N52" s="74"/>
+      <c r="O52" s="68">
         <f t="shared" si="8"/>
-        <v>68230.39</v>
-      </c>
-      <c r="P52" s="91">
+        <v>57816.39</v>
+      </c>
+      <c r="P52" s="83">
         <f t="shared" si="14"/>
-        <v>70277.39</v>
-      </c>
-      <c r="Q52" s="40">
+        <v>59550.39</v>
+      </c>
+      <c r="Q52" s="32">
         <f t="shared" si="12"/>
         <v>0.39000000000000018</v>
       </c>
@@ -6298,182 +6287,182 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="83">
+      <c r="A53" s="75">
         <f t="shared" si="15"/>
         <v>40</v>
       </c>
-      <c r="B53" s="123" t="s">
+      <c r="B53" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="78" t="s">
+      <c r="C53" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="77" t="s">
+      <c r="D53" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="E53" s="74">
+      <c r="E53" s="66">
         <v>0.77</v>
       </c>
-      <c r="F53" s="63">
+      <c r="F53" s="55">
         <v>59571.4</v>
       </c>
-      <c r="G53" s="264">
+      <c r="G53" s="55">
         <v>61358.400000000001</v>
       </c>
-      <c r="H53" s="75">
+      <c r="H53" s="67">
         <f t="shared" si="1"/>
         <v>-1787</v>
       </c>
-      <c r="I53" s="75">
+      <c r="I53" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J53" s="82">
+      <c r="J53" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K53" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K53" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L53" s="82">
+      <c r="L53" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="82">
+      <c r="M53" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N53" s="82"/>
-      <c r="O53" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N53" s="74"/>
+      <c r="O53" s="68">
         <f t="shared" si="8"/>
-        <v>57784.4</v>
-      </c>
-      <c r="P53" s="91">
+        <v>47371.4</v>
+      </c>
+      <c r="P53" s="83">
         <f t="shared" si="14"/>
-        <v>59518.400000000001</v>
-      </c>
-      <c r="Q53" s="40">
+        <v>48792.4</v>
+      </c>
+      <c r="Q53" s="32">
         <f t="shared" si="12"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="83">
+      <c r="A54" s="75">
         <f t="shared" si="15"/>
         <v>41</v>
       </c>
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="78" t="s">
+      <c r="C54" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="77" t="s">
+      <c r="D54" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="E54" s="74">
+      <c r="E54" s="66">
         <v>0.81</v>
       </c>
-      <c r="F54" s="63">
+      <c r="F54" s="55">
         <v>177656.41</v>
       </c>
-      <c r="G54" s="63">
-        <v>0</v>
-      </c>
-      <c r="H54" s="75">
+      <c r="G54" s="55">
+        <v>0</v>
+      </c>
+      <c r="H54" s="67">
         <f t="shared" si="1"/>
         <v>177656.41</v>
       </c>
-      <c r="I54" s="75">
+      <c r="I54" s="67">
         <f t="shared" si="4"/>
         <v>5329.6922999999997</v>
       </c>
-      <c r="J54" s="82">
+      <c r="J54" s="74">
         <f t="shared" si="5"/>
-        <v>47199.513888000001</v>
-      </c>
-      <c r="K54" s="82">
+        <v>34020</v>
+      </c>
+      <c r="K54" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L54" s="82">
+      <c r="L54" s="74">
         <f t="shared" si="6"/>
         <v>1480.866381</v>
       </c>
-      <c r="M54" s="82">
+      <c r="M54" s="74">
         <f t="shared" si="7"/>
-        <v>13985.430759000001</v>
-      </c>
-      <c r="N54" s="82"/>
-      <c r="O54" s="76">
+        <v>16210.632869999999</v>
+      </c>
+      <c r="N54" s="74"/>
+      <c r="O54" s="68">
         <f t="shared" si="8"/>
-        <v>245652.41</v>
-      </c>
-      <c r="P54" s="91">
+        <v>234698.41</v>
+      </c>
+      <c r="P54" s="83">
         <f t="shared" si="14"/>
-        <v>253022.41</v>
-      </c>
-      <c r="Q54" s="40">
+        <v>241739.41</v>
+      </c>
+      <c r="Q54" s="32">
         <f t="shared" si="12"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="83">
+      <c r="A55" s="75">
         <f t="shared" si="15"/>
         <v>42</v>
       </c>
-      <c r="B55" s="123" t="s">
+      <c r="B55" s="115" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="78" t="s">
+      <c r="C55" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D55" s="77" t="s">
+      <c r="D55" s="69" t="s">
         <v>152</v>
       </c>
-      <c r="E55" s="74">
+      <c r="E55" s="66">
         <v>0.77</v>
       </c>
-      <c r="F55" s="63">
+      <c r="F55" s="55">
         <v>59571.42</v>
       </c>
-      <c r="G55" s="264">
+      <c r="G55" s="55">
         <f>F55</f>
         <v>59571.42</v>
       </c>
-      <c r="H55" s="75">
+      <c r="H55" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I55" s="75"/>
-      <c r="J55" s="82">
+      <c r="I55" s="67"/>
+      <c r="J55" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K55" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K55" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L55" s="82">
+      <c r="L55" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M55" s="82">
+      <c r="M55" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N55" s="82"/>
-      <c r="O55" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N55" s="74"/>
+      <c r="O55" s="68">
         <f t="shared" si="8"/>
-        <v>59571.42</v>
-      </c>
-      <c r="P55" s="91">
+        <v>49158.42</v>
+      </c>
+      <c r="P55" s="83">
         <f t="shared" si="14"/>
-        <v>61358.42</v>
-      </c>
-      <c r="Q55" s="40">
+        <v>50633.42</v>
+      </c>
+      <c r="Q55" s="32">
         <f t="shared" si="12"/>
         <v>0.42000000000000021</v>
       </c>
@@ -6482,234 +6471,234 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="83">
+      <c r="A56" s="75">
         <f t="shared" si="15"/>
         <v>43</v>
       </c>
-      <c r="B56" s="123" t="s">
+      <c r="B56" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="C56" s="78" t="s">
+      <c r="C56" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="77"/>
-      <c r="E56" s="74">
+      <c r="D56" s="69"/>
+      <c r="E56" s="66">
         <v>0.77</v>
       </c>
-      <c r="F56" s="63">
+      <c r="F56" s="55">
         <v>363220.43</v>
       </c>
-      <c r="G56" s="63"/>
-      <c r="H56" s="75">
+      <c r="G56" s="55"/>
+      <c r="H56" s="67">
         <f t="shared" si="1"/>
         <v>363220.43</v>
       </c>
-      <c r="I56" s="75">
+      <c r="I56" s="67">
         <f t="shared" si="4"/>
         <v>10896.6129</v>
       </c>
-      <c r="J56" s="82">
+      <c r="J56" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K56" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K56" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L56" s="82">
+      <c r="L56" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M56" s="82">
+      <c r="M56" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N56" s="82"/>
-      <c r="O56" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N56" s="74"/>
+      <c r="O56" s="68">
         <f t="shared" si="8"/>
-        <v>433688.43</v>
-      </c>
-      <c r="P56" s="91">
+        <v>423275.43</v>
+      </c>
+      <c r="P56" s="83">
         <f t="shared" si="14"/>
-        <v>446699.43</v>
-      </c>
-      <c r="Q56" s="40">
+        <v>435973.43</v>
+      </c>
+      <c r="Q56" s="32">
         <f t="shared" si="12"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="83">
+      <c r="A57" s="75">
         <f t="shared" si="15"/>
         <v>44</v>
       </c>
-      <c r="B57" s="123" t="s">
+      <c r="B57" s="115" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="78" t="s">
+      <c r="C57" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="D57" s="77"/>
-      <c r="E57" s="74">
+      <c r="D57" s="69"/>
+      <c r="E57" s="66">
         <v>0.77</v>
       </c>
-      <c r="F57" s="63">
+      <c r="F57" s="55">
         <v>291885.44</v>
       </c>
-      <c r="G57" s="63"/>
-      <c r="H57" s="75">
+      <c r="G57" s="55"/>
+      <c r="H57" s="67">
         <f t="shared" si="1"/>
         <v>291885.44</v>
       </c>
-      <c r="I57" s="75">
+      <c r="I57" s="67">
         <f t="shared" si="4"/>
         <v>8756.5632000000005</v>
       </c>
-      <c r="J57" s="82">
+      <c r="J57" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K57" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K57" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L57" s="82">
+      <c r="L57" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M57" s="82">
+      <c r="M57" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N57" s="82"/>
-      <c r="O57" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N57" s="74"/>
+      <c r="O57" s="68">
         <f t="shared" si="8"/>
-        <v>360213.44</v>
-      </c>
-      <c r="P57" s="91">
+        <v>349800.44</v>
+      </c>
+      <c r="P57" s="83">
         <f t="shared" si="14"/>
-        <v>371019.44</v>
-      </c>
-      <c r="Q57" s="40">
+        <v>360294.44</v>
+      </c>
+      <c r="Q57" s="32">
         <f t="shared" si="12"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="83">
+      <c r="A58" s="75">
         <f t="shared" si="15"/>
         <v>45</v>
       </c>
-      <c r="B58" s="123" t="s">
+      <c r="B58" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="78" t="s">
+      <c r="C58" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="77" t="s">
+      <c r="D58" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="E58" s="74">
+      <c r="E58" s="66">
         <v>0.77</v>
       </c>
-      <c r="F58" s="63">
+      <c r="F58" s="55">
         <v>59571.45</v>
       </c>
-      <c r="G58" s="264">
+      <c r="G58" s="55">
         <f t="shared" ref="G58" si="19">F58</f>
         <v>59571.45</v>
       </c>
-      <c r="H58" s="75">
+      <c r="H58" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I58" s="75">
+      <c r="I58" s="67">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J58" s="82">
+      <c r="J58" s="74">
         <f t="shared" si="5"/>
-        <v>44868.673695999998</v>
-      </c>
-      <c r="K58" s="82">
+        <v>32340</v>
+      </c>
+      <c r="K58" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L58" s="82">
+      <c r="L58" s="74">
         <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
-      <c r="M58" s="82">
+      <c r="M58" s="74">
         <f t="shared" si="7"/>
-        <v>13294.792202999999</v>
-      </c>
-      <c r="N58" s="82"/>
-      <c r="O58" s="76">
+        <v>15410.107790000002</v>
+      </c>
+      <c r="N58" s="74"/>
+      <c r="O58" s="68">
         <f t="shared" si="8"/>
-        <v>59571.45</v>
-      </c>
-      <c r="P58" s="91">
+        <v>49158.45</v>
+      </c>
+      <c r="P58" s="83">
         <f t="shared" si="14"/>
-        <v>61358.45</v>
-      </c>
-      <c r="Q58" s="40">
+        <v>50633.45</v>
+      </c>
+      <c r="Q58" s="32">
         <f t="shared" si="12"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="83">
+      <c r="A59" s="75">
         <f t="shared" si="15"/>
         <v>46</v>
       </c>
-      <c r="B59" s="123" t="s">
+      <c r="B59" s="115" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="78" t="s">
+      <c r="C59" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D59" s="77"/>
-      <c r="E59" s="74">
+      <c r="D59" s="69"/>
+      <c r="E59" s="66">
         <v>0.86</v>
       </c>
-      <c r="F59" s="63">
+      <c r="F59" s="55">
         <v>15867.46</v>
       </c>
-      <c r="G59" s="63"/>
-      <c r="H59" s="75">
+      <c r="G59" s="55"/>
+      <c r="H59" s="67">
         <f t="shared" si="1"/>
         <v>15867.46</v>
       </c>
-      <c r="I59" s="75">
+      <c r="I59" s="67">
         <f t="shared" si="4"/>
         <v>476.02379999999994</v>
       </c>
-      <c r="J59" s="82">
+      <c r="J59" s="74">
         <f t="shared" si="5"/>
-        <v>50113.064127999991</v>
-      </c>
-      <c r="K59" s="82">
+        <v>36120</v>
+      </c>
+      <c r="K59" s="74">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L59" s="82">
+      <c r="L59" s="74">
         <f t="shared" si="6"/>
         <v>1572.2778860000001</v>
       </c>
-      <c r="M59" s="82">
+      <c r="M59" s="74">
         <f t="shared" si="7"/>
-        <v>14848.728953999998</v>
-      </c>
-      <c r="N59" s="82"/>
-      <c r="O59" s="76">
+        <v>17211.289219999999</v>
+      </c>
+      <c r="N59" s="74"/>
+      <c r="O59" s="68">
         <f t="shared" si="8"/>
-        <v>82878.460000000006</v>
-      </c>
-      <c r="P59" s="91">
+        <v>71247.460000000006</v>
+      </c>
+      <c r="P59" s="83">
         <f t="shared" si="14"/>
-        <v>85364.46</v>
-      </c>
-      <c r="Q59" s="40">
+        <v>73384.460000000006</v>
+      </c>
+      <c r="Q59" s="32">
         <f t="shared" si="12"/>
         <v>0.46000000000000024</v>
       </c>
@@ -6718,182 +6707,174 @@
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="83"/>
-      <c r="B60" s="123"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="77"/>
-      <c r="E60" s="74"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="75"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
-      <c r="M60" s="82"/>
-      <c r="N60" s="82"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="91"/>
-      <c r="Q60" s="40"/>
+      <c r="A60" s="75"/>
+      <c r="B60" s="115"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
+      <c r="L60" s="74"/>
+      <c r="M60" s="74"/>
+      <c r="N60" s="74"/>
+      <c r="O60" s="68"/>
+      <c r="P60" s="83"/>
+      <c r="Q60" s="32"/>
     </row>
     <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
-      <c r="B61" s="124"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="85"/>
-      <c r="E61" s="86">
+      <c r="A61" s="76"/>
+      <c r="B61" s="116"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="78">
         <f t="shared" ref="E61:M61" si="20">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F61" s="87">
+      <c r="F61" s="79">
         <f t="shared" si="20"/>
         <v>13013409.810000001</v>
       </c>
-      <c r="G61" s="88">
+      <c r="G61" s="253">
         <f>SUM(G14:G60)</f>
-        <v>10127798.860000001</v>
-      </c>
-      <c r="H61" s="88">
+        <v>10411472.860000003</v>
+      </c>
+      <c r="H61" s="80">
         <f t="shared" si="20"/>
-        <v>2885610.95</v>
-      </c>
-      <c r="I61" s="88">
+        <v>2601936.9500000002</v>
+      </c>
+      <c r="I61" s="80">
         <f t="shared" si="20"/>
-        <v>90143.001900000003</v>
-      </c>
-      <c r="J61" s="89">
+        <v>81632.781900000002</v>
+      </c>
+      <c r="J61" s="81">
         <f t="shared" si="20"/>
-        <v>5827100.4799999986</v>
-      </c>
-      <c r="K61" s="89">
+        <v>4200000</v>
+      </c>
+      <c r="K61" s="81">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="L61" s="89">
+      <c r="L61" s="81">
         <f t="shared" si="20"/>
         <v>182823.00999999992</v>
       </c>
-      <c r="M61" s="89">
+      <c r="M61" s="81">
         <f t="shared" si="20"/>
-        <v>1726596.389999999</v>
-      </c>
-      <c r="N61" s="90"/>
-      <c r="O61" s="95">
+        <v>2001312.7000000011</v>
+      </c>
+      <c r="N61" s="82"/>
+      <c r="O61" s="87">
         <f>SUM(O14:O60)</f>
-        <v>10755785.809999999</v>
-      </c>
-      <c r="P61" s="92">
+        <v>9067717.8100000005</v>
+      </c>
+      <c r="P61" s="84">
         <f>SUM(P14:P60)</f>
-        <v>11078459.809999999</v>
+        <v>9339747.8100000005</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="64"/>
-      <c r="D62" s="64"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="230" t="s">
+      <c r="C64" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="230"/>
-      <c r="E64" s="230"/>
-      <c r="F64" s="230"/>
-      <c r="G64" s="230"/>
-      <c r="H64" s="230"/>
-      <c r="I64" s="230"/>
-      <c r="J64" s="230"/>
-      <c r="K64" s="230"/>
-      <c r="L64" s="230"/>
-      <c r="M64" s="230"/>
-      <c r="N64" s="230"/>
-      <c r="O64" s="230"/>
+      <c r="D64" s="220"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
+      <c r="G64" s="220"/>
+      <c r="H64" s="220"/>
+      <c r="I64" s="220"/>
+      <c r="J64" s="220"/>
+      <c r="K64" s="220"/>
+      <c r="L64" s="220"/>
+      <c r="M64" s="220"/>
+      <c r="N64" s="220"/>
+      <c r="O64" s="220"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="230"/>
-      <c r="D65" s="230"/>
-      <c r="E65" s="230"/>
-      <c r="F65" s="230"/>
-      <c r="G65" s="230"/>
-      <c r="H65" s="230"/>
-      <c r="I65" s="230"/>
-      <c r="J65" s="230"/>
-      <c r="K65" s="230"/>
-      <c r="L65" s="230"/>
-      <c r="M65" s="230"/>
-      <c r="N65" s="230"/>
-      <c r="O65" s="230"/>
+      <c r="C65" s="220"/>
+      <c r="D65" s="220"/>
+      <c r="E65" s="220"/>
+      <c r="F65" s="220"/>
+      <c r="G65" s="220"/>
+      <c r="H65" s="220"/>
+      <c r="I65" s="220"/>
+      <c r="J65" s="220"/>
+      <c r="K65" s="220"/>
+      <c r="L65" s="220"/>
+      <c r="M65" s="220"/>
+      <c r="N65" s="220"/>
+      <c r="O65" s="220"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="230"/>
-      <c r="D66" s="230"/>
-      <c r="E66" s="230"/>
-      <c r="F66" s="230"/>
-      <c r="G66" s="230"/>
-      <c r="H66" s="230"/>
-      <c r="I66" s="230"/>
-      <c r="J66" s="230"/>
-      <c r="K66" s="230"/>
-      <c r="L66" s="230"/>
-      <c r="M66" s="230"/>
-      <c r="N66" s="230"/>
-      <c r="O66" s="230"/>
+      <c r="C66" s="220"/>
+      <c r="D66" s="220"/>
+      <c r="E66" s="220"/>
+      <c r="F66" s="220"/>
+      <c r="G66" s="220"/>
+      <c r="H66" s="220"/>
+      <c r="I66" s="220"/>
+      <c r="J66" s="220"/>
+      <c r="K66" s="220"/>
+      <c r="L66" s="220"/>
+      <c r="M66" s="220"/>
+      <c r="N66" s="220"/>
+      <c r="O66" s="220"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="230"/>
-      <c r="D67" s="230"/>
-      <c r="E67" s="230"/>
-      <c r="F67" s="230"/>
-      <c r="G67" s="230"/>
-      <c r="H67" s="230"/>
-      <c r="I67" s="230"/>
-      <c r="J67" s="230"/>
-      <c r="K67" s="230"/>
-      <c r="L67" s="230"/>
-      <c r="M67" s="230"/>
-      <c r="N67" s="230"/>
-      <c r="O67" s="230"/>
+      <c r="C67" s="220"/>
+      <c r="D67" s="220"/>
+      <c r="E67" s="220"/>
+      <c r="F67" s="220"/>
+      <c r="G67" s="220"/>
+      <c r="H67" s="220"/>
+      <c r="I67" s="220"/>
+      <c r="J67" s="220"/>
+      <c r="K67" s="220"/>
+      <c r="L67" s="220"/>
+      <c r="M67" s="220"/>
+      <c r="N67" s="220"/>
+      <c r="O67" s="220"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="230"/>
-      <c r="D68" s="230"/>
-      <c r="E68" s="230"/>
-      <c r="F68" s="230"/>
-      <c r="G68" s="230"/>
-      <c r="H68" s="230"/>
-      <c r="I68" s="230"/>
-      <c r="J68" s="230"/>
-      <c r="K68" s="230"/>
-      <c r="L68" s="230"/>
-      <c r="M68" s="230"/>
-      <c r="N68" s="230"/>
-      <c r="O68" s="230"/>
+      <c r="C68" s="220"/>
+      <c r="D68" s="220"/>
+      <c r="E68" s="220"/>
+      <c r="F68" s="220"/>
+      <c r="G68" s="220"/>
+      <c r="H68" s="220"/>
+      <c r="I68" s="220"/>
+      <c r="J68" s="220"/>
+      <c r="K68" s="220"/>
+      <c r="L68" s="220"/>
+      <c r="M68" s="220"/>
+      <c r="N68" s="220"/>
+      <c r="O68" s="220"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
-      <c r="I69" s="230"/>
-      <c r="J69" s="230"/>
-      <c r="K69" s="230"/>
-      <c r="L69" s="230"/>
-      <c r="M69" s="230"/>
-      <c r="N69" s="230"/>
-      <c r="O69" s="230"/>
+      <c r="C69" s="220"/>
+      <c r="D69" s="220"/>
+      <c r="E69" s="220"/>
+      <c r="F69" s="220"/>
+      <c r="G69" s="220"/>
+      <c r="H69" s="220"/>
+      <c r="I69" s="220"/>
+      <c r="J69" s="220"/>
+      <c r="K69" s="220"/>
+      <c r="L69" s="220"/>
+      <c r="M69" s="220"/>
+      <c r="N69" s="220"/>
+      <c r="O69" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J1:P5"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C64:O69"/>
     <mergeCell ref="A6:P10"/>
     <mergeCell ref="A12:A13"/>
@@ -6906,8 +6887,16 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="J1:P5"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="60" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6923,23 +6912,23 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="198"/>
+      <c r="D4" s="181"/>
       <c r="E4" t="s">
         <v>52</v>
       </c>
       <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="112"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="197" t="s">
+      <c r="C5" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="198" t="s">
+      <c r="D5" s="181" t="s">
         <v>55</v>
       </c>
       <c r="E5" t="s">
@@ -6951,35 +6940,35 @@
       <c r="H5" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="112"/>
+      <c r="J5" s="104"/>
     </row>
     <row r="6" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="112"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="256" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="257"/>
-      <c r="E7" s="257"/>
-      <c r="F7" s="257"/>
-      <c r="G7" s="257"/>
-      <c r="H7" s="257"/>
-      <c r="I7" s="257"/>
-      <c r="J7" s="258"/>
+      <c r="C7" s="242" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="244"/>
     </row>
     <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="259"/>
-      <c r="D8" s="260"/>
-      <c r="E8" s="260"/>
-      <c r="F8" s="260"/>
-      <c r="G8" s="260"/>
-      <c r="H8" s="260"/>
-      <c r="I8" s="260"/>
-      <c r="J8" s="261"/>
+      <c r="C8" s="245"/>
+      <c r="D8" s="246"/>
+      <c r="E8" s="246"/>
+      <c r="F8" s="246"/>
+      <c r="G8" s="246"/>
+      <c r="H8" s="246"/>
+      <c r="I8" s="246"/>
+      <c r="J8" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD17D286-1F17-4330-AD99-82EBD5829BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA48F3B4-F81F-4FFE-BEAA-DB38085C3AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -666,9 +666,6 @@
     <t>Transf 28/09</t>
   </si>
   <si>
-    <t>Transferencia 09/09 Vazquez Miguel Angel</t>
-  </si>
-  <si>
     <t>Deposito 23/09</t>
   </si>
   <si>
@@ -682,6 +679,9 @@
   </si>
   <si>
     <t>Ingresos correspondientes a caja SUM</t>
+  </si>
+  <si>
+    <t>Vazquez Miguel Angel</t>
   </si>
 </sst>
 </file>
@@ -1764,180 +1764,6 @@
     <xf numFmtId="0" fontId="15" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="9" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="9" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1947,6 +1773,180 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2350,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2368,12 +2368,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="196" t="s">
+      <c r="B1" s="201" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="197"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="202"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2386,12 +2386,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="203" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="204"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2429,18 +2429,18 @@
       <c r="E6" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="205" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="200"/>
+      <c r="C8" s="205"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -2449,34 +2449,34 @@
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="248" t="s">
+      <c r="A13" s="206" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="248"/>
-      <c r="C13" s="248"/>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="248"/>
-      <c r="B14" s="248"/>
-      <c r="C14" s="248"/>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="248"/>
-      <c r="B15" s="248"/>
-      <c r="C15" s="248"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="248"/>
-      <c r="B16" s="248"/>
-      <c r="C16" s="248"/>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30"/>
@@ -2486,7 +2486,7 @@
       <c r="E17" s="30"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="249"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -2518,10 +2518,10 @@
       <c r="E21" s="88"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="191" t="s">
+      <c r="A22" s="196" t="s">
         <v>186</v>
       </c>
-      <c r="B22" s="192"/>
+      <c r="B22" s="197"/>
       <c r="C22" s="136"/>
       <c r="D22" s="177">
         <v>1448764.03</v>
@@ -2530,10 +2530,10 @@
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="191" t="s">
+      <c r="A23" s="196" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="192"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="136"/>
       <c r="D23" s="177">
         <v>-315106.03000000003</v>
@@ -2543,10 +2543,10 @@
       <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="191" t="s">
+      <c r="A24" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="192"/>
+      <c r="B24" s="197"/>
       <c r="C24" s="136"/>
       <c r="D24" s="175"/>
       <c r="E24" s="13"/>
@@ -2725,12 +2725,12 @@
       <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="201" t="s">
+      <c r="A39" s="207" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="202"/>
+      <c r="B39" s="208"/>
       <c r="C39" s="140"/>
-      <c r="D39" s="250">
+      <c r="D39" s="192">
         <v>205033.71</v>
       </c>
       <c r="E39" s="13" t="s">
@@ -2739,12 +2739,12 @@
       <c r="F39" s="30"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="201" t="s">
+      <c r="A40" s="207" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="202"/>
+      <c r="B40" s="208"/>
       <c r="C40" s="140"/>
-      <c r="D40" s="250">
+      <c r="D40" s="192">
         <v>1426.62</v>
       </c>
       <c r="E40" s="13" t="str">
@@ -2817,16 +2817,16 @@
       <c r="F45" s="30"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="201" t="s">
+      <c r="A46" s="207" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="202"/>
+      <c r="B46" s="208"/>
       <c r="C46" s="25"/>
       <c r="D46" s="176">
         <v>549962.86</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F46" s="30"/>
     </row>
@@ -2868,10 +2868,10 @@
       <c r="F49" s="30"/>
     </row>
     <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="191" t="s">
+      <c r="A50" s="196" t="s">
         <v>185</v>
       </c>
-      <c r="B50" s="192"/>
+      <c r="B50" s="197"/>
       <c r="C50" s="25"/>
       <c r="D50" s="176">
         <v>298200</v>
@@ -2882,10 +2882,10 @@
       <c r="F50" s="30"/>
     </row>
     <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="203" t="s">
+      <c r="A51" s="209" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="204"/>
+      <c r="B51" s="210"/>
       <c r="C51" s="136"/>
       <c r="D51" s="176">
         <v>50000</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="53" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="182" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B53" s="183"/>
       <c r="C53" s="136"/>
@@ -2947,12 +2947,12 @@
       <c r="F55" s="30"/>
     </row>
     <row r="56" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="191" t="s">
+      <c r="A56" s="196" t="s">
         <v>200</v>
       </c>
-      <c r="B56" s="192"/>
+      <c r="B56" s="197"/>
       <c r="C56" s="136"/>
-      <c r="D56" s="251">
+      <c r="D56" s="193">
         <f>420000*2</f>
         <v>840000</v>
       </c>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B57" s="183"/>
       <c r="C57" s="136"/>
-      <c r="D57" s="251">
+      <c r="D57" s="193">
         <v>50000</v>
       </c>
       <c r="E57" s="89" t="s">
@@ -3104,8 +3104,8 @@
       <c r="F69" s="30"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="194"/>
-      <c r="B70" s="195"/>
+      <c r="A70" s="199"/>
+      <c r="B70" s="200"/>
       <c r="C70" s="25"/>
       <c r="D70" s="155"/>
       <c r="E70" s="105"/>
@@ -3461,8 +3461,8 @@
         <v>24</v>
       </c>
       <c r="B103" s="44">
-        <f>B116</f>
-        <v>687432</v>
+        <f>B115</f>
+        <v>418200</v>
       </c>
       <c r="D103" s="30"/>
       <c r="E103" s="30"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B104" s="45">
         <f>PRORRATEO!G61</f>
-        <v>10411472.860000003</v>
+        <v>10680704.860000003</v>
       </c>
       <c r="D104" s="30"/>
       <c r="E104" s="30"/>
@@ -3482,9 +3482,9 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B105" s="252">
+        <v>211</v>
+      </c>
+      <c r="B105" s="194">
         <f>-B92</f>
         <v>-43500</v>
       </c>
@@ -3531,59 +3531,49 @@
     </row>
     <row r="110" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="193" t="s">
+      <c r="A111" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="B111" s="193"/>
-      <c r="C111" s="193"/>
+      <c r="B111" s="198"/>
+      <c r="C111" s="198"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="193"/>
-      <c r="B112" s="193"/>
-      <c r="C112" s="193"/>
+      <c r="A112" s="198"/>
+      <c r="B112" s="198"/>
+      <c r="C112" s="198"/>
     </row>
     <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="48" t="s">
         <v>207</v>
       </c>
       <c r="B113" s="71">
-        <v>269232</v>
+        <v>376000</v>
       </c>
       <c r="C113" s="49"/>
       <c r="D113" s="35"/>
     </row>
     <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B114" s="71">
-        <v>376000</v>
+        <v>42200</v>
       </c>
       <c r="C114" s="49"/>
       <c r="D114" s="35"/>
     </row>
-    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="B115" s="71">
-        <v>42200</v>
-      </c>
-      <c r="C115" s="49"/>
-      <c r="D115" s="35"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="51">
+        <f>SUM(B113:B114)</f>
+        <v>418200</v>
+      </c>
+      <c r="C115" s="52"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B116" s="51">
-        <f>SUM(B113:B115)</f>
-        <v>687432</v>
-      </c>
-      <c r="C116" s="52"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M117" s="53"/>
+      <c r="M116" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3642,19 +3632,19 @@
       <c r="G1" s="112"/>
       <c r="H1" s="112"/>
       <c r="I1" s="112"/>
-      <c r="J1" s="211" t="str">
+      <c r="J1" s="239" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="211"/>
-      <c r="P1" s="212"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
+      <c r="M1" s="239"/>
+      <c r="N1" s="239"/>
+      <c r="O1" s="239"/>
+      <c r="P1" s="240"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -3668,17 +3658,17 @@
         <v>7736519.879999999</v>
       </c>
       <c r="E2" s="60"/>
-      <c r="F2" s="219"/>
-      <c r="G2" s="219"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="247"/>
       <c r="H2" s="60"/>
       <c r="I2" s="60"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="213"/>
-      <c r="L2" s="213"/>
-      <c r="M2" s="213"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="213"/>
-      <c r="P2" s="214"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
+      <c r="L2" s="241"/>
+      <c r="M2" s="241"/>
+      <c r="N2" s="241"/>
+      <c r="O2" s="241"/>
+      <c r="P2" s="242"/>
       <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3695,13 +3685,13 @@
       <c r="G3" s="117"/>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="213"/>
-      <c r="M3" s="213"/>
-      <c r="N3" s="213"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="M3" s="241"/>
+      <c r="N3" s="241"/>
+      <c r="O3" s="241"/>
+      <c r="P3" s="242"/>
       <c r="Q3" s="54"/>
       <c r="R3" s="32"/>
     </row>
@@ -3719,13 +3709,13 @@
       <c r="G4" s="117"/>
       <c r="H4" s="60"/>
       <c r="I4" s="60"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="214"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="241"/>
+      <c r="N4" s="241"/>
+      <c r="O4" s="241"/>
+      <c r="P4" s="242"/>
       <c r="Q4" s="54"/>
       <c r="R4" s="32"/>
     </row>
@@ -3743,201 +3733,201 @@
       <c r="G5" s="62"/>
       <c r="H5" s="61"/>
       <c r="I5" s="61"/>
-      <c r="J5" s="215"/>
-      <c r="K5" s="215"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="215"/>
-      <c r="N5" s="215"/>
-      <c r="O5" s="215"/>
-      <c r="P5" s="216"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
+      <c r="O5" s="243"/>
+      <c r="P5" s="244"/>
       <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="212" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="222"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="223"/>
-      <c r="O6" s="223"/>
-      <c r="P6" s="224"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="214"/>
+      <c r="F6" s="214"/>
+      <c r="G6" s="214"/>
+      <c r="H6" s="214"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="214"/>
+      <c r="K6" s="214"/>
+      <c r="L6" s="214"/>
+      <c r="M6" s="214"/>
+      <c r="N6" s="214"/>
+      <c r="O6" s="214"/>
+      <c r="P6" s="215"/>
       <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="226"/>
-      <c r="P7" s="227"/>
+      <c r="A7" s="216"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="217"/>
+      <c r="K7" s="217"/>
+      <c r="L7" s="217"/>
+      <c r="M7" s="217"/>
+      <c r="N7" s="217"/>
+      <c r="O7" s="217"/>
+      <c r="P7" s="218"/>
       <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="225"/>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="226"/>
-      <c r="O8" s="226"/>
-      <c r="P8" s="227"/>
+      <c r="A8" s="216"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="217"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="217"/>
+      <c r="J8" s="217"/>
+      <c r="K8" s="217"/>
+      <c r="L8" s="217"/>
+      <c r="M8" s="217"/>
+      <c r="N8" s="217"/>
+      <c r="O8" s="217"/>
+      <c r="P8" s="218"/>
       <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="225"/>
-      <c r="B9" s="226"/>
-      <c r="C9" s="226"/>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="226"/>
-      <c r="H9" s="226"/>
-      <c r="I9" s="226"/>
-      <c r="J9" s="226"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="226"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="226"/>
-      <c r="O9" s="226"/>
-      <c r="P9" s="227"/>
+      <c r="A9" s="216"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
+      <c r="D9" s="217"/>
+      <c r="E9" s="217"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="217"/>
+      <c r="J9" s="217"/>
+      <c r="K9" s="217"/>
+      <c r="L9" s="217"/>
+      <c r="M9" s="217"/>
+      <c r="N9" s="217"/>
+      <c r="O9" s="217"/>
+      <c r="P9" s="218"/>
       <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="228"/>
-      <c r="B10" s="229"/>
-      <c r="C10" s="229"/>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="229"/>
-      <c r="I10" s="229"/>
-      <c r="J10" s="229"/>
-      <c r="K10" s="229"/>
-      <c r="L10" s="229"/>
-      <c r="M10" s="229"/>
-      <c r="N10" s="229"/>
-      <c r="O10" s="229"/>
-      <c r="P10" s="230"/>
+      <c r="A10" s="219"/>
+      <c r="B10" s="220"/>
+      <c r="C10" s="220"/>
+      <c r="D10" s="220"/>
+      <c r="E10" s="220"/>
+      <c r="F10" s="220"/>
+      <c r="G10" s="220"/>
+      <c r="H10" s="220"/>
+      <c r="I10" s="220"/>
+      <c r="J10" s="220"/>
+      <c r="K10" s="220"/>
+      <c r="L10" s="220"/>
+      <c r="M10" s="220"/>
+      <c r="N10" s="220"/>
+      <c r="O10" s="220"/>
+      <c r="P10" s="221"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="239" t="s">
+      <c r="A11" s="232" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="240"/>
-      <c r="C11" s="240"/>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
-      <c r="M11" s="240"/>
-      <c r="N11" s="240"/>
-      <c r="O11" s="240"/>
-      <c r="P11" s="241"/>
+      <c r="B11" s="233"/>
+      <c r="C11" s="233"/>
+      <c r="D11" s="233"/>
+      <c r="E11" s="233"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="233"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="233"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="233"/>
+      <c r="P11" s="234"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="231" t="s">
+      <c r="A12" s="222" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="207" t="s">
+      <c r="B12" s="237" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="233" t="s">
+      <c r="C12" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="233" t="s">
+      <c r="D12" s="224" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="233" t="s">
+      <c r="E12" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="209" t="s">
+      <c r="F12" s="226" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="235" t="s">
+      <c r="G12" s="228" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="237" t="s">
+      <c r="H12" s="230" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="209" t="s">
+      <c r="I12" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="209" t="s">
+      <c r="J12" s="226" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="209" t="s">
+      <c r="K12" s="226" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="207" t="s">
+      <c r="L12" s="237" t="s">
         <v>169</v>
       </c>
-      <c r="M12" s="209" t="s">
+      <c r="M12" s="226" t="s">
         <v>166</v>
       </c>
-      <c r="N12" s="205" t="s">
+      <c r="N12" s="235" t="s">
         <v>179</v>
       </c>
       <c r="O12" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="217" t="s">
+      <c r="P12" s="245" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="232"/>
-      <c r="B13" s="208"/>
-      <c r="C13" s="234"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-      <c r="F13" s="210"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="210"/>
-      <c r="J13" s="210"/>
-      <c r="K13" s="210"/>
-      <c r="L13" s="208"/>
-      <c r="M13" s="210"/>
-      <c r="N13" s="206"/>
+      <c r="A13" s="223"/>
+      <c r="B13" s="238"/>
+      <c r="C13" s="225"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="227"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="231"/>
+      <c r="I13" s="227"/>
+      <c r="J13" s="227"/>
+      <c r="K13" s="227"/>
+      <c r="L13" s="238"/>
+      <c r="M13" s="227"/>
+      <c r="N13" s="236"/>
       <c r="O13" s="86" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P13" s="218"/>
+      <c r="P13" s="246"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="75">
@@ -4058,7 +4048,7 @@
         <v>0.02</v>
       </c>
       <c r="R15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4566,14 +4556,16 @@
       <c r="F24" s="55">
         <v>263042.11</v>
       </c>
-      <c r="G24" s="55"/>
+      <c r="G24" s="55">
+        <v>269232</v>
+      </c>
       <c r="H24" s="67">
         <f t="shared" si="1"/>
-        <v>263042.11</v>
+        <v>-6189.890000000014</v>
       </c>
       <c r="I24" s="67">
         <f t="shared" si="4"/>
-        <v>7891.2632999999996</v>
+        <v>0</v>
       </c>
       <c r="J24" s="74">
         <f t="shared" si="5"/>
@@ -4594,15 +4586,18 @@
       <c r="N24" s="74"/>
       <c r="O24" s="68">
         <f t="shared" si="8"/>
-        <v>487994.11</v>
+        <v>210871.11</v>
       </c>
       <c r="P24" s="83">
         <f t="shared" si="3"/>
-        <v>502634.11</v>
+        <v>217197.11</v>
       </c>
       <c r="Q24" s="32">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
+      </c>
+      <c r="R24" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5629,7 +5624,7 @@
         <v>0.28000000000000008</v>
       </c>
       <c r="R41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -6738,17 +6733,17 @@
         <f t="shared" si="20"/>
         <v>13013409.810000001</v>
       </c>
-      <c r="G61" s="253">
+      <c r="G61" s="195">
         <f>SUM(G14:G60)</f>
-        <v>10411472.860000003</v>
+        <v>10680704.860000003</v>
       </c>
       <c r="H61" s="80">
         <f t="shared" si="20"/>
-        <v>2601936.9500000002</v>
+        <v>2332704.9500000002</v>
       </c>
       <c r="I61" s="80">
         <f t="shared" si="20"/>
-        <v>81632.781900000002</v>
+        <v>73741.518599999996</v>
       </c>
       <c r="J61" s="81">
         <f t="shared" si="20"/>
@@ -6769,11 +6764,11 @@
       <c r="N61" s="82"/>
       <c r="O61" s="87">
         <f>SUM(O14:O60)</f>
-        <v>9067717.8100000005</v>
+        <v>8790594.8100000005</v>
       </c>
       <c r="P61" s="84">
         <f>SUM(P14:P60)</f>
-        <v>9339747.8100000005</v>
+        <v>9054310.8100000005</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6782,99 +6777,103 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="220" t="s">
+      <c r="C64" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="220"/>
-      <c r="E64" s="220"/>
-      <c r="F64" s="220"/>
-      <c r="G64" s="220"/>
-      <c r="H64" s="220"/>
-      <c r="I64" s="220"/>
-      <c r="J64" s="220"/>
-      <c r="K64" s="220"/>
-      <c r="L64" s="220"/>
-      <c r="M64" s="220"/>
-      <c r="N64" s="220"/>
-      <c r="O64" s="220"/>
+      <c r="D64" s="211"/>
+      <c r="E64" s="211"/>
+      <c r="F64" s="211"/>
+      <c r="G64" s="211"/>
+      <c r="H64" s="211"/>
+      <c r="I64" s="211"/>
+      <c r="J64" s="211"/>
+      <c r="K64" s="211"/>
+      <c r="L64" s="211"/>
+      <c r="M64" s="211"/>
+      <c r="N64" s="211"/>
+      <c r="O64" s="211"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="220"/>
-      <c r="D65" s="220"/>
-      <c r="E65" s="220"/>
-      <c r="F65" s="220"/>
-      <c r="G65" s="220"/>
-      <c r="H65" s="220"/>
-      <c r="I65" s="220"/>
-      <c r="J65" s="220"/>
-      <c r="K65" s="220"/>
-      <c r="L65" s="220"/>
-      <c r="M65" s="220"/>
-      <c r="N65" s="220"/>
-      <c r="O65" s="220"/>
+      <c r="C65" s="211"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="211"/>
+      <c r="F65" s="211"/>
+      <c r="G65" s="211"/>
+      <c r="H65" s="211"/>
+      <c r="I65" s="211"/>
+      <c r="J65" s="211"/>
+      <c r="K65" s="211"/>
+      <c r="L65" s="211"/>
+      <c r="M65" s="211"/>
+      <c r="N65" s="211"/>
+      <c r="O65" s="211"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="220"/>
-      <c r="D66" s="220"/>
-      <c r="E66" s="220"/>
-      <c r="F66" s="220"/>
-      <c r="G66" s="220"/>
-      <c r="H66" s="220"/>
-      <c r="I66" s="220"/>
-      <c r="J66" s="220"/>
-      <c r="K66" s="220"/>
-      <c r="L66" s="220"/>
-      <c r="M66" s="220"/>
-      <c r="N66" s="220"/>
-      <c r="O66" s="220"/>
+      <c r="C66" s="211"/>
+      <c r="D66" s="211"/>
+      <c r="E66" s="211"/>
+      <c r="F66" s="211"/>
+      <c r="G66" s="211"/>
+      <c r="H66" s="211"/>
+      <c r="I66" s="211"/>
+      <c r="J66" s="211"/>
+      <c r="K66" s="211"/>
+      <c r="L66" s="211"/>
+      <c r="M66" s="211"/>
+      <c r="N66" s="211"/>
+      <c r="O66" s="211"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="220"/>
-      <c r="D67" s="220"/>
-      <c r="E67" s="220"/>
-      <c r="F67" s="220"/>
-      <c r="G67" s="220"/>
-      <c r="H67" s="220"/>
-      <c r="I67" s="220"/>
-      <c r="J67" s="220"/>
-      <c r="K67" s="220"/>
-      <c r="L67" s="220"/>
-      <c r="M67" s="220"/>
-      <c r="N67" s="220"/>
-      <c r="O67" s="220"/>
+      <c r="C67" s="211"/>
+      <c r="D67" s="211"/>
+      <c r="E67" s="211"/>
+      <c r="F67" s="211"/>
+      <c r="G67" s="211"/>
+      <c r="H67" s="211"/>
+      <c r="I67" s="211"/>
+      <c r="J67" s="211"/>
+      <c r="K67" s="211"/>
+      <c r="L67" s="211"/>
+      <c r="M67" s="211"/>
+      <c r="N67" s="211"/>
+      <c r="O67" s="211"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="220"/>
-      <c r="D68" s="220"/>
-      <c r="E68" s="220"/>
-      <c r="F68" s="220"/>
-      <c r="G68" s="220"/>
-      <c r="H68" s="220"/>
-      <c r="I68" s="220"/>
-      <c r="J68" s="220"/>
-      <c r="K68" s="220"/>
-      <c r="L68" s="220"/>
-      <c r="M68" s="220"/>
-      <c r="N68" s="220"/>
-      <c r="O68" s="220"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="211"/>
+      <c r="E68" s="211"/>
+      <c r="F68" s="211"/>
+      <c r="G68" s="211"/>
+      <c r="H68" s="211"/>
+      <c r="I68" s="211"/>
+      <c r="J68" s="211"/>
+      <c r="K68" s="211"/>
+      <c r="L68" s="211"/>
+      <c r="M68" s="211"/>
+      <c r="N68" s="211"/>
+      <c r="O68" s="211"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="220"/>
-      <c r="D69" s="220"/>
-      <c r="E69" s="220"/>
-      <c r="F69" s="220"/>
-      <c r="G69" s="220"/>
-      <c r="H69" s="220"/>
-      <c r="I69" s="220"/>
-      <c r="J69" s="220"/>
-      <c r="K69" s="220"/>
-      <c r="L69" s="220"/>
-      <c r="M69" s="220"/>
-      <c r="N69" s="220"/>
-      <c r="O69" s="220"/>
+      <c r="C69" s="211"/>
+      <c r="D69" s="211"/>
+      <c r="E69" s="211"/>
+      <c r="F69" s="211"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="211"/>
+      <c r="I69" s="211"/>
+      <c r="J69" s="211"/>
+      <c r="K69" s="211"/>
+      <c r="L69" s="211"/>
+      <c r="M69" s="211"/>
+      <c r="N69" s="211"/>
+      <c r="O69" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="J1:P5"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C64:O69"/>
     <mergeCell ref="A6:P10"/>
     <mergeCell ref="A12:A13"/>
@@ -6891,10 +6890,6 @@
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J1:P5"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6949,26 +6944,26 @@
       <c r="J6" s="104"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="242" t="s">
+      <c r="C7" s="248" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="E7" s="243"/>
-      <c r="F7" s="243"/>
-      <c r="G7" s="243"/>
-      <c r="H7" s="243"/>
-      <c r="I7" s="243"/>
-      <c r="J7" s="244"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="249"/>
+      <c r="H7" s="249"/>
+      <c r="I7" s="249"/>
+      <c r="J7" s="250"/>
     </row>
     <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="245"/>
-      <c r="D8" s="246"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="246"/>
-      <c r="G8" s="246"/>
-      <c r="H8" s="246"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="247"/>
+      <c r="C8" s="251"/>
+      <c r="D8" s="252"/>
+      <c r="E8" s="252"/>
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="252"/>
+      <c r="J8" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Septiembre/Septiembre ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA48F3B4-F81F-4FFE-BEAA-DB38085C3AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CA20C8-9D98-4AEB-91CF-6B4AB0A69183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="214">
   <si>
     <t>TOTAL</t>
   </si>
@@ -682,6 +677,9 @@
   </si>
   <si>
     <t>Vazquez Miguel Angel</t>
+  </si>
+  <si>
+    <t>Cambon Maria estele transfiere a nombre de la unidad funcional 17 (6B) respetando centavos - Como nos suena "raro el monto" le  repreguntamos: che estas segura que esto es para el 6B? Nos lo confirmas? - Aguardamos respuesta</t>
   </si>
 </sst>
 </file>
@@ -852,7 +850,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -943,6 +941,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="40">
     <border>
@@ -1446,7 +1450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1818,6 +1822,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1863,12 +1900,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1902,33 +1933,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1947,6 +1951,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2030,9 +2038,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2070,9 +2078,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2105,26 +2113,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2157,26 +2148,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2351,22 +2325,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="201" t="s">
         <v>59</v>
@@ -2375,7 +2349,7 @@
       <c r="D1" s="201"/>
       <c r="E1" s="202"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>45</v>
@@ -2384,7 +2358,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="203" t="s">
         <v>142</v>
@@ -2393,7 +2367,7 @@
       <c r="D3" s="203"/>
       <c r="E3" s="204"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -2404,7 +2378,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
@@ -2417,7 +2391,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="57" t="s">
         <v>180</v>
       </c>
@@ -2428,27 +2402,27 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="205" t="s">
         <v>187</v>
       </c>
       <c r="C8" s="205"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="205"/>
       <c r="C10" s="205"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="206" t="s">
         <v>143</v>
       </c>
@@ -2457,49 +2431,49 @@
       <c r="D13" s="206"/>
       <c r="E13" s="206"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="206"/>
       <c r="B14" s="206"/>
       <c r="C14" s="206"/>
       <c r="D14" s="206"/>
       <c r="E14" s="206"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="206"/>
       <c r="B15" s="206"/>
       <c r="C15" s="206"/>
       <c r="D15" s="206"/>
       <c r="E15" s="206"/>
     </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="206"/>
       <c r="B16" s="206"/>
       <c r="C16" s="206"/>
       <c r="D16" s="206"/>
       <c r="E16" s="206"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="191"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="152" t="s">
         <v>7</v>
       </c>
@@ -2508,7 +2482,7 @@
       <c r="D20" s="37"/>
       <c r="E20" s="38"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>60</v>
       </c>
@@ -2517,7 +2491,7 @@
       <c r="D21" s="73"/>
       <c r="E21" s="88"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="196" t="s">
         <v>186</v>
       </c>
@@ -2529,7 +2503,7 @@
       <c r="E22" s="89"/>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="196" t="s">
         <v>48</v>
       </c>
@@ -2542,7 +2516,7 @@
       <c r="F23" s="30"/>
       <c r="H23" s="12"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="196" t="s">
         <v>1</v>
       </c>
@@ -2553,7 +2527,7 @@
       <c r="F24" s="30"/>
       <c r="H24" s="12"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="137" t="s">
         <v>8</v>
       </c>
@@ -2566,7 +2540,7 @@
       </c>
       <c r="F25" s="30"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="137" t="s">
         <v>50</v>
       </c>
@@ -2576,7 +2550,7 @@
       <c r="E26" s="91"/>
       <c r="F26" s="30"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="136"/>
       <c r="B27" s="136"/>
       <c r="C27" s="136"/>
@@ -2584,7 +2558,7 @@
       <c r="E27" s="102"/>
       <c r="F27" s="30"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="136"/>
       <c r="B28" s="136"/>
       <c r="C28" s="136"/>
@@ -2592,7 +2566,7 @@
       <c r="E28" s="102"/>
       <c r="F28" s="30"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="136"/>
       <c r="B29" s="136"/>
       <c r="C29" s="136"/>
@@ -2600,7 +2574,7 @@
       <c r="E29" s="102"/>
       <c r="F29" s="30"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="137" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2587,7 @@
       </c>
       <c r="F30" s="30"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>38</v>
       </c>
@@ -2623,7 +2597,7 @@
       <c r="E31" s="91"/>
       <c r="F31" s="30"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="136" t="s">
         <v>61</v>
       </c>
@@ -2638,7 +2612,7 @@
       <c r="F32" s="30"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="136" t="s">
         <v>146</v>
       </c>
@@ -2655,7 +2629,7 @@
       <c r="F33" s="30"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="136" t="s">
         <v>40</v>
       </c>
@@ -2670,7 +2644,7 @@
       <c r="F34" s="30"/>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="136" t="s">
         <v>42</v>
       </c>
@@ -2686,7 +2660,7 @@
       <c r="F35" s="30"/>
       <c r="G35" s="32"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="136" t="s">
         <v>41</v>
       </c>
@@ -2701,7 +2675,7 @@
       </c>
       <c r="F36" s="30"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="137" t="s">
         <v>39</v>
       </c>
@@ -2714,7 +2688,7 @@
       </c>
       <c r="F37" s="30"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>9</v>
       </c>
@@ -2724,7 +2698,7 @@
       <c r="E38" s="93"/>
       <c r="F38" s="30"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="207" t="s">
         <v>66</v>
       </c>
@@ -2738,7 +2712,7 @@
       </c>
       <c r="F39" s="30"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="207" t="s">
         <v>67</v>
       </c>
@@ -2753,7 +2727,7 @@
       </c>
       <c r="F40" s="30"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="137" t="s">
         <v>10</v>
       </c>
@@ -2766,7 +2740,7 @@
       </c>
       <c r="F41" s="30"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
         <v>11</v>
       </c>
@@ -2776,7 +2750,7 @@
       <c r="E42" s="94"/>
       <c r="F42" s="30"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
         <v>144</v>
       </c>
@@ -2790,7 +2764,7 @@
       </c>
       <c r="F43" s="30"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>64</v>
       </c>
@@ -2802,7 +2776,7 @@
       <c r="E44" s="19"/>
       <c r="F44" s="30"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
         <v>64</v>
       </c>
@@ -2816,7 +2790,7 @@
       </c>
       <c r="F45" s="30"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="207" t="s">
         <v>65</v>
       </c>
@@ -2830,7 +2804,7 @@
       </c>
       <c r="F46" s="30"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="185" t="s">
         <v>63</v>
       </c>
@@ -2844,7 +2818,7 @@
       </c>
       <c r="F47" s="30"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="137" t="s">
         <v>12</v>
       </c>
@@ -2857,7 +2831,7 @@
       </c>
       <c r="F48" s="30"/>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="21" t="s">
         <v>62</v>
       </c>
@@ -2867,7 +2841,7 @@
       <c r="E49" s="96"/>
       <c r="F49" s="30"/>
     </row>
-    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="196" t="s">
         <v>185</v>
       </c>
@@ -2881,7 +2855,7 @@
       </c>
       <c r="F50" s="30"/>
     </row>
-    <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="209" t="s">
         <v>194</v>
       </c>
@@ -2895,7 +2869,7 @@
       </c>
       <c r="F51" s="118"/>
     </row>
-    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="185" t="s">
         <v>205</v>
       </c>
@@ -2909,7 +2883,7 @@
       </c>
       <c r="F52" s="118"/>
     </row>
-    <row r="53" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="182" t="s">
         <v>208</v>
       </c>
@@ -2923,7 +2897,7 @@
       </c>
       <c r="F53" s="118"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="137" t="s">
         <v>0</v>
       </c>
@@ -2936,7 +2910,7 @@
       </c>
       <c r="F54" s="30"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="21" t="s">
         <v>13</v>
       </c>
@@ -2946,7 +2920,7 @@
       <c r="E55" s="88"/>
       <c r="F55" s="30"/>
     </row>
-    <row r="56" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="196" t="s">
         <v>200</v>
       </c>
@@ -2961,7 +2935,7 @@
       </c>
       <c r="F56" s="30"/>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="142" t="s">
         <v>192</v>
       </c>
@@ -2975,7 +2949,7 @@
       </c>
       <c r="F57" s="30"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="137" t="s">
         <v>8</v>
       </c>
@@ -2988,7 +2962,7 @@
       </c>
       <c r="F58" s="30"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="21" t="s">
         <v>14</v>
       </c>
@@ -2998,7 +2972,7 @@
       <c r="E59" s="24"/>
       <c r="F59" s="30"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>68</v>
       </c>
@@ -3010,7 +2984,7 @@
       <c r="E60" s="97"/>
       <c r="F60" s="30"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="25" t="s">
         <v>173</v>
       </c>
@@ -3023,7 +2997,7 @@
       <c r="E61" s="97"/>
       <c r="F61" s="30"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="146" t="s">
         <v>8</v>
       </c>
@@ -3036,7 +3010,7 @@
       </c>
       <c r="F62" s="30"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="25"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -3044,7 +3018,7 @@
       <c r="E63" s="26"/>
       <c r="F63" s="30"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="147" t="s">
         <v>15</v>
       </c>
@@ -3054,7 +3028,7 @@
       <c r="E64" s="28"/>
       <c r="F64" s="30"/>
     </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="148"/>
       <c r="B65" s="30"/>
       <c r="C65" s="30"/>
@@ -3062,7 +3036,7 @@
       <c r="E65" s="31"/>
       <c r="F65" s="118"/>
     </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="149" t="s">
         <v>16</v>
       </c>
@@ -3076,7 +3050,7 @@
       <c r="F66" s="151"/>
       <c r="G66" s="32"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="30"/>
       <c r="B67" s="30"/>
       <c r="C67" s="30"/>
@@ -3084,7 +3058,7 @@
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
     </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="30"/>
       <c r="B68" s="30"/>
       <c r="C68" s="30"/>
@@ -3093,7 +3067,7 @@
       <c r="F68" s="30"/>
       <c r="H68" s="36"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="152" t="s">
         <v>17</v>
       </c>
@@ -3103,7 +3077,7 @@
       <c r="E69" s="38"/>
       <c r="F69" s="30"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="199"/>
       <c r="B70" s="200"/>
       <c r="C70" s="25"/>
@@ -3111,7 +3085,7 @@
       <c r="E70" s="105"/>
       <c r="F70" s="30"/>
     </row>
-    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="30"/>
       <c r="B71" s="30"/>
       <c r="C71" s="30"/>
@@ -3119,7 +3093,7 @@
       <c r="E71" s="25"/>
       <c r="F71" s="30"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="156"/>
       <c r="B72" s="157"/>
       <c r="C72" s="25"/>
@@ -3127,7 +3101,7 @@
       <c r="E72" s="39"/>
       <c r="F72" s="30"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="158" t="s">
         <v>44</v>
       </c>
@@ -3140,7 +3114,7 @@
       </c>
       <c r="F73" s="30"/>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="30"/>
       <c r="B74" s="30"/>
       <c r="C74" s="30"/>
@@ -3148,7 +3122,7 @@
       <c r="E74" s="30"/>
       <c r="F74" s="30"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="147" t="s">
         <v>18</v>
       </c>
@@ -3160,7 +3134,7 @@
       </c>
       <c r="F75" s="30"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="30"/>
       <c r="B76" s="30"/>
       <c r="C76" s="30"/>
@@ -3168,7 +3142,7 @@
       <c r="E76" s="30"/>
       <c r="F76" s="30"/>
     </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="149" t="s">
         <v>19</v>
       </c>
@@ -3181,7 +3155,7 @@
       </c>
       <c r="F77" s="30"/>
     </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="30"/>
       <c r="B78" s="30"/>
       <c r="C78" s="30"/>
@@ -3189,7 +3163,7 @@
       <c r="E78" s="30"/>
       <c r="F78" s="30"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="160" t="s">
         <v>20</v>
       </c>
@@ -3202,7 +3176,7 @@
       <c r="E79" s="30"/>
       <c r="F79" s="30"/>
     </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="160" t="s">
         <v>21</v>
       </c>
@@ -3215,7 +3189,7 @@
       <c r="E80" s="30"/>
       <c r="F80" s="30"/>
     </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="160" t="s">
         <v>22</v>
       </c>
@@ -3228,7 +3202,7 @@
       <c r="E81" s="30"/>
       <c r="F81" s="30"/>
     </row>
-    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="160" t="s">
         <v>23</v>
       </c>
@@ -3241,7 +3215,7 @@
       <c r="E82" s="30"/>
       <c r="F82" s="30"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="30"/>
       <c r="B83" s="30"/>
       <c r="C83" s="30"/>
@@ -3249,7 +3223,7 @@
       <c r="E83" s="30"/>
       <c r="F83" s="30"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="30"/>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -3257,7 +3231,7 @@
       <c r="E84" s="30"/>
       <c r="F84" s="30"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="103" t="s">
         <v>178</v>
       </c>
@@ -3269,7 +3243,7 @@
       <c r="E85" s="30"/>
       <c r="F85" s="30"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="140" t="s">
         <v>184</v>
       </c>
@@ -3281,7 +3255,7 @@
       <c r="E86" s="30"/>
       <c r="F86" s="30"/>
     </row>
-    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="140" t="s">
         <v>183</v>
       </c>
@@ -3294,7 +3268,7 @@
       <c r="E87" s="30"/>
       <c r="F87" s="30"/>
     </row>
-    <row r="88" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="164" t="s">
         <v>175</v>
       </c>
@@ -3307,7 +3281,7 @@
       <c r="E88" s="30"/>
       <c r="F88" s="30"/>
     </row>
-    <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="166"/>
       <c r="B89" s="167"/>
       <c r="C89" s="30"/>
@@ -3315,7 +3289,7 @@
       <c r="E89" s="30"/>
       <c r="F89" s="30"/>
     </row>
-    <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="166"/>
       <c r="B90" s="167"/>
       <c r="C90" s="30"/>
@@ -3323,7 +3297,7 @@
       <c r="E90" s="30"/>
       <c r="F90" s="30"/>
     </row>
-    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="103" t="s">
         <v>159</v>
       </c>
@@ -3335,7 +3309,7 @@
       <c r="E91" s="30"/>
       <c r="F91" s="30"/>
     </row>
-    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="140" t="s">
         <v>160</v>
       </c>
@@ -3347,7 +3321,7 @@
       <c r="E92" s="30"/>
       <c r="F92" s="30"/>
     </row>
-    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="140" t="s">
         <v>161</v>
       </c>
@@ -3357,7 +3331,7 @@
       <c r="E93" s="30"/>
       <c r="F93" s="30"/>
     </row>
-    <row r="94" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="164" t="s">
         <v>175</v>
       </c>
@@ -3370,7 +3344,7 @@
       <c r="E94" s="30"/>
       <c r="F94" s="30"/>
     </row>
-    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="166"/>
       <c r="B95" s="167"/>
       <c r="C95" s="30"/>
@@ -3378,7 +3352,7 @@
       <c r="E95" s="30"/>
       <c r="F95" s="30"/>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="103" t="s">
         <v>162</v>
       </c>
@@ -3390,7 +3364,7 @@
       <c r="E96" s="30"/>
       <c r="F96" s="30"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="140" t="s">
         <v>160</v>
       </c>
@@ -3402,7 +3376,7 @@
       <c r="E97" s="30"/>
       <c r="F97" s="30"/>
     </row>
-    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="140" t="s">
         <v>191</v>
       </c>
@@ -3414,7 +3388,7 @@
       <c r="E98" s="30"/>
       <c r="F98" s="30"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="164" t="s">
         <v>175</v>
       </c>
@@ -3427,14 +3401,14 @@
       <c r="E99" s="30"/>
       <c r="F99" s="30"/>
     </row>
-    <row r="100" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100"/>
       <c r="B100" s="40"/>
       <c r="C100" s="41"/>
       <c r="D100" s="99"/>
       <c r="E100" s="99"/>
     </row>
-    <row r="101" spans="1:6" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" s="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="103" t="s">
         <v>174</v>
       </c>
@@ -3445,7 +3419,7 @@
       <c r="D101" s="100"/>
       <c r="E101" s="100"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="16" t="s">
         <v>43</v>
       </c>
@@ -3456,7 +3430,7 @@
       <c r="D102" s="30"/>
       <c r="E102" s="30"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="16" t="s">
         <v>24</v>
       </c>
@@ -3468,7 +3442,7 @@
       <c r="E103" s="30"/>
       <c r="F103" s="40"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="16" t="s">
         <v>2</v>
       </c>
@@ -3480,7 +3454,7 @@
       <c r="E104" s="30"/>
       <c r="F104" s="40"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="16" t="s">
         <v>211</v>
       </c>
@@ -3492,7 +3466,7 @@
       <c r="E105" s="30"/>
       <c r="F105" s="40"/>
     </row>
-    <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="16" t="s">
         <v>182</v>
       </c>
@@ -3503,7 +3477,7 @@
       <c r="E106" s="30"/>
       <c r="F106" s="40"/>
     </row>
-    <row r="107" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="46" t="s">
         <v>47</v>
       </c>
@@ -3515,10 +3489,10 @@
       <c r="E107" s="32"/>
       <c r="F107" s="32"/>
     </row>
-    <row r="108" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E108" s="32"/>
     </row>
-    <row r="109" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="121" t="s">
         <v>163</v>
       </c>
@@ -3529,20 +3503,20 @@
       <c r="D109" s="32"/>
       <c r="E109" s="32"/>
     </row>
-    <row r="110" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="198" t="s">
         <v>25</v>
       </c>
       <c r="B111" s="198"/>
       <c r="C111" s="198"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="198"/>
       <c r="B112" s="198"/>
       <c r="C112" s="198"/>
     </row>
-    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
         <v>207</v>
       </c>
@@ -3552,7 +3526,7 @@
       <c r="C113" s="49"/>
       <c r="D113" s="35"/>
     </row>
-    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
         <v>207</v>
       </c>
@@ -3562,7 +3536,7 @@
       <c r="C114" s="49"/>
       <c r="D114" s="35"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="50" t="s">
         <v>0</v>
       </c>
@@ -3572,7 +3546,7 @@
       </c>
       <c r="C115" s="52"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M116" s="53"/>
     </row>
   </sheetData>
@@ -3602,27 +3576,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="7" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="8.5546875" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="58"/>
       <c r="B1" s="112"/>
       <c r="C1" s="59"/>
@@ -3632,21 +3606,21 @@
       <c r="G1" s="112"/>
       <c r="H1" s="112"/>
       <c r="I1" s="112"/>
-      <c r="J1" s="239" t="str">
+      <c r="J1" s="211" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
-      <c r="P1" s="240"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="212"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>164</v>
       </c>
@@ -3658,20 +3632,20 @@
         <v>7736519.879999999</v>
       </c>
       <c r="E2" s="60"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="247"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
       <c r="H2" s="60"/>
       <c r="I2" s="60"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
-      <c r="M2" s="241"/>
-      <c r="N2" s="241"/>
-      <c r="O2" s="241"/>
-      <c r="P2" s="242"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="213"/>
+      <c r="L2" s="213"/>
+      <c r="M2" s="213"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="213"/>
+      <c r="P2" s="214"/>
       <c r="Q2" s="54"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -3685,17 +3659,17 @@
       <c r="G3" s="117"/>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
-      <c r="M3" s="241"/>
-      <c r="N3" s="241"/>
-      <c r="O3" s="241"/>
-      <c r="P3" s="242"/>
+      <c r="J3" s="213"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="213"/>
+      <c r="M3" s="213"/>
+      <c r="N3" s="213"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="214"/>
       <c r="Q3" s="54"/>
       <c r="R3" s="32"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>170</v>
       </c>
@@ -3709,17 +3683,17 @@
       <c r="G4" s="117"/>
       <c r="H4" s="60"/>
       <c r="I4" s="60"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="241"/>
-      <c r="N4" s="241"/>
-      <c r="O4" s="241"/>
-      <c r="P4" s="242"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="214"/>
       <c r="Q4" s="54"/>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="123" t="s">
         <v>165</v>
       </c>
@@ -3733,203 +3707,203 @@
       <c r="G5" s="62"/>
       <c r="H5" s="61"/>
       <c r="I5" s="61"/>
-      <c r="J5" s="243"/>
-      <c r="K5" s="243"/>
-      <c r="L5" s="243"/>
-      <c r="M5" s="243"/>
-      <c r="N5" s="243"/>
-      <c r="O5" s="243"/>
-      <c r="P5" s="244"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="215"/>
+      <c r="L5" s="215"/>
+      <c r="M5" s="215"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="215"/>
+      <c r="P5" s="216"/>
       <c r="Q5" s="54"/>
     </row>
-    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="212" t="s">
+    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="223" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="214"/>
-      <c r="F6" s="214"/>
-      <c r="G6" s="214"/>
-      <c r="H6" s="214"/>
-      <c r="I6" s="214"/>
-      <c r="J6" s="214"/>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="214"/>
-      <c r="N6" s="214"/>
-      <c r="O6" s="214"/>
-      <c r="P6" s="215"/>
+      <c r="B6" s="224"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="225"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
       <c r="Q6" s="54"/>
     </row>
-    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="216"/>
-      <c r="B7" s="217"/>
-      <c r="C7" s="217"/>
-      <c r="D7" s="217"/>
-      <c r="E7" s="217"/>
-      <c r="F7" s="217"/>
-      <c r="G7" s="217"/>
-      <c r="H7" s="217"/>
-      <c r="I7" s="217"/>
-      <c r="J7" s="217"/>
-      <c r="K7" s="217"/>
-      <c r="L7" s="217"/>
-      <c r="M7" s="217"/>
-      <c r="N7" s="217"/>
-      <c r="O7" s="217"/>
-      <c r="P7" s="218"/>
+    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="227"/>
+      <c r="B7" s="228"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="228"/>
+      <c r="H7" s="228"/>
+      <c r="I7" s="228"/>
+      <c r="J7" s="228"/>
+      <c r="K7" s="228"/>
+      <c r="L7" s="228"/>
+      <c r="M7" s="228"/>
+      <c r="N7" s="228"/>
+      <c r="O7" s="228"/>
+      <c r="P7" s="229"/>
       <c r="Q7" s="54"/>
     </row>
-    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="216"/>
-      <c r="B8" s="217"/>
-      <c r="C8" s="217"/>
-      <c r="D8" s="217"/>
-      <c r="E8" s="217"/>
-      <c r="F8" s="217"/>
-      <c r="G8" s="217"/>
-      <c r="H8" s="217"/>
-      <c r="I8" s="217"/>
-      <c r="J8" s="217"/>
-      <c r="K8" s="217"/>
-      <c r="L8" s="217"/>
-      <c r="M8" s="217"/>
-      <c r="N8" s="217"/>
-      <c r="O8" s="217"/>
-      <c r="P8" s="218"/>
+    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="227"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="228"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="229"/>
       <c r="Q8" s="54"/>
     </row>
-    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="216"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
-      <c r="D9" s="217"/>
-      <c r="E9" s="217"/>
-      <c r="F9" s="217"/>
-      <c r="G9" s="217"/>
-      <c r="H9" s="217"/>
-      <c r="I9" s="217"/>
-      <c r="J9" s="217"/>
-      <c r="K9" s="217"/>
-      <c r="L9" s="217"/>
-      <c r="M9" s="217"/>
-      <c r="N9" s="217"/>
-      <c r="O9" s="217"/>
-      <c r="P9" s="218"/>
+    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="227"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="228"/>
+      <c r="D9" s="228"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="228"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="228"/>
+      <c r="J9" s="228"/>
+      <c r="K9" s="228"/>
+      <c r="L9" s="228"/>
+      <c r="M9" s="228"/>
+      <c r="N9" s="228"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="229"/>
       <c r="Q9" s="54"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="219"/>
-      <c r="B10" s="220"/>
-      <c r="C10" s="220"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="220"/>
-      <c r="F10" s="220"/>
-      <c r="G10" s="220"/>
-      <c r="H10" s="220"/>
-      <c r="I10" s="220"/>
-      <c r="J10" s="220"/>
-      <c r="K10" s="220"/>
-      <c r="L10" s="220"/>
-      <c r="M10" s="220"/>
-      <c r="N10" s="220"/>
-      <c r="O10" s="220"/>
-      <c r="P10" s="221"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="232" t="s">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="230"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="231"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="231"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="231"/>
+      <c r="N10" s="231"/>
+      <c r="O10" s="231"/>
+      <c r="P10" s="232"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="241" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="233"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
-      <c r="M11" s="233"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="233"/>
-      <c r="P11" s="234"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="222" t="s">
+      <c r="B11" s="242"/>
+      <c r="C11" s="242"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
+      <c r="M11" s="242"/>
+      <c r="N11" s="242"/>
+      <c r="O11" s="242"/>
+      <c r="P11" s="243"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="233" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="246" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="224" t="s">
+      <c r="C12" s="235" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="224" t="s">
+      <c r="D12" s="235" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="224" t="s">
+      <c r="E12" s="235" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="226" t="s">
+      <c r="F12" s="217" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="228" t="s">
+      <c r="G12" s="237" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="230" t="s">
+      <c r="H12" s="239" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="226" t="s">
+      <c r="I12" s="217" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="226" t="s">
+      <c r="J12" s="217" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="226" t="s">
+      <c r="K12" s="217" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="237" t="s">
+      <c r="L12" s="246" t="s">
         <v>169</v>
       </c>
-      <c r="M12" s="226" t="s">
+      <c r="M12" s="217" t="s">
         <v>166</v>
       </c>
-      <c r="N12" s="235" t="s">
+      <c r="N12" s="244" t="s">
         <v>179</v>
       </c>
       <c r="O12" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="245" t="s">
+      <c r="P12" s="219" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="223"/>
-      <c r="B13" s="238"/>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="227"/>
-      <c r="G13" s="229"/>
-      <c r="H13" s="231"/>
-      <c r="I13" s="227"/>
-      <c r="J13" s="227"/>
-      <c r="K13" s="227"/>
-      <c r="L13" s="238"/>
-      <c r="M13" s="227"/>
-      <c r="N13" s="236"/>
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="234"/>
+      <c r="B13" s="247"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="218"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="240"/>
+      <c r="I13" s="218"/>
+      <c r="J13" s="218"/>
+      <c r="K13" s="218"/>
+      <c r="L13" s="247"/>
+      <c r="M13" s="218"/>
+      <c r="N13" s="245"/>
       <c r="O13" s="86" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P13" s="246"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="220"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="75">
         <v>1</v>
       </c>
@@ -3987,7 +3961,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="187">
         <v>2</v>
       </c>
@@ -4051,7 +4025,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="75">
         <v>3</v>
       </c>
@@ -4114,7 +4088,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="75">
         <v>4</v>
       </c>
@@ -4178,7 +4152,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="75">
         <v>5</v>
       </c>
@@ -4238,7 +4212,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="75">
         <v>6</v>
       </c>
@@ -4299,7 +4273,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="75">
         <v>7</v>
       </c>
@@ -4358,7 +4332,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="75">
         <v>8</v>
       </c>
@@ -4417,7 +4391,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="187">
         <v>9</v>
       </c>
@@ -4478,7 +4452,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="75">
         <v>10</v>
       </c>
@@ -4537,7 +4511,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="75">
         <v>11</v>
       </c>
@@ -4600,7 +4574,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="75">
         <v>12</v>
       </c>
@@ -4661,7 +4635,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="75">
         <v>13</v>
       </c>
@@ -4720,7 +4694,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="126">
         <v>14</v>
       </c>
@@ -4779,7 +4753,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="75">
         <v>15</v>
       </c>
@@ -4840,7 +4814,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="75">
         <v>16</v>
       </c>
@@ -4899,11 +4873,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="187">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="256">
         <v>17</v>
       </c>
-      <c r="B30" s="188" t="s">
+      <c r="B30" s="257" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="189" t="s">
@@ -4959,7 +4933,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="75">
         <v>18</v>
       </c>
@@ -5018,7 +4992,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="75">
         <v>19</v>
       </c>
@@ -5077,7 +5051,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="75">
         <v>20</v>
       </c>
@@ -5133,7 +5107,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="75">
         <v>21</v>
       </c>
@@ -5194,7 +5168,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="75">
         <f>A34+1</f>
         <v>22</v>
@@ -5256,7 +5230,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="75">
         <f t="shared" ref="A36:A59" si="15">A35+1</f>
         <v>23</v>
@@ -5317,7 +5291,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="75">
         <f t="shared" si="15"/>
         <v>24</v>
@@ -5380,7 +5354,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="75">
         <f t="shared" si="15"/>
         <v>25</v>
@@ -5442,7 +5416,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="75">
         <f t="shared" si="15"/>
         <v>26</v>
@@ -5502,7 +5476,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="75">
         <f t="shared" si="15"/>
         <v>27</v>
@@ -5562,7 +5536,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="187">
         <f t="shared" si="15"/>
         <v>28</v>
@@ -5627,7 +5601,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="75">
         <f t="shared" si="15"/>
         <v>29</v>
@@ -5686,7 +5660,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="75">
         <f t="shared" si="15"/>
         <v>30</v>
@@ -5746,7 +5720,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="75">
         <f t="shared" si="15"/>
         <v>31</v>
@@ -5811,7 +5785,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="75">
         <f t="shared" si="15"/>
         <v>32</v>
@@ -5871,7 +5845,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="75">
         <f t="shared" si="15"/>
         <v>33</v>
@@ -5928,7 +5902,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="75">
         <f t="shared" si="15"/>
         <v>34</v>
@@ -5987,7 +5961,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="106">
         <f t="shared" si="15"/>
         <v>35</v>
@@ -6044,7 +6018,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="75">
         <f t="shared" si="15"/>
         <v>36</v>
@@ -6104,7 +6078,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="75">
         <f t="shared" si="15"/>
         <v>37</v>
@@ -6161,7 +6135,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="75">
         <f t="shared" si="15"/>
         <v>38</v>
@@ -6221,7 +6195,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="75">
         <f t="shared" si="15"/>
         <v>39</v>
@@ -6281,7 +6255,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="75">
         <f t="shared" si="15"/>
         <v>40</v>
@@ -6342,7 +6316,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="75">
         <f t="shared" si="15"/>
         <v>41</v>
@@ -6403,7 +6377,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="75">
         <f t="shared" si="15"/>
         <v>42</v>
@@ -6465,7 +6439,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="75">
         <f t="shared" si="15"/>
         <v>43</v>
@@ -6522,7 +6496,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="75">
         <f t="shared" si="15"/>
         <v>44</v>
@@ -6579,7 +6553,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="75">
         <f t="shared" si="15"/>
         <v>45</v>
@@ -6641,7 +6615,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="75">
         <f t="shared" si="15"/>
         <v>46</v>
@@ -6701,7 +6675,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="75"/>
       <c r="B60" s="115"/>
       <c r="C60" s="64"/>
@@ -6720,7 +6694,7 @@
       <c r="P60" s="83"/>
       <c r="Q60" s="32"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="76"/>
       <c r="B61" s="116"/>
       <c r="C61" s="77"/>
@@ -6771,105 +6745,109 @@
         <v>9054310.8100000005</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="211" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="211"/>
-      <c r="E64" s="211"/>
-      <c r="F64" s="211"/>
-      <c r="G64" s="211"/>
-      <c r="H64" s="211"/>
-      <c r="I64" s="211"/>
-      <c r="J64" s="211"/>
-      <c r="K64" s="211"/>
-      <c r="L64" s="211"/>
-      <c r="M64" s="211"/>
-      <c r="N64" s="211"/>
-      <c r="O64" s="211"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="211"/>
-      <c r="D65" s="211"/>
-      <c r="E65" s="211"/>
-      <c r="F65" s="211"/>
-      <c r="G65" s="211"/>
-      <c r="H65" s="211"/>
-      <c r="I65" s="211"/>
-      <c r="J65" s="211"/>
-      <c r="K65" s="211"/>
-      <c r="L65" s="211"/>
-      <c r="M65" s="211"/>
-      <c r="N65" s="211"/>
-      <c r="O65" s="211"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="211"/>
-      <c r="D66" s="211"/>
-      <c r="E66" s="211"/>
-      <c r="F66" s="211"/>
-      <c r="G66" s="211"/>
-      <c r="H66" s="211"/>
-      <c r="I66" s="211"/>
-      <c r="J66" s="211"/>
-      <c r="K66" s="211"/>
-      <c r="L66" s="211"/>
-      <c r="M66" s="211"/>
-      <c r="N66" s="211"/>
-      <c r="O66" s="211"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="211"/>
-      <c r="D67" s="211"/>
-      <c r="E67" s="211"/>
-      <c r="F67" s="211"/>
-      <c r="G67" s="211"/>
-      <c r="H67" s="211"/>
-      <c r="I67" s="211"/>
-      <c r="J67" s="211"/>
-      <c r="K67" s="211"/>
-      <c r="L67" s="211"/>
-      <c r="M67" s="211"/>
-      <c r="N67" s="211"/>
-      <c r="O67" s="211"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="211"/>
-      <c r="D68" s="211"/>
-      <c r="E68" s="211"/>
-      <c r="F68" s="211"/>
-      <c r="G68" s="211"/>
-      <c r="H68" s="211"/>
-      <c r="I68" s="211"/>
-      <c r="J68" s="211"/>
-      <c r="K68" s="211"/>
-      <c r="L68" s="211"/>
-      <c r="M68" s="211"/>
-      <c r="N68" s="211"/>
-      <c r="O68" s="211"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="211"/>
-      <c r="D69" s="211"/>
-      <c r="E69" s="211"/>
-      <c r="F69" s="211"/>
-      <c r="G69" s="211"/>
-      <c r="H69" s="211"/>
-      <c r="I69" s="211"/>
-      <c r="J69" s="211"/>
-      <c r="K69" s="211"/>
-      <c r="L69" s="211"/>
-      <c r="M69" s="211"/>
-      <c r="N69" s="211"/>
-      <c r="O69" s="211"/>
+      <c r="D64" s="222"/>
+      <c r="E64" s="222"/>
+      <c r="F64" s="222"/>
+      <c r="G64" s="222"/>
+      <c r="H64" s="222"/>
+      <c r="I64" s="222"/>
+      <c r="J64" s="222"/>
+      <c r="K64" s="222"/>
+      <c r="L64" s="222"/>
+      <c r="M64" s="222"/>
+      <c r="N64" s="222"/>
+      <c r="O64" s="222"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="222"/>
+      <c r="D65" s="222"/>
+      <c r="E65" s="222"/>
+      <c r="F65" s="222"/>
+      <c r="G65" s="222"/>
+      <c r="H65" s="222"/>
+      <c r="I65" s="222"/>
+      <c r="J65" s="222"/>
+      <c r="K65" s="222"/>
+      <c r="L65" s="222"/>
+      <c r="M65" s="222"/>
+      <c r="N65" s="222"/>
+      <c r="O65" s="222"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="222"/>
+      <c r="D66" s="222"/>
+      <c r="E66" s="222"/>
+      <c r="F66" s="222"/>
+      <c r="G66" s="222"/>
+      <c r="H66" s="222"/>
+      <c r="I66" s="222"/>
+      <c r="J66" s="222"/>
+      <c r="K66" s="222"/>
+      <c r="L66" s="222"/>
+      <c r="M66" s="222"/>
+      <c r="N66" s="222"/>
+      <c r="O66" s="222"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="222"/>
+      <c r="D67" s="222"/>
+      <c r="E67" s="222"/>
+      <c r="F67" s="222"/>
+      <c r="G67" s="222"/>
+      <c r="H67" s="222"/>
+      <c r="I67" s="222"/>
+      <c r="J67" s="222"/>
+      <c r="K67" s="222"/>
+      <c r="L67" s="222"/>
+      <c r="M67" s="222"/>
+      <c r="N67" s="222"/>
+      <c r="O67" s="222"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="222"/>
+      <c r="D68" s="222"/>
+      <c r="E68" s="222"/>
+      <c r="F68" s="222"/>
+      <c r="G68" s="222"/>
+      <c r="H68" s="222"/>
+      <c r="I68" s="222"/>
+      <c r="J68" s="222"/>
+      <c r="K68" s="222"/>
+      <c r="L68" s="222"/>
+      <c r="M68" s="222"/>
+      <c r="N68" s="222"/>
+      <c r="O68" s="222"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="222"/>
+      <c r="D69" s="222"/>
+      <c r="E69" s="222"/>
+      <c r="F69" s="222"/>
+      <c r="G69" s="222"/>
+      <c r="H69" s="222"/>
+      <c r="I69" s="222"/>
+      <c r="J69" s="222"/>
+      <c r="K69" s="222"/>
+      <c r="L69" s="222"/>
+      <c r="M69" s="222"/>
+      <c r="N69" s="222"/>
+      <c r="O69" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6886,10 +6864,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6899,14 +6873,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C4:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C4:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" s="180" t="s">
         <v>51</v>
       </c>
@@ -6919,7 +6893,7 @@
       </c>
       <c r="J4" s="104"/>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" s="180" t="s">
         <v>54</v>
       </c>
@@ -6937,13 +6911,13 @@
       </c>
       <c r="J5" s="104"/>
     </row>
-    <row r="6" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="29" t="s">
         <v>57</v>
       </c>
       <c r="J6" s="104"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="248" t="s">
         <v>199</v>
       </c>
@@ -6955,7 +6929,7 @@
       <c r="I7" s="249"/>
       <c r="J7" s="250"/>
     </row>
-    <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="251"/>
       <c r="D8" s="252"/>
       <c r="E8" s="252"/>
@@ -6965,9 +6939,73 @@
       <c r="I8" s="252"/>
       <c r="J8" s="253"/>
     </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="255" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="254"/>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="104"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="255" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="254" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="104"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="104"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="248" t="s">
+        <v>213</v>
+      </c>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="250"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="251"/>
+      <c r="D15" s="252"/>
+      <c r="E15" s="252"/>
+      <c r="F15" s="252"/>
+      <c r="G15" s="252"/>
+      <c r="H15" s="252"/>
+      <c r="I15" s="252"/>
+      <c r="J15" s="253"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C7:J8"/>
+    <mergeCell ref="C14:J15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
